--- a/SYMBEAST_Evolve_Forms.xlsx
+++ b/SYMBEAST_Evolve_Forms.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\skyit\Desktop\Symbeast-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65711DEB-68B4-4330-A764-22A77FC06920}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A144408-308F-45E6-BBF4-CD63EAA0DFF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2607" uniqueCount="1660">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2601" uniqueCount="1656">
   <si>
     <t>SYMBEAST — Evolved Forms (Stage 1, 10 forms)</t>
   </si>
@@ -4065,18 +4065,6 @@
   </si>
   <si>
     <t>39%</t>
-  </si>
-  <si>
-    <t>42%</t>
-  </si>
-  <si>
-    <t>23%</t>
-  </si>
-  <si>
-    <t>43%</t>
-  </si>
-  <si>
-    <t>32%</t>
   </si>
   <si>
     <t>Weapon การันตี 1 ชิ้นทุกครั้งที่ชนะ Wave 3 (บอสพิเศษ) — เกรดสุ่มตามตาราง</t>
@@ -5048,9 +5036,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -8055,11 +8044,11 @@
       <c r="B62" t="s">
         <v>918</v>
       </c>
-      <c r="C62" t="s">
-        <v>1344</v>
-      </c>
-      <c r="D62" t="s">
-        <v>1345</v>
+      <c r="C62" s="2">
+        <v>0.45</v>
+      </c>
+      <c r="D62" s="2">
+        <v>0.2</v>
       </c>
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.3">
@@ -8069,11 +8058,11 @@
       <c r="B63" t="s">
         <v>905</v>
       </c>
-      <c r="C63" t="s">
-        <v>1346</v>
-      </c>
-      <c r="D63" t="s">
-        <v>1347</v>
+      <c r="C63" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="D63" s="2">
+        <v>0.25</v>
       </c>
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.3">
@@ -8083,21 +8072,21 @@
       <c r="B64" t="s">
         <v>976</v>
       </c>
-      <c r="C64" t="s">
-        <v>1012</v>
-      </c>
-      <c r="D64" t="s">
-        <v>1342</v>
+      <c r="C64" s="2">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="D64" s="2">
+        <v>0.3</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>1348</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>1349</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
@@ -8105,19 +8094,19 @@
         <v>1331</v>
       </c>
       <c r="B69" t="s">
+        <v>1346</v>
+      </c>
+      <c r="C69" t="s">
+        <v>1347</v>
+      </c>
+      <c r="D69" t="s">
+        <v>1348</v>
+      </c>
+      <c r="E69" t="s">
+        <v>1349</v>
+      </c>
+      <c r="F69" t="s">
         <v>1350</v>
-      </c>
-      <c r="C69" t="s">
-        <v>1351</v>
-      </c>
-      <c r="D69" t="s">
-        <v>1352</v>
-      </c>
-      <c r="E69" t="s">
-        <v>1353</v>
-      </c>
-      <c r="F69" t="s">
-        <v>1354</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
@@ -8145,7 +8134,7 @@
         <v>985</v>
       </c>
       <c r="B71" t="s">
-        <v>1355</v>
+        <v>1351</v>
       </c>
       <c r="C71" t="s">
         <v>910</v>
@@ -8185,7 +8174,7 @@
         <v>979</v>
       </c>
       <c r="B73" t="s">
-        <v>1356</v>
+        <v>1352</v>
       </c>
       <c r="C73" t="s">
         <v>910</v>
@@ -8194,7 +8183,7 @@
         <v>910</v>
       </c>
       <c r="E73" t="s">
-        <v>1357</v>
+        <v>1353</v>
       </c>
       <c r="F73" t="s">
         <v>913</v>
@@ -8205,7 +8194,7 @@
         <v>978</v>
       </c>
       <c r="B74" t="s">
-        <v>1358</v>
+        <v>1354</v>
       </c>
       <c r="C74" t="s">
         <v>980</v>
@@ -8234,10 +8223,10 @@
         <v>910</v>
       </c>
       <c r="E75" t="s">
-        <v>1359</v>
+        <v>1355</v>
       </c>
       <c r="F75" t="s">
-        <v>1360</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
@@ -8245,7 +8234,7 @@
         <v>1309</v>
       </c>
       <c r="B76" t="s">
-        <v>1361</v>
+        <v>1357</v>
       </c>
       <c r="C76" t="s">
         <v>984</v>
@@ -8265,7 +8254,7 @@
         <v>983</v>
       </c>
       <c r="B77" t="s">
-        <v>1362</v>
+        <v>1358</v>
       </c>
       <c r="C77" t="s">
         <v>908</v>
@@ -8274,10 +8263,10 @@
         <v>986</v>
       </c>
       <c r="E77" t="s">
-        <v>1363</v>
+        <v>1359</v>
       </c>
       <c r="F77" t="s">
-        <v>1355</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
@@ -8285,7 +8274,7 @@
         <v>1312</v>
       </c>
       <c r="B78" t="s">
-        <v>1364</v>
+        <v>1360</v>
       </c>
       <c r="C78" t="s">
         <v>1041</v>
@@ -8294,7 +8283,7 @@
         <v>980</v>
       </c>
       <c r="E78" t="s">
-        <v>1365</v>
+        <v>1361</v>
       </c>
       <c r="F78" t="s">
         <v>976</v>
@@ -8305,7 +8294,7 @@
         <v>977</v>
       </c>
       <c r="B79" t="s">
-        <v>1366</v>
+        <v>1362</v>
       </c>
       <c r="C79" t="s">
         <v>1019</v>
@@ -8322,18 +8311,18 @@
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>1367</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:M82" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:M61 A65:M82 A62:B62 E62:M62 A63:B63 E63:M63 A64:B64 E64:M64" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -8345,17 +8334,17 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -8371,7 +8360,7 @@
         <v>1263</v>
       </c>
       <c r="B6" t="s">
-        <v>1372</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
@@ -8379,23 +8368,23 @@
         <v>1265</v>
       </c>
       <c r="B7" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>1374</v>
+        <v>1370</v>
       </c>
       <c r="B8" t="s">
-        <v>1375</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>1376</v>
+        <v>1372</v>
       </c>
       <c r="B9" t="s">
-        <v>1377</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
@@ -8403,7 +8392,7 @@
         <v>1277</v>
       </c>
       <c r="B10" t="s">
-        <v>1378</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
@@ -8411,157 +8400,157 @@
         <v>1279</v>
       </c>
       <c r="B11" t="s">
-        <v>1379</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>1380</v>
+        <v>1376</v>
       </c>
       <c r="B12" t="s">
-        <v>1381</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>1382</v>
+        <v>1378</v>
       </c>
       <c r="B13" t="s">
-        <v>1383</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>1384</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>1385</v>
+        <v>1381</v>
       </c>
       <c r="B16" t="s">
-        <v>1386</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>1387</v>
+        <v>1383</v>
       </c>
       <c r="B17" t="s">
-        <v>1388</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>1389</v>
+        <v>1385</v>
       </c>
       <c r="B18" t="s">
-        <v>1390</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>1391</v>
+        <v>1387</v>
       </c>
       <c r="B19" t="s">
-        <v>1392</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>1393</v>
+        <v>1389</v>
       </c>
       <c r="B20" t="s">
-        <v>1394</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>1395</v>
+        <v>1391</v>
       </c>
       <c r="B22" t="s">
-        <v>1396</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>1397</v>
+        <v>1393</v>
       </c>
       <c r="B23" t="s">
-        <v>1398</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>1399</v>
+        <v>1395</v>
       </c>
       <c r="B24" t="s">
-        <v>1400</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>1401</v>
+        <v>1397</v>
       </c>
       <c r="B25" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>1403</v>
+        <v>1399</v>
       </c>
       <c r="B26" t="s">
-        <v>1404</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>1406</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>1395</v>
+        <v>1391</v>
       </c>
       <c r="B31" t="s">
-        <v>1407</v>
+        <v>1403</v>
       </c>
       <c r="C31" t="s">
-        <v>1408</v>
+        <v>1404</v>
       </c>
       <c r="D31" t="s">
-        <v>1409</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>1410</v>
+        <v>1406</v>
       </c>
       <c r="B32" t="s">
-        <v>1411</v>
+        <v>1407</v>
       </c>
       <c r="C32" t="s">
-        <v>1411</v>
+        <v>1407</v>
       </c>
       <c r="D32" t="s">
-        <v>1412</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>1413</v>
+        <v>1409</v>
       </c>
       <c r="B33" t="s">
-        <v>1414</v>
+        <v>1410</v>
       </c>
       <c r="C33" t="s">
-        <v>1411</v>
+        <v>1407</v>
       </c>
       <c r="D33" t="s">
         <v>906</v>
@@ -8569,77 +8558,77 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>1415</v>
+        <v>1411</v>
       </c>
       <c r="B34" t="s">
-        <v>1414</v>
+        <v>1410</v>
       </c>
       <c r="C34" t="s">
-        <v>1414</v>
+        <v>1410</v>
       </c>
       <c r="D34" t="s">
-        <v>1416</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>1417</v>
+        <v>1413</v>
       </c>
       <c r="B35" t="s">
-        <v>1411</v>
+        <v>1407</v>
       </c>
       <c r="C35" t="s">
-        <v>1418</v>
+        <v>1414</v>
       </c>
       <c r="D35" t="s">
-        <v>1419</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>1420</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>1421</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>1422</v>
+        <v>1418</v>
       </c>
       <c r="B40" t="s">
-        <v>1423</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>1424</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>1395</v>
+        <v>1391</v>
       </c>
       <c r="B43" t="s">
-        <v>1425</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>1426</v>
+        <v>1422</v>
       </c>
       <c r="B44" t="s">
-        <v>1427</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>1428</v>
+        <v>1424</v>
       </c>
       <c r="B45" t="s">
-        <v>1429</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
@@ -8647,17 +8636,17 @@
         <v>1314</v>
       </c>
       <c r="B46" t="s">
-        <v>1430</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>1431</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>1432</v>
+        <v>1428</v>
       </c>
       <c r="B50" t="s">
         <v>944</v>
@@ -8668,15 +8657,15 @@
         <v>977</v>
       </c>
       <c r="B51" t="s">
-        <v>1433</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>1434</v>
+        <v>1430</v>
       </c>
       <c r="B52" t="s">
-        <v>1435</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
@@ -8684,7 +8673,7 @@
         <v>1302</v>
       </c>
       <c r="B53" t="s">
-        <v>1436</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
@@ -8692,7 +8681,7 @@
         <v>1303</v>
       </c>
       <c r="B54" t="s">
-        <v>1437</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
@@ -8700,7 +8689,7 @@
         <v>1305</v>
       </c>
       <c r="B55" t="s">
-        <v>1438</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
@@ -8708,7 +8697,7 @@
         <v>1307</v>
       </c>
       <c r="B56" t="s">
-        <v>1439</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
@@ -8716,7 +8705,7 @@
         <v>1310</v>
       </c>
       <c r="B57" t="s">
-        <v>1440</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
@@ -8724,7 +8713,7 @@
         <v>1311</v>
       </c>
       <c r="B58" t="s">
-        <v>1439</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
@@ -8732,7 +8721,7 @@
         <v>1313</v>
       </c>
       <c r="B59" t="s">
-        <v>1438</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
@@ -8740,47 +8729,47 @@
         <v>1314</v>
       </c>
       <c r="B60" t="s">
-        <v>1441</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>1442</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>1443</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>1444</v>
+        <v>1440</v>
       </c>
       <c r="B65" t="s">
-        <v>1445</v>
+        <v>1441</v>
       </c>
       <c r="C65" t="s">
-        <v>1446</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>1447</v>
+        <v>1443</v>
       </c>
       <c r="B66" t="s">
-        <v>1448</v>
+        <v>1444</v>
       </c>
       <c r="C66" t="s">
-        <v>1449</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>1450</v>
+        <v>1446</v>
       </c>
       <c r="B67" t="s">
-        <v>1451</v>
+        <v>1447</v>
       </c>
       <c r="C67" t="s">
         <v>792</v>
@@ -8788,10 +8777,10 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>1452</v>
+        <v>1448</v>
       </c>
       <c r="B68" t="s">
-        <v>1453</v>
+        <v>1449</v>
       </c>
       <c r="C68" t="s">
         <v>798</v>
@@ -8799,17 +8788,17 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>1454</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>1455</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>1432</v>
+        <v>1428</v>
       </c>
       <c r="B73" t="s">
         <v>5</v>
@@ -8996,90 +8985,90 @@
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>1456</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>1457</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>1444</v>
+        <v>1440</v>
       </c>
       <c r="B88" t="s">
-        <v>1458</v>
+        <v>1454</v>
       </c>
       <c r="C88" t="s">
-        <v>1459</v>
+        <v>1455</v>
       </c>
       <c r="D88" t="s">
-        <v>1460</v>
+        <v>1456</v>
       </c>
       <c r="E88" t="s">
-        <v>1461</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>1447</v>
+        <v>1443</v>
       </c>
       <c r="B89" t="s">
-        <v>1462</v>
+        <v>1458</v>
       </c>
       <c r="C89" t="s">
-        <v>1463</v>
+        <v>1459</v>
       </c>
       <c r="D89" t="s">
-        <v>1464</v>
+        <v>1460</v>
       </c>
       <c r="E89" t="s">
-        <v>1465</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>1450</v>
+        <v>1446</v>
       </c>
       <c r="B90" t="s">
-        <v>1466</v>
+        <v>1462</v>
       </c>
       <c r="C90" t="s">
-        <v>1465</v>
+        <v>1461</v>
       </c>
       <c r="D90" t="s">
-        <v>1467</v>
+        <v>1463</v>
       </c>
       <c r="E90" t="s">
-        <v>1468</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>1452</v>
+        <v>1448</v>
       </c>
       <c r="B91" t="s">
-        <v>1469</v>
+        <v>1465</v>
       </c>
       <c r="C91" t="s">
-        <v>1464</v>
+        <v>1460</v>
       </c>
       <c r="D91" t="s">
-        <v>1470</v>
+        <v>1466</v>
       </c>
       <c r="E91" t="s">
-        <v>1471</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>1472</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>1473</v>
+        <v>1469</v>
       </c>
       <c r="B94" t="s">
         <v>944</v>
@@ -9087,23 +9076,23 @@
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>1474</v>
+        <v>1470</v>
       </c>
       <c r="B95" t="s">
-        <v>1475</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>1476</v>
+        <v>1472</v>
       </c>
       <c r="B96" t="s">
-        <v>1477</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>1478</v>
+        <v>1474</v>
       </c>
     </row>
   </sheetData>
@@ -9121,17 +9110,17 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>1479</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>1480</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>1481</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -9144,18 +9133,18 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>1482</v>
+        <v>1478</v>
       </c>
       <c r="B6" t="s">
-        <v>1483</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>1484</v>
+        <v>1480</v>
       </c>
       <c r="B7" t="s">
-        <v>1485</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
@@ -9163,23 +9152,23 @@
         <v>1300</v>
       </c>
       <c r="B8" t="s">
-        <v>1486</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>1487</v>
+        <v>1483</v>
       </c>
       <c r="B9" t="s">
-        <v>1488</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>1489</v>
+        <v>1485</v>
       </c>
       <c r="B10" t="s">
-        <v>1490</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
@@ -9187,15 +9176,15 @@
         <v>823</v>
       </c>
       <c r="B11" t="s">
-        <v>1491</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>1382</v>
+        <v>1378</v>
       </c>
       <c r="B12" t="s">
-        <v>1492</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
@@ -9203,70 +9192,70 @@
         <v>1279</v>
       </c>
       <c r="B13" t="s">
-        <v>1493</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>1494</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>1495</v>
+        <v>1491</v>
       </c>
       <c r="B16" t="s">
-        <v>1496</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>1497</v>
+        <v>1493</v>
       </c>
       <c r="B17" t="s">
-        <v>1498</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>1499</v>
+        <v>1495</v>
       </c>
       <c r="B18" t="s">
-        <v>1500</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>1389</v>
+        <v>1385</v>
       </c>
       <c r="B19" t="s">
-        <v>1501</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>1391</v>
+        <v>1387</v>
       </c>
       <c r="B20" t="s">
-        <v>1502</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>1393</v>
+        <v>1389</v>
       </c>
       <c r="B21" t="s">
-        <v>1503</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>1504</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>1505</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
@@ -9274,70 +9263,70 @@
         <v>944</v>
       </c>
       <c r="B26" t="s">
-        <v>1506</v>
+        <v>1502</v>
       </c>
       <c r="C26" t="s">
-        <v>1507</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>1508</v>
+        <v>1504</v>
       </c>
       <c r="B27" t="s">
-        <v>1509</v>
+        <v>1505</v>
       </c>
       <c r="C27" t="s">
-        <v>1510</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>1511</v>
+        <v>1507</v>
       </c>
       <c r="B28" t="s">
-        <v>1512</v>
+        <v>1508</v>
       </c>
       <c r="C28" t="s">
-        <v>1513</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>1514</v>
+        <v>1510</v>
       </c>
       <c r="B29" t="s">
-        <v>1515</v>
+        <v>1511</v>
       </c>
       <c r="C29" t="s">
-        <v>1513</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>1516</v>
+        <v>1512</v>
       </c>
       <c r="B30" t="s">
-        <v>1517</v>
+        <v>1513</v>
       </c>
       <c r="C30" t="s">
-        <v>1518</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>1519</v>
+        <v>1515</v>
       </c>
       <c r="B31" t="s">
-        <v>1520</v>
+        <v>1516</v>
       </c>
       <c r="C31" t="s">
-        <v>1521</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>1522</v>
+        <v>1518</v>
       </c>
       <c r="B32" t="s">
         <v>904</v>
@@ -9348,7 +9337,7 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>1523</v>
+        <v>1519</v>
       </c>
       <c r="B33" t="s">
         <v>905</v>
@@ -9359,7 +9348,7 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>1524</v>
+        <v>1520</v>
       </c>
       <c r="B34" t="s">
         <v>913</v>
@@ -9370,7 +9359,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>1525</v>
+        <v>1521</v>
       </c>
       <c r="B35" t="s">
         <v>908</v>
@@ -9381,7 +9370,7 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>1526</v>
+        <v>1522</v>
       </c>
       <c r="B36" t="s">
         <v>910</v>
@@ -9392,7 +9381,7 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>1527</v>
+        <v>1523</v>
       </c>
       <c r="B37" t="s">
         <v>910</v>
@@ -9403,29 +9392,29 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>1528</v>
+        <v>1524</v>
       </c>
       <c r="B38" t="s">
         <v>910</v>
       </c>
       <c r="C38" t="s">
-        <v>1529</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>1530</v>
+        <v>1526</v>
       </c>
       <c r="B39" t="s">
         <v>910</v>
       </c>
       <c r="C39" t="s">
-        <v>1531</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>1532</v>
+        <v>1528</v>
       </c>
       <c r="B40" t="s">
         <v>913</v>
@@ -9436,7 +9425,7 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>1533</v>
+        <v>1529</v>
       </c>
       <c r="B41" t="s">
         <v>913</v>
@@ -9447,7 +9436,7 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>1534</v>
+        <v>1530</v>
       </c>
       <c r="B42" t="s">
         <v>910</v>
@@ -9458,7 +9447,7 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>1535</v>
+        <v>1531</v>
       </c>
       <c r="B43" t="s">
         <v>905</v>
@@ -9469,7 +9458,7 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>1536</v>
+        <v>1532</v>
       </c>
       <c r="B44" t="s">
         <v>913</v>
@@ -9480,35 +9469,35 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>1537</v>
+        <v>1533</v>
       </c>
       <c r="B45" t="s">
-        <v>1538</v>
+        <v>1534</v>
       </c>
       <c r="C45" t="s">
-        <v>1539</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>1540</v>
+        <v>1536</v>
       </c>
       <c r="B46" t="s">
-        <v>1541</v>
+        <v>1537</v>
       </c>
       <c r="C46" t="s">
-        <v>1521</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>1542</v>
+        <v>1538</v>
       </c>
       <c r="B48" t="s">
-        <v>1543</v>
+        <v>1539</v>
       </c>
       <c r="C48" t="s">
-        <v>1544</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
@@ -9516,32 +9505,32 @@
         <v>781</v>
       </c>
       <c r="B49" t="s">
-        <v>1545</v>
+        <v>1541</v>
       </c>
       <c r="C49" t="s">
-        <v>1546</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>1547</v>
+        <v>1543</v>
       </c>
       <c r="B50" t="s">
-        <v>1548</v>
+        <v>1544</v>
       </c>
       <c r="C50" t="s">
-        <v>1549</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>1550</v>
+        <v>1546</v>
       </c>
       <c r="B51" t="s">
-        <v>1551</v>
+        <v>1547</v>
       </c>
       <c r="C51" t="s">
-        <v>1552</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
@@ -9549,26 +9538,26 @@
         <v>823</v>
       </c>
       <c r="B52" t="s">
-        <v>1553</v>
+        <v>1549</v>
       </c>
       <c r="C52" t="s">
-        <v>1554</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>1555</v>
+        <v>1551</v>
       </c>
       <c r="B54" t="s">
         <v>969</v>
       </c>
       <c r="C54" t="s">
-        <v>1556</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>1557</v>
+        <v>1553</v>
       </c>
       <c r="B55" t="s">
         <v>939</v>
@@ -9579,7 +9568,7 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>1558</v>
+        <v>1554</v>
       </c>
       <c r="B56" t="s">
         <v>920</v>
@@ -9590,10 +9579,10 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>1559</v>
+        <v>1555</v>
       </c>
       <c r="B57" t="s">
-        <v>1560</v>
+        <v>1556</v>
       </c>
       <c r="C57" t="s">
         <v>905</v>
@@ -9601,40 +9590,40 @@
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>1561</v>
+        <v>1557</v>
       </c>
       <c r="B58" t="s">
-        <v>1560</v>
+        <v>1556</v>
       </c>
       <c r="C58" t="s">
-        <v>1560</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>1562</v>
+        <v>1558</v>
       </c>
       <c r="B59" t="s">
-        <v>1560</v>
+        <v>1556</v>
       </c>
       <c r="C59" t="s">
-        <v>1560</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>1563</v>
+        <v>1559</v>
       </c>
       <c r="B60" t="s">
-        <v>1560</v>
+        <v>1556</v>
       </c>
       <c r="C60" t="s">
-        <v>1560</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>1564</v>
+        <v>1560</v>
       </c>
       <c r="B61" t="s">
         <v>940</v>
@@ -9645,36 +9634,36 @@
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>1565</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>1568</v>
+        <v>1564</v>
       </c>
       <c r="B67" t="s">
         <v>969</v>
       </c>
       <c r="C67" t="s">
-        <v>1569</v>
+        <v>1565</v>
       </c>
       <c r="D67" t="s">
-        <v>1570</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>1557</v>
+        <v>1553</v>
       </c>
       <c r="B68" t="s">
         <v>905</v>
@@ -9688,13 +9677,13 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>1558</v>
+        <v>1554</v>
       </c>
       <c r="B69" t="s">
         <v>908</v>
       </c>
       <c r="C69" t="s">
-        <v>1571</v>
+        <v>1567</v>
       </c>
       <c r="D69" t="s">
         <v>1018</v>
@@ -9702,13 +9691,13 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>1559</v>
+        <v>1555</v>
       </c>
       <c r="B70" t="s">
         <v>908</v>
       </c>
       <c r="C70" t="s">
-        <v>1572</v>
+        <v>1568</v>
       </c>
       <c r="D70" t="s">
         <v>1018</v>
@@ -9716,133 +9705,133 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>1561</v>
+        <v>1557</v>
       </c>
       <c r="B71" t="s">
         <v>908</v>
       </c>
       <c r="C71" t="s">
-        <v>1573</v>
+        <v>1569</v>
       </c>
       <c r="D71" t="s">
-        <v>1574</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>1562</v>
+        <v>1558</v>
       </c>
       <c r="B72" t="s">
         <v>908</v>
       </c>
       <c r="C72" t="s">
-        <v>1573</v>
+        <v>1569</v>
       </c>
       <c r="D72" t="s">
-        <v>1574</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>1563</v>
+        <v>1559</v>
       </c>
       <c r="B73" t="s">
         <v>908</v>
       </c>
       <c r="C73" t="s">
-        <v>1573</v>
+        <v>1569</v>
       </c>
       <c r="D73" t="s">
-        <v>1574</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>1575</v>
+        <v>1571</v>
       </c>
       <c r="B74" t="s">
         <v>913</v>
       </c>
       <c r="C74" t="s">
-        <v>1576</v>
+        <v>1572</v>
       </c>
       <c r="D74" t="s">
-        <v>1577</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>1578</v>
+        <v>1574</v>
       </c>
       <c r="B75" t="s">
         <v>913</v>
       </c>
       <c r="C75" t="s">
-        <v>1576</v>
+        <v>1572</v>
       </c>
       <c r="D75" t="s">
-        <v>1577</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>1579</v>
+        <v>1575</v>
       </c>
       <c r="B76" t="s">
         <v>913</v>
       </c>
       <c r="C76" t="s">
-        <v>1576</v>
+        <v>1572</v>
       </c>
       <c r="D76" t="s">
-        <v>1577</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>1580</v>
+        <v>1576</v>
       </c>
       <c r="B77" t="s">
         <v>913</v>
       </c>
       <c r="C77" t="s">
-        <v>1581</v>
+        <v>1577</v>
       </c>
       <c r="D77" t="s">
-        <v>1582</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>1583</v>
+        <v>1579</v>
       </c>
       <c r="B78" t="s">
         <v>913</v>
       </c>
       <c r="C78" t="s">
-        <v>1584</v>
+        <v>1580</v>
       </c>
       <c r="D78" t="s">
-        <v>1585</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>1586</v>
+        <v>1582</v>
       </c>
       <c r="B79" t="s">
         <v>972</v>
       </c>
       <c r="C79" t="s">
-        <v>1576</v>
+        <v>1572</v>
       </c>
       <c r="D79" t="s">
-        <v>1587</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>1588</v>
+        <v>1584</v>
       </c>
       <c r="B80" t="s">
         <v>972</v>
@@ -9851,17 +9840,17 @@
         <v>972</v>
       </c>
       <c r="D80" t="s">
-        <v>1589</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>1590</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>1591</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.3">
@@ -9872,88 +9861,88 @@
         <v>992</v>
       </c>
       <c r="C85" t="s">
-        <v>1592</v>
+        <v>1588</v>
       </c>
       <c r="D85" t="s">
-        <v>1593</v>
+        <v>1589</v>
       </c>
       <c r="E85" t="s">
-        <v>1594</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>1595</v>
+        <v>1591</v>
       </c>
       <c r="B86" t="s">
         <v>997</v>
       </c>
       <c r="C86" t="s">
-        <v>1596</v>
+        <v>1592</v>
       </c>
       <c r="D86" t="s">
         <v>910</v>
       </c>
       <c r="E86" t="s">
-        <v>1597</v>
+        <v>1593</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>1598</v>
+        <v>1594</v>
       </c>
       <c r="B87" t="s">
-        <v>1599</v>
+        <v>1595</v>
       </c>
       <c r="C87" t="s">
-        <v>1600</v>
+        <v>1596</v>
       </c>
       <c r="D87" t="s">
         <v>1003</v>
       </c>
       <c r="E87" t="s">
-        <v>1601</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>1602</v>
+        <v>1598</v>
       </c>
       <c r="B88" t="s">
-        <v>1603</v>
+        <v>1599</v>
       </c>
       <c r="C88" t="s">
-        <v>1604</v>
+        <v>1600</v>
       </c>
       <c r="D88" t="s">
         <v>984</v>
       </c>
       <c r="E88" t="s">
-        <v>1605</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>1606</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>1607</v>
+        <v>1603</v>
       </c>
       <c r="B91" t="s">
         <v>969</v>
       </c>
       <c r="C91" t="s">
-        <v>1569</v>
+        <v>1565</v>
       </c>
       <c r="D91" t="s">
-        <v>1570</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>1557</v>
+        <v>1553</v>
       </c>
       <c r="B92" t="s">
         <v>1012</v>
@@ -9967,7 +9956,7 @@
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>1558</v>
+        <v>1554</v>
       </c>
       <c r="B93" t="s">
         <v>972</v>
@@ -9981,7 +9970,7 @@
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>1559</v>
+        <v>1555</v>
       </c>
       <c r="B94" t="s">
         <v>908</v>
@@ -9995,7 +9984,7 @@
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>1561</v>
+        <v>1557</v>
       </c>
       <c r="B95" t="s">
         <v>1017</v>
@@ -10009,7 +9998,7 @@
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>1562</v>
+        <v>1558</v>
       </c>
       <c r="B96" t="s">
         <v>1019</v>
@@ -10023,7 +10012,7 @@
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>1563</v>
+        <v>1559</v>
       </c>
       <c r="B97" t="s">
         <v>908</v>
@@ -10037,7 +10026,7 @@
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>1583</v>
+        <v>1579</v>
       </c>
       <c r="B98" t="s">
         <v>984</v>
@@ -10051,7 +10040,7 @@
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>1586</v>
+        <v>1582</v>
       </c>
       <c r="B99" t="s">
         <v>972</v>
@@ -10065,21 +10054,21 @@
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>1608</v>
+        <v>1604</v>
       </c>
       <c r="B101" t="s">
         <v>969</v>
       </c>
       <c r="C101" t="s">
-        <v>1569</v>
+        <v>1565</v>
       </c>
       <c r="D101" t="s">
-        <v>1570</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>1557</v>
+        <v>1553</v>
       </c>
       <c r="B102" t="s">
         <v>1013</v>
@@ -10093,7 +10082,7 @@
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>1558</v>
+        <v>1554</v>
       </c>
       <c r="B103" t="s">
         <v>972</v>
@@ -10102,26 +10091,26 @@
         <v>1026</v>
       </c>
       <c r="D103" t="s">
-        <v>1609</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>1559</v>
+        <v>1555</v>
       </c>
       <c r="B104" t="s">
         <v>1015</v>
       </c>
       <c r="C104" t="s">
-        <v>1610</v>
+        <v>1606</v>
       </c>
       <c r="D104" t="s">
-        <v>1610</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>1561</v>
+        <v>1557</v>
       </c>
       <c r="B105" t="s">
         <v>1018</v>
@@ -10130,12 +10119,12 @@
         <v>1028</v>
       </c>
       <c r="D105" t="s">
-        <v>1611</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>1562</v>
+        <v>1558</v>
       </c>
       <c r="B106" t="s">
         <v>1018</v>
@@ -10144,12 +10133,12 @@
         <v>1028</v>
       </c>
       <c r="D106" t="s">
-        <v>1611</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>1563</v>
+        <v>1559</v>
       </c>
       <c r="B107" t="s">
         <v>1020</v>
@@ -10158,12 +10147,12 @@
         <v>1030</v>
       </c>
       <c r="D107" t="s">
-        <v>1612</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>1580</v>
+        <v>1576</v>
       </c>
       <c r="B108" t="s">
         <v>1022</v>
@@ -10177,7 +10166,7 @@
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>1583</v>
+        <v>1579</v>
       </c>
       <c r="B109" t="s">
         <v>1023</v>
@@ -10186,26 +10175,26 @@
         <v>1033</v>
       </c>
       <c r="D109" t="s">
-        <v>1613</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>1586</v>
+        <v>1582</v>
       </c>
       <c r="B110" t="s">
         <v>1024</v>
       </c>
       <c r="C110" t="s">
-        <v>1614</v>
+        <v>1610</v>
       </c>
       <c r="D110" t="s">
-        <v>1560</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>1588</v>
+        <v>1584</v>
       </c>
       <c r="B111" t="s">
         <v>972</v>
@@ -10219,21 +10208,21 @@
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>1615</v>
+        <v>1611</v>
       </c>
       <c r="B113" t="s">
         <v>969</v>
       </c>
       <c r="C113" t="s">
-        <v>1569</v>
+        <v>1565</v>
       </c>
       <c r="D113" t="s">
-        <v>1570</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>1557</v>
+        <v>1553</v>
       </c>
       <c r="B114" t="s">
         <v>1014</v>
@@ -10247,133 +10236,133 @@
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>1558</v>
+        <v>1554</v>
       </c>
       <c r="B115" t="s">
         <v>972</v>
       </c>
       <c r="C115" t="s">
-        <v>1616</v>
+        <v>1612</v>
       </c>
       <c r="D115" t="s">
-        <v>1617</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>1559</v>
+        <v>1555</v>
       </c>
       <c r="B116" t="s">
         <v>1016</v>
       </c>
       <c r="C116" t="s">
-        <v>1618</v>
+        <v>1614</v>
       </c>
       <c r="D116" t="s">
-        <v>1619</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>1561</v>
+        <v>1557</v>
       </c>
       <c r="B117" t="s">
         <v>1016</v>
       </c>
       <c r="C117" t="s">
-        <v>1620</v>
+        <v>1616</v>
       </c>
       <c r="D117" t="s">
-        <v>1621</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>1562</v>
+        <v>1558</v>
       </c>
       <c r="B118" t="s">
         <v>1016</v>
       </c>
       <c r="C118" t="s">
-        <v>1620</v>
+        <v>1616</v>
       </c>
       <c r="D118" t="s">
-        <v>1621</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>1563</v>
+        <v>1559</v>
       </c>
       <c r="B119" t="s">
         <v>1021</v>
       </c>
       <c r="C119" t="s">
-        <v>1622</v>
+        <v>1618</v>
       </c>
       <c r="D119" t="s">
-        <v>1623</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>1580</v>
+        <v>1576</v>
       </c>
       <c r="B120" t="s">
         <v>1021</v>
       </c>
       <c r="C120" t="s">
-        <v>1622</v>
+        <v>1618</v>
       </c>
       <c r="D120" t="s">
-        <v>1623</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>1583</v>
+        <v>1579</v>
       </c>
       <c r="B121" t="s">
-        <v>1624</v>
+        <v>1620</v>
       </c>
       <c r="C121" t="s">
-        <v>1625</v>
+        <v>1621</v>
       </c>
       <c r="D121" t="s">
-        <v>1573</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>1586</v>
+        <v>1582</v>
       </c>
       <c r="B122" t="s">
-        <v>1626</v>
+        <v>1622</v>
       </c>
       <c r="C122" t="s">
-        <v>1622</v>
+        <v>1618</v>
       </c>
       <c r="D122" t="s">
-        <v>1627</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>1564</v>
+        <v>1560</v>
       </c>
       <c r="B123" t="s">
-        <v>1628</v>
+        <v>1624</v>
       </c>
       <c r="C123" t="s">
-        <v>1622</v>
+        <v>1618</v>
       </c>
       <c r="D123" t="s">
-        <v>1623</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>1588</v>
+        <v>1584</v>
       </c>
       <c r="B124" t="s">
         <v>972</v>
@@ -10387,20 +10376,20 @@
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>1629</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>1630</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="129" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>1444</v>
+        <v>1440</v>
       </c>
       <c r="B129" t="s">
-        <v>1631</v>
+        <v>1627</v>
       </c>
       <c r="C129" t="s">
         <v>806</v>
@@ -10411,100 +10400,100 @@
     </row>
     <row r="130" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>1447</v>
+        <v>1443</v>
       </c>
       <c r="B130" t="s">
-        <v>1632</v>
+        <v>1628</v>
       </c>
       <c r="C130" t="s">
-        <v>1633</v>
+        <v>1629</v>
       </c>
       <c r="D130" t="s">
-        <v>1634</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="131" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>1450</v>
+        <v>1446</v>
       </c>
       <c r="B131" t="s">
-        <v>1635</v>
+        <v>1631</v>
       </c>
       <c r="C131" t="s">
-        <v>1636</v>
+        <v>1632</v>
       </c>
       <c r="D131" t="s">
-        <v>1637</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="132" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>1452</v>
+        <v>1448</v>
       </c>
       <c r="B132" t="s">
-        <v>1638</v>
+        <v>1634</v>
       </c>
       <c r="C132" t="s">
-        <v>1639</v>
+        <v>1635</v>
       </c>
       <c r="D132" t="s">
-        <v>1640</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="134" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>1641</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="136" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>1642</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="137" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>1643</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="138" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B138" t="s">
+        <v>1641</v>
+      </c>
+      <c r="C138" t="s">
+        <v>1642</v>
+      </c>
+      <c r="D138" t="s">
+        <v>1643</v>
+      </c>
+      <c r="E138" t="s">
         <v>1644</v>
       </c>
-      <c r="B138" t="s">
+      <c r="F138" t="s">
         <v>1645</v>
       </c>
-      <c r="C138" t="s">
+      <c r="G138" t="s">
         <v>1646</v>
       </c>
-      <c r="D138" t="s">
+      <c r="H138" t="s">
         <v>1647</v>
       </c>
-      <c r="E138" t="s">
+      <c r="I138" t="s">
         <v>1648</v>
       </c>
-      <c r="F138" t="s">
+      <c r="J138" t="s">
         <v>1649</v>
       </c>
-      <c r="G138" t="s">
+      <c r="K138" t="s">
         <v>1650</v>
       </c>
-      <c r="H138" t="s">
+      <c r="L138" t="s">
         <v>1651</v>
       </c>
-      <c r="I138" t="s">
+      <c r="M138" t="s">
         <v>1652</v>
-      </c>
-      <c r="J138" t="s">
-        <v>1653</v>
-      </c>
-      <c r="K138" t="s">
-        <v>1654</v>
-      </c>
-      <c r="L138" t="s">
-        <v>1655</v>
-      </c>
-      <c r="M138" t="s">
-        <v>1656</v>
       </c>
     </row>
     <row r="139" spans="1:13" x14ac:dyDescent="0.3">
@@ -12969,80 +12958,80 @@
     </row>
     <row r="200" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>1657</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="202" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>1457</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="203" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>1444</v>
+        <v>1440</v>
       </c>
       <c r="B203" t="s">
-        <v>1458</v>
+        <v>1454</v>
       </c>
       <c r="C203" t="s">
-        <v>1459</v>
+        <v>1455</v>
       </c>
       <c r="D203" t="s">
-        <v>1460</v>
+        <v>1456</v>
       </c>
       <c r="E203" t="s">
-        <v>1461</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="204" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>1447</v>
+        <v>1443</v>
       </c>
       <c r="B204" t="s">
-        <v>1462</v>
+        <v>1458</v>
       </c>
       <c r="C204" t="s">
-        <v>1463</v>
+        <v>1459</v>
       </c>
       <c r="D204" t="s">
-        <v>1464</v>
+        <v>1460</v>
       </c>
       <c r="E204" t="s">
-        <v>1465</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="205" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>1450</v>
+        <v>1446</v>
       </c>
       <c r="B205" t="s">
-        <v>1466</v>
+        <v>1462</v>
       </c>
       <c r="C205" t="s">
-        <v>1465</v>
+        <v>1461</v>
       </c>
       <c r="D205" t="s">
-        <v>1467</v>
+        <v>1463</v>
       </c>
       <c r="E205" t="s">
-        <v>1468</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="206" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>1452</v>
+        <v>1448</v>
       </c>
       <c r="B206" t="s">
-        <v>1469</v>
+        <v>1465</v>
       </c>
       <c r="C206" t="s">
-        <v>1464</v>
+        <v>1460</v>
       </c>
       <c r="D206" t="s">
-        <v>1470</v>
+        <v>1466</v>
       </c>
       <c r="E206" t="s">
-        <v>1471</v>
+        <v>1467</v>
       </c>
     </row>
   </sheetData>
@@ -14836,12 +14825,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="B29:B31"/>
-    <mergeCell ref="B14:B16"/>
-    <mergeCell ref="A8:A10"/>
-    <mergeCell ref="A26:A28"/>
-    <mergeCell ref="A17:A19"/>
-    <mergeCell ref="A20:A22"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A5:A7"/>
     <mergeCell ref="A23:A25"/>
@@ -14858,6 +14841,12 @@
     <mergeCell ref="B17:B19"/>
     <mergeCell ref="B23:B25"/>
     <mergeCell ref="A29:A31"/>
+    <mergeCell ref="B29:B31"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="A8:A10"/>
+    <mergeCell ref="A26:A28"/>
+    <mergeCell ref="A17:A19"/>
+    <mergeCell ref="A20:A22"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <ignoredErrors>
@@ -15752,10 +15741,10 @@
         <v>493</v>
       </c>
       <c r="F41" t="s">
-        <v>1658</v>
+        <v>1654</v>
       </c>
       <c r="G41" t="s">
-        <v>1659</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">

--- a/SYMBEAST_Evolve_Forms.xlsx
+++ b/SYMBEAST_Evolve_Forms.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\skyit\Desktop\Symbeast-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EF239C5-A0BE-42C2-83F7-E4C449AD9C46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EE5C70A-802E-4FF3-93D9-8F61F65F94A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5000,7 +5000,7 @@
     <t>โจมตี ×2.0 ทะลุ DEF ทั้งหมด + สะท้อนดาเมจทั้งหมดเทิร์นนี้ จากนั้นสะท้อน 50% และลดดาเมจที่รับ 15% นาน 3 เทิร์น</t>
   </si>
   <si>
-    <t>เมื่อ HP &gt; 50%: ATK+25% เมื่อ HP &lt; 50%: DEF+25% โต้กลับด้วยดาเมจ 75% ทุกรอบ และเมื่อโดนโจมตีมีโอกาส 10% ทำให้ศัตรูสต้น</t>
+    <t>เมื่อ HP &gt; 50%: ATK+25% เมื่อ HP &lt; 50%: DEF+25% โต้กลับด้วยดาเมจ 75% ทุกรอบ และมีโอกาส 10% ทำให้ศัตรูสต้นเมื่อโดนโจมตี</t>
   </si>
 </sst>
 </file>
@@ -14829,12 +14829,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="B29:B31"/>
-    <mergeCell ref="B14:B16"/>
-    <mergeCell ref="A8:A10"/>
-    <mergeCell ref="A26:A28"/>
-    <mergeCell ref="A17:A19"/>
-    <mergeCell ref="A20:A22"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A5:A7"/>
     <mergeCell ref="A23:A25"/>
@@ -14851,6 +14845,12 @@
     <mergeCell ref="B17:B19"/>
     <mergeCell ref="B23:B25"/>
     <mergeCell ref="A29:A31"/>
+    <mergeCell ref="B29:B31"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="A8:A10"/>
+    <mergeCell ref="A26:A28"/>
+    <mergeCell ref="A17:A19"/>
+    <mergeCell ref="A20:A22"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <ignoredErrors>

--- a/SYMBEAST_Evolve_Forms.xlsx
+++ b/SYMBEAST_Evolve_Forms.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\skyit\Desktop\Symbeast-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73699FB6-166A-4DFB-B66A-C717A868DC6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2068D9C-48DA-419B-8811-7E187A3DE873}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="10" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Evolved Forms" sheetId="1" r:id="rId1"/>
@@ -27,13 +27,15 @@
     <sheet name="Raid Rewards" sheetId="12" r:id="rId12"/>
     <sheet name="Tower Rewards" sheetId="13" r:id="rId13"/>
     <sheet name="Scout Rewards" sheetId="14" r:id="rId14"/>
+    <sheet name="Fusion Passives" sheetId="15" r:id="rId15"/>
+    <sheet name="Fusion Passives v2" sheetId="16" r:id="rId16"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2601" uniqueCount="1656">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3203" uniqueCount="1991">
   <si>
     <t>SYMBEAST — Evolved Forms (Stage 1, 10 forms)</t>
   </si>
@@ -5001,6 +5003,1011 @@
   </si>
   <si>
     <t>15% โอกาสทำให้ศัตรูติดเผาไหม้เมื่อโจมตีโดน</t>
+  </si>
+  <si>
+    <t>SYMBEAST — Fusion Passives (proposal, ยังไม่ implement) — Fuse 2 Evolved-stage pets -&gt; Fusion Egg -&gt; hatch normally -&gt; pet carries 1 inherited passive slot</t>
+  </si>
+  <si>
+    <t>Category | Parent 1 | Parent 2 | Icon | Name | Effect (EN) | Effect (TH)</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Parent 1</t>
+  </si>
+  <si>
+    <t>Parent 2</t>
+  </si>
+  <si>
+    <t>Pure-blood</t>
+  </si>
+  <si>
+    <t>💢</t>
+  </si>
+  <si>
+    <t>RAGE BLOOD</t>
+  </si>
+  <si>
+    <t>On each WIN, ATK +10% (stacks up to 3 times)</t>
+  </si>
+  <si>
+    <t>ทุกครั้งที่ WIN, ATK+10% สะสม (สูงสุด 3 ครั้ง)</t>
+  </si>
+  <si>
+    <t>🐼</t>
+  </si>
+  <si>
+    <t>TWIN FANG</t>
+  </si>
+  <si>
+    <t>On crit, 10% chance to strike again immediately for 50% damage</t>
+  </si>
+  <si>
+    <t>คริติคอลแล้ว 10% โอกาสโจมตีซ้ำทันที (ดาเมจ 50%)</t>
+  </si>
+  <si>
+    <t>🩸</t>
+  </si>
+  <si>
+    <t>CRIMSON CORE</t>
+  </si>
+  <si>
+    <t>Lifesteal is doubled while HP &lt; 50%</t>
+  </si>
+  <si>
+    <t>ดูดเลือดที่ได้ ×2 เมื่อ HP&lt;50%</t>
+  </si>
+  <si>
+    <t>CHAIN LIGHTNING</t>
+  </si>
+  <si>
+    <t>When you stun the enemy, 20% chance to stun them again next round</t>
+  </si>
+  <si>
+    <t>สตันติดแล้ว มีโอกาส 20% สตันต่ออีกเทิร์น</t>
+  </si>
+  <si>
+    <t>🏆</t>
+  </si>
+  <si>
+    <t>GRAND CHAMPION</t>
+  </si>
+  <si>
+    <t>Win 2 rounds in a row: permanent ATK+30% for the rest of the battle (once)</t>
+  </si>
+  <si>
+    <t>ชนะ 2 รอบติด ATK+30% ถาวรตลอดการต่อสู้ (ครั้งเดียว)</t>
+  </si>
+  <si>
+    <t>🗿</t>
+  </si>
+  <si>
+    <t>STONE BLOOD</t>
+  </si>
+  <si>
+    <t>Every 3 turns, 20% chance to fully block all damage (100%)</t>
+  </si>
+  <si>
+    <t>ทุก 3 เทิร์น 20% โอกาสบล็อกดาเมจเต็ม 100%</t>
+  </si>
+  <si>
+    <t>👻</t>
+  </si>
+  <si>
+    <t>GHOST BLOOD</t>
+  </si>
+  <si>
+    <t>After a successful dodge, the next attack is a guaranteed crit</t>
+  </si>
+  <si>
+    <t>หลบสำเร็จแล้ว โจมตีถัดไปคริติคอลการันตี</t>
+  </si>
+  <si>
+    <t>🌪️</t>
+  </si>
+  <si>
+    <t>ETERNAL GUARD</t>
+  </si>
+  <si>
+    <t>On a successful dodge, heal an extra 10% Max HP (total 25%)</t>
+  </si>
+  <si>
+    <t>หลบสำเร็จ ฟื้น HP เพิ่มอีก 10% (รวม 25%)</t>
+  </si>
+  <si>
+    <t>🦅</t>
+  </si>
+  <si>
+    <t>SKYFORT</t>
+  </si>
+  <si>
+    <t>Both on WIN and LOSE, reduce damage taken by an extra 10%</t>
+  </si>
+  <si>
+    <t>WIN และ LOSE ลดดาเมจเพิ่มอีก 10% ทั้ง 2 กรณี</t>
+  </si>
+  <si>
+    <t>ABSOLUTE WALL</t>
+  </si>
+  <si>
+    <t>When the damage-halving effect triggers, reduce the remaining damage by another 10%</t>
+  </si>
+  <si>
+    <t>ลดดาเมจสำเร็จ (halve) ดาเมจที่เหลือ -10% เพิ่ม</t>
+  </si>
+  <si>
+    <t>Cross-blood</t>
+  </si>
+  <si>
+    <t>🔥</t>
+  </si>
+  <si>
+    <t>BERSERK FOCUS</t>
+  </si>
+  <si>
+    <t>On crit, ATK+15% stacking for the rest of the battle</t>
+  </si>
+  <si>
+    <t>คริติคอลแล้ว ATK+15% สะสมตลอดการต่อสู้</t>
+  </si>
+  <si>
+    <t>💪</t>
+  </si>
+  <si>
+    <t>BLOODRAGE</t>
+  </si>
+  <si>
+    <t>Lifesteal gained is converted into permanent ATK +5% per proc (stacks)</t>
+  </si>
+  <si>
+    <t>ดูดเลือดที่ได้ เปลี่ยนเป็น ATK ถาวร +5%/ครั้ง (สะสมได้)</t>
+  </si>
+  <si>
+    <t>THUNDER FIST</t>
+  </si>
+  <si>
+    <t>On WIN, 20% chance to stun the enemy</t>
+  </si>
+  <si>
+    <t>WIN แล้ว 20% โอกาสสตันศัตรู</t>
+  </si>
+  <si>
+    <t>🥊</t>
+  </si>
+  <si>
+    <t>RISING FIST</t>
+  </si>
+  <si>
+    <t>Win 3 rounds in a row: permanent ATK+50% (once per battle)</t>
+  </si>
+  <si>
+    <t>ชนะ 3 รอบติด ATK+50% ถาวร (ครั้งเดียว/battle)</t>
+  </si>
+  <si>
+    <t>UNSTOPPABLE WALL</t>
+  </si>
+  <si>
+    <t>15% chance to counter-attack for 50% damage when hit</t>
+  </si>
+  <si>
+    <t>15% โอกาสโต้กลับดาเมจ 50% เมื่อถูกโจมตี</t>
+  </si>
+  <si>
+    <t>👊</t>
+  </si>
+  <si>
+    <t>PHANTOM FIST</t>
+  </si>
+  <si>
+    <t>15% chance to dodge and counter-attack for 75% damage</t>
+  </si>
+  <si>
+    <t>15% โอกาสหลบ พร้อมโจมตีสวนกลับดาเมจ 75%</t>
+  </si>
+  <si>
+    <t>🦶</t>
+  </si>
+  <si>
+    <t>SWIFT FIST</t>
+  </si>
+  <si>
+    <t>10% chance to dodge, with ATK+15% next round</t>
+  </si>
+  <si>
+    <t>10% โอกาสหลบ พร้อม ATK+15% เทิร์นถัดไป</t>
+  </si>
+  <si>
+    <t>AERIAL BRUISER</t>
+  </si>
+  <si>
+    <t>On WIN, ATK+20% and damage taken -15% that round</t>
+  </si>
+  <si>
+    <t>WIN: ATK+20% และรับดาเมจ-15% รอบนั้น</t>
+  </si>
+  <si>
+    <t>🗻</t>
+  </si>
+  <si>
+    <t>JUGGERNAUT</t>
+  </si>
+  <si>
+    <t>Every 3 turns, deal +50% damage on that attack once</t>
+  </si>
+  <si>
+    <t>ทุก 3 เทิร์น โจมตีดาเมจ+50% ครั้งเดียว</t>
+  </si>
+  <si>
+    <t>CRIMSON STRIKE</t>
+  </si>
+  <si>
+    <t>On crit, lifesteal 30% of the damage dealt</t>
+  </si>
+  <si>
+    <t>คริติคอลแล้ว ดูดเลือด 30% ของดาเมจที่สร้าง</t>
+  </si>
+  <si>
+    <t>FLASH CRIT</t>
+  </si>
+  <si>
+    <t>On crit, 25% chance to instantly stun the enemy</t>
+  </si>
+  <si>
+    <t>คริติคอลแล้ว 25% โอกาสสตันศัตรูทันที</t>
+  </si>
+  <si>
+    <t>🎯</t>
+  </si>
+  <si>
+    <t>CHAMPION'S EYE</t>
+  </si>
+  <si>
+    <t>On WIN, crit chance +15% next round</t>
+  </si>
+  <si>
+    <t>WIN: โอกาสคริติคอล+15% รอบถัดไป</t>
+  </si>
+  <si>
+    <t>🪨</t>
+  </si>
+  <si>
+    <t>IRON CRIT</t>
+  </si>
+  <si>
+    <t>On crit, damage taken -20% next round</t>
+  </si>
+  <si>
+    <t>คริติคอลแล้ว รับดาเมจ-20% เทิร์นถัดไป</t>
+  </si>
+  <si>
+    <t>🥷</t>
+  </si>
+  <si>
+    <t>SHADOW CRIT</t>
+  </si>
+  <si>
+    <t>On a successful dodge, crit chance +30% next attack</t>
+  </si>
+  <si>
+    <t>หลบสำเร็จ โจมตีถัดไปคริ+30%</t>
+  </si>
+  <si>
+    <t>🌀</t>
+  </si>
+  <si>
+    <t>CRITICAL GUARD</t>
+  </si>
+  <si>
+    <t>On a successful dodge, heal 10% HP with crit chance +10%</t>
+  </si>
+  <si>
+    <t>หลบสำเร็จ ฟื้น HP 10% พร้อมคริ+10%</t>
+  </si>
+  <si>
+    <t>SKY CRIT</t>
+  </si>
+  <si>
+    <t>On WIN, guaranteed crit x2.0 that round</t>
+  </si>
+  <si>
+    <t>WIN: คริติคอล ×2.0 การันตีเทิร์นนั้น</t>
+  </si>
+  <si>
+    <t>GUARDIAN CRIT</t>
+  </si>
+  <si>
+    <t>When the damage-halving effect triggers, next attack is a guaranteed crit</t>
+  </si>
+  <si>
+    <t>ลดดาเมจสำเร็จ โจมตีถัดไปคริการันตี</t>
+  </si>
+  <si>
+    <t>🦷</t>
+  </si>
+  <si>
+    <t>VENOM FANG</t>
+  </si>
+  <si>
+    <t>On a successful lifesteal, 15% chance to stun the enemy</t>
+  </si>
+  <si>
+    <t>ดูดเลือดสำเร็จ 15% โอกาสสตันศัตรู</t>
+  </si>
+  <si>
+    <t>VICTOR'S BITE</t>
+  </si>
+  <si>
+    <t>On WIN, lifesteal increases to 40% of damage dealt</t>
+  </si>
+  <si>
+    <t>WIN: ดูดเลือดเพิ่มเป็น 40% ของดาเมจ</t>
+  </si>
+  <si>
+    <t>🔄</t>
+  </si>
+  <si>
+    <t>VAMPIRIC WALL</t>
+  </si>
+  <si>
+    <t>Reflected damage converts half of itself into HP healed</t>
+  </si>
+  <si>
+    <t>สะท้อนดาเมจ เปลี่ยนครึ่งหนึ่งเป็นฟื้น HP</t>
+  </si>
+  <si>
+    <t>🐺</t>
+  </si>
+  <si>
+    <t>PHANTOM FANGS</t>
+  </si>
+  <si>
+    <t>15% chance to lifesteal 50% of damage dealt and dodge that same turn</t>
+  </si>
+  <si>
+    <t>15% โอกาสดูดเลือด 50% พร้อมหลบเทิร์นนั้น</t>
+  </si>
+  <si>
+    <t>DRAIN STEP</t>
+  </si>
+  <si>
+    <t>On a successful dodge, instantly lifesteal 15% Max HP</t>
+  </si>
+  <si>
+    <t>หลบสำเร็จ ดูดเลือด 15% MaxHP ทันที</t>
+  </si>
+  <si>
+    <t>BLOOD WING</t>
+  </si>
+  <si>
+    <t>On WIN, lifesteal an extra +15% on top of the base amount</t>
+  </si>
+  <si>
+    <t>WIN: ดูดเลือดเพิ่ม+15% จากที่มีอยู่</t>
+  </si>
+  <si>
+    <t>STONE FANG</t>
+  </si>
+  <si>
+    <t>When the damage-halving effect triggers, lifesteal 20% of the damage reduced</t>
+  </si>
+  <si>
+    <t>ลดดาเมจสำเร็จ ดูดเลือด 20% ของดาเมจที่ลดได้</t>
+  </si>
+  <si>
+    <t>VICTORY SHOCK</t>
+  </si>
+  <si>
+    <t>On WIN, 25% chance to instantly stun the enemy</t>
+  </si>
+  <si>
+    <t>WIN: 25% โอกาสสตันศัตรูทันที</t>
+  </si>
+  <si>
+    <t>STATIC WALL</t>
+  </si>
+  <si>
+    <t>When you reflect damage, 15% chance to also stun the enemy</t>
+  </si>
+  <si>
+    <t>สะท้อนดาเมจ 15% โอกาสสตันติดไปด้วย</t>
+  </si>
+  <si>
+    <t>GHOST BOLT</t>
+  </si>
+  <si>
+    <t>After a successful stun, automatically dodge the enemy's next attack</t>
+  </si>
+  <si>
+    <t>สตันสำเร็จ หลบการโจมตีเทิร์นถัดไปอัตโนมัติ</t>
+  </si>
+  <si>
+    <t>QUICK SHOCK</t>
+  </si>
+  <si>
+    <t>On a successful dodge, 20% chance to stun the enemy back</t>
+  </si>
+  <si>
+    <t>หลบสำเร็จ 20% โอกาสสตันศัตรูสวน</t>
+  </si>
+  <si>
+    <t>STORM WING</t>
+  </si>
+  <si>
+    <t>On WIN, SPD+30% next round</t>
+  </si>
+  <si>
+    <t>WIN: SPD+30% เทิร์นถัดไป</t>
+  </si>
+  <si>
+    <t>THUNDER WALL</t>
+  </si>
+  <si>
+    <t>When the damage-halving effect triggers, 20% chance to stun the enemy</t>
+  </si>
+  <si>
+    <t>ลดดาเมจสำเร็จ 20% โอกาสสตันศัตรู</t>
+  </si>
+  <si>
+    <t>UNBREAKABLE</t>
+  </si>
+  <si>
+    <t>On WIN, reflect an extra 30% damage that round</t>
+  </si>
+  <si>
+    <t>WIN: สะท้อนดาเมจเพิ่ม 30% รอบนั้น</t>
+  </si>
+  <si>
+    <t>👑</t>
+  </si>
+  <si>
+    <t>PHANTOM VICTOR</t>
+  </si>
+  <si>
+    <t>On WIN, fully dodge the enemy's next attack (100%)</t>
+  </si>
+  <si>
+    <t>WIN: หลบการโจมตีรอบถัดไป 100%</t>
+  </si>
+  <si>
+    <t>🏅</t>
+  </si>
+  <si>
+    <t>SWIFT VICTORY</t>
+  </si>
+  <si>
+    <t>On WIN, instantly heal 15% HP</t>
+  </si>
+  <si>
+    <t>WIN: ฟื้น HP 15% ทันที</t>
+  </si>
+  <si>
+    <t>VICTOR'S AEGIS</t>
+  </si>
+  <si>
+    <t>On WIN, damage taken -30% for the next 2 rounds (including the win round)</t>
+  </si>
+  <si>
+    <t>WIN: รับดาเมจ-30% ต่อเนื่อง 2 รอบ</t>
+  </si>
+  <si>
+    <t>IRON CROWN</t>
+  </si>
+  <si>
+    <t>On WIN, also halve damage taken next round</t>
+  </si>
+  <si>
+    <t>WIN: ลดดาเมจครึ่งหนึ่งรอบถัดไปด้วย</t>
+  </si>
+  <si>
+    <t>SPECTRAL WALL</t>
+  </si>
+  <si>
+    <t>When you reflect damage, 20% chance to also dodge next round</t>
+  </si>
+  <si>
+    <t>สะท้อนดาเมจ 20% โอกาสหลบเทิร์นถัดไป</t>
+  </si>
+  <si>
+    <t>REFLECT STEP</t>
+  </si>
+  <si>
+    <t>When you reflect damage, heal 20% of the reflected amount</t>
+  </si>
+  <si>
+    <t>สะท้อนดาเมจ ฟื้น HP 20% ของดาเมจที่สะท้อนได้</t>
+  </si>
+  <si>
+    <t>IRON SKY</t>
+  </si>
+  <si>
+    <t>Both on WIN and LOSE, reduce damage taken by an extra 15%</t>
+  </si>
+  <si>
+    <t>WIN/LOSE ลดดาเมจเพิ่ม 15% ทั้ง 2 กรณี</t>
+  </si>
+  <si>
+    <t>ETERNAL WALL</t>
+  </si>
+  <si>
+    <t>The reflect and damage-halving effects can both trigger in the same turn</t>
+  </si>
+  <si>
+    <t>สะท้อนและลดดาเมจ (halve) เกิดพร้อมกันได้ในเทิร์นเดียว</t>
+  </si>
+  <si>
+    <t>DOUBLE EVASION</t>
+  </si>
+  <si>
+    <t>On a successful dodge, 20% chance to dodge again next round</t>
+  </si>
+  <si>
+    <t>หลบสำเร็จ 20% โอกาสหลบซ้ำเทิร์นถัดไป</t>
+  </si>
+  <si>
+    <t>GHOST WING</t>
+  </si>
+  <si>
+    <t>On a successful dodge, damage taken -30% for the next 2 turns</t>
+  </si>
+  <si>
+    <t>หลบสำเร็จ รับดาเมจ-30% อีก 2 เทิร์น</t>
+  </si>
+  <si>
+    <t>PHANTOM WALL</t>
+  </si>
+  <si>
+    <t>On a successful dodge, guarantee the damage-halving effect next round</t>
+  </si>
+  <si>
+    <t>หลบสำเร็จ เทิร์นถัดไปลดดาเมจครึ่งหนึ่งการันตี</t>
+  </si>
+  <si>
+    <t>SKY STEP</t>
+  </si>
+  <si>
+    <t>On a successful dodge, heal an extra 10% HP (total 25%)</t>
+  </si>
+  <si>
+    <t>⚖️</t>
+  </si>
+  <si>
+    <t>AEGIS STEP</t>
+  </si>
+  <si>
+    <t>10% chance to halve damage taken while also healing 10% HP that turn</t>
+  </si>
+  <si>
+    <t>10% โอกาสลดดาเมจครึ่งหนึ่ง พร้อมฟื้น HP 10%</t>
+  </si>
+  <si>
+    <t>FORTRESS WING</t>
+  </si>
+  <si>
+    <t>On WIN, guarantee the damage-halving effect</t>
+  </si>
+  <si>
+    <t>WIN: ลดดาเมจครึ่งหนึ่งการันตี</t>
+  </si>
+  <si>
+    <t>SYMBEAST — Fusion Passives v2 (proposal, ยังไม่ implement) — Approach B: 1 new half-strength Echo passive per Evolve II form (40 total, not per-pair)</t>
+  </si>
+  <si>
+    <t>Fusion = choose/random 1 of the 2 parents' own Evolve II form -&gt; egg inherits that form's Echo passive (numbers ~halved, freshly coded, no shared battle-state vars, so it never conflicts with any natural passive)</t>
+  </si>
+  <si>
+    <t>Evolve II Form | Icon | Echo Passive Name | Effect (EN) | Effect (TH)</t>
+  </si>
+  <si>
+    <t>Evolve II Form</t>
+  </si>
+  <si>
+    <t>Echo Passive Name</t>
+  </si>
+  <si>
+    <t>RAGING ECHO</t>
+  </si>
+  <si>
+    <t>On WIN: damage dealt +8% per stack (max 5 stacks per battle)</t>
+  </si>
+  <si>
+    <t>เมื่อ WIN ดาเมจเพิ่มขึ้นครั้งละ 8% (สะสมสูงสุด 5 ครั้ง)</t>
+  </si>
+  <si>
+    <t>🗡</t>
+  </si>
+  <si>
+    <t>WINDBLADE ECHO</t>
+  </si>
+  <si>
+    <t>☯️</t>
+  </si>
+  <si>
+    <t>CRIMSON ECHO</t>
+  </si>
+  <si>
+    <t>Every round: ATK+5% and SPD+5% (max 3 stacks per battle)</t>
+  </si>
+  <si>
+    <t>ทุกรอบ ATK+5% และ SPD+5% (สะสมสูงสุด 3 ครั้ง)</t>
+  </si>
+  <si>
+    <t>🦖</t>
+  </si>
+  <si>
+    <t>KAIJU ECHO</t>
+  </si>
+  <si>
+    <t>On LOSE: next round ATK+25%, DEF+25%, and 12% chance to burn the enemy</t>
+  </si>
+  <si>
+    <t>เมื่อ LOSE รอบถัดไป ATK+25%, DEF+25% และ 12% โอกาสทำให้ศัตรูติดเผาไหม้</t>
+  </si>
+  <si>
+    <t>FIGHTER ECHO</t>
+  </si>
+  <si>
+    <t>On LOSE: damage dealt +35% that turn</t>
+  </si>
+  <si>
+    <t>เมื่อ LOSE ดาเมจเพิ่มขึ้น 35% ในเทิร์นนั้น</t>
+  </si>
+  <si>
+    <t>NINJA ECHO</t>
+  </si>
+  <si>
+    <t>12% chance to fully dodge; on dodge, crit chance +50% next attack</t>
+  </si>
+  <si>
+    <t>12% โอกาสหลบการโจมตี เมื่อหลบสำเร็จ โอกาสคริ+50% ในการโจมตีถัดไป</t>
+  </si>
+  <si>
+    <t>WARRIOR ECHO</t>
+  </si>
+  <si>
+    <t>🛡</t>
+  </si>
+  <si>
+    <t>ARMOR ECHO</t>
+  </si>
+  <si>
+    <t>TYRANT ECHO</t>
+  </si>
+  <si>
+    <t>Damage dealt +10% and lifesteal +5%</t>
+  </si>
+  <si>
+    <t>ดาเมจที่สร้างเพิ่มขึ้น 10% และดูดเลือดเพิ่ม 5%</t>
+  </si>
+  <si>
+    <t>AGILE ECHO</t>
+  </si>
+  <si>
+    <t>12% chance to attack twice</t>
+  </si>
+  <si>
+    <t>12% โอกาสโจมตี 2 ครั้ง</t>
+  </si>
+  <si>
+    <t>🔮</t>
+  </si>
+  <si>
+    <t>RUNE ECHO</t>
+  </si>
+  <si>
+    <t>FULLARMOR ECHO</t>
+  </si>
+  <si>
+    <t>STRONG ECHO</t>
+  </si>
+  <si>
+    <t>On WIN: damage dealt +10% and 8% chance to stun the enemy for 1 round</t>
+  </si>
+  <si>
+    <t>เมื่อ WIN ดาเมจเพิ่มขึ้น 10% และ 8% โอกาส Stun ศัตรู 1 รอบ</t>
+  </si>
+  <si>
+    <t>🌩</t>
+  </si>
+  <si>
+    <t>STORM ECHO</t>
+  </si>
+  <si>
+    <t>THUNDERCLOUD ECHO</t>
+  </si>
+  <si>
+    <t>BULWARK ECHO</t>
+  </si>
+  <si>
+    <t>WARLORD ECHO</t>
+  </si>
+  <si>
+    <t>Damage dealt +10%; 5% chance to attack 4 times</t>
+  </si>
+  <si>
+    <t>ดาเมจที่สร้างเพิ่มขึ้น 10% และมีโอกาส 5% ที่จะโจมตี 4 ครั้ง</t>
+  </si>
+  <si>
+    <t>KING ECHO</t>
+  </si>
+  <si>
+    <t>10% chance to fully dodge; on dodge, ATK/DEF/SPD +5% (max 5 stacks per battle)</t>
+  </si>
+  <si>
+    <t>10% โอกาสหลบการโจมตี เมื่อหลบสำเร็จ ATK/DEF/SPD+5% (สะสมสูงสุด 5 ครั้ง)</t>
+  </si>
+  <si>
+    <t>SOUL ECHO</t>
+  </si>
+  <si>
+    <t>On WIN: ATK+12% and 12% chance to burn the enemy; on LOSE: dodge +12% and damage dealt +12% that round</t>
+  </si>
+  <si>
+    <t>เมื่อ WIN: ATK+12% และ 12% โอกาสทำให้ศัตรูติดเผาไหม้ เมื่อ LOSE: โอกาสหลบ+12% และดาเมจเพิ่ม 12% ในรอบนั้น</t>
+  </si>
+  <si>
+    <t>ROLLING ECHO</t>
+  </si>
+  <si>
+    <t>Damage taken -10%; every 3 rounds the attack deals +25% damage and cannot miss</t>
+  </si>
+  <si>
+    <t>ลดดาเมจที่รับ 10% และทุกๆ 3 รอบจะโจมตีแรงขึ้น 25% และไม่พลาดเป้า</t>
+  </si>
+  <si>
+    <t>BLAZING ECHO</t>
+  </si>
+  <si>
+    <t>On WIN: damage dealt +8% and DEF +8% per stack (max 3 stacks), 10% chance to poison the enemy</t>
+  </si>
+  <si>
+    <t>เมื่อ WIN ดาเมจ+8% และ DEF+8% สะสม (สูงสุด 3 ครั้ง) และ 10% โอกาสทำให้ศัตรูติดพิษ</t>
+  </si>
+  <si>
+    <t>SWIFT ECHO</t>
+  </si>
+  <si>
+    <t>Every 3 turns: reflects 35% of damage taken, recovers 5% HP, and 25% chance to poison the enemy</t>
+  </si>
+  <si>
+    <t>ทุก 3 เทิร์น สะท้อนดาเมจที่รับ 35% ฟื้นฟู HP 5% และ 25% โอกาสทำให้ศัตรูติดพิษ</t>
+  </si>
+  <si>
+    <t>POISON ECHO</t>
+  </si>
+  <si>
+    <t>Damage taken -5%; 12% chance to poison the enemy when hit (6% MaxHP/turn, 3 turns)</t>
+  </si>
+  <si>
+    <t>ลดดาเมจที่รับ 5% และ 12% โอกาสทำให้ศัตรูติดพิษเมื่อถูกโจมตี (6% MaxHP/เทิร์น นาน 3 เทิร์น)</t>
+  </si>
+  <si>
+    <t>🏰</t>
+  </si>
+  <si>
+    <t>GUARDIAN ECHO</t>
+  </si>
+  <si>
+    <t>Damage taken -12%; while HP &lt; 50%, reflects an extra 12% of damage taken back</t>
+  </si>
+  <si>
+    <t>ลดดาเมจที่รับ 12% และเมื่อ HP &lt; 50% จะสะท้อนดาเมจเพิ่มอีก 12%</t>
+  </si>
+  <si>
+    <t>🌑</t>
+  </si>
+  <si>
+    <t>DARK ECHO</t>
+  </si>
+  <si>
+    <t>Damage dealt +10%, crit chance +12%, lifesteal 7%</t>
+  </si>
+  <si>
+    <t>ดาเมจที่สร้างเพิ่มขึ้น 10%, คริ+12%, ดูดเลือด 7%</t>
+  </si>
+  <si>
+    <t>SPECTER ECHO</t>
+  </si>
+  <si>
+    <t>10% chance to fully dodge; on dodge, the next attack hits twice</t>
+  </si>
+  <si>
+    <t>10% โอกาสหลบการโจมตี เมื่อหลบสำเร็จ การโจมตีถัดไปโจมตี 2 ครั้ง</t>
+  </si>
+  <si>
+    <t>🧙</t>
+  </si>
+  <si>
+    <t>MAGE ECHO</t>
+  </si>
+  <si>
+    <t>⚰️</t>
+  </si>
+  <si>
+    <t>GRAVE ECHO</t>
+  </si>
+  <si>
+    <t>🥋</t>
+  </si>
+  <si>
+    <t>FIGHT ECHO</t>
+  </si>
+  <si>
+    <t>On WIN: damage dealt +8%, dodge +3%, crit chance +3% per stack (max 3 stacks)</t>
+  </si>
+  <si>
+    <t>เมื่อ WIN ดาเมจ+8%, หลบ+3%, คริ+3% (สะสมสูงสุด 3 ครั้ง)</t>
+  </si>
+  <si>
+    <t>QUICK ECHO</t>
+  </si>
+  <si>
+    <t>12% chance to fully dodge; on dodge, the next attack pierces DEF and cannot miss</t>
+  </si>
+  <si>
+    <t>12% โอกาสหลบการโจมตี เมื่อหลบสำเร็จ การโจมตีถัดไปทะลุ DEF และไม่พลาดเป้า</t>
+  </si>
+  <si>
+    <t>PHOENIX ECHO</t>
+  </si>
+  <si>
+    <t>Every attack has an 8% chance to burn the enemy; once per battle when HP &lt; 30%: heal 50% HP + ATK/DEF/SPD +8%</t>
+  </si>
+  <si>
+    <t>ทุกการโจมตีมีโอกาส 8% ทำให้ศัตรูติดเผาไหม้ เมื่อ HP&lt;30% (ครั้งเดียว): ฟื้น HP 50% + ATK/DEF/SPD +8%</t>
+  </si>
+  <si>
+    <t>IRON ECHO</t>
+  </si>
+  <si>
+    <t>On LOSE: damage taken -8% per stack (max 3 stacks per battle)</t>
+  </si>
+  <si>
+    <t>เมื่อ LOSE ลดดาเมจที่รับ 8% สะสม (สูงสุด 3 ครั้ง)</t>
+  </si>
+  <si>
+    <t>🔨</t>
+  </si>
+  <si>
+    <t>HAMMER ECHO</t>
+  </si>
+  <si>
+    <t>On WIN: damage dealt +10%, 8% chance to stun, and the attack pierces DEF</t>
+  </si>
+  <si>
+    <t>เมื่อ WIN ดาเมจ+10%, 8% โอกาสสตัน และโจมตีทะลุ DEF</t>
+  </si>
+  <si>
+    <t>❄️</t>
+  </si>
+  <si>
+    <t>CHILL ECHO</t>
+  </si>
+  <si>
+    <t>Every 3 turns: dodges 50% and attacks through DEF with ATK +25%</t>
+  </si>
+  <si>
+    <t>ทุก 3 เทิร์น: หลบ 50% และโจมตีทะลุ DEF ด้วย ATK+25%</t>
+  </si>
+  <si>
+    <t>🌿</t>
+  </si>
+  <si>
+    <t>GAIA ECHO</t>
+  </si>
+  <si>
+    <t>Every 3 rounds: recovers 8% of Max HP and ATK/DEF +10% that round</t>
+  </si>
+  <si>
+    <t>ทุก 3 รอบ: ฟื้น HP 8% ของ Max HP และ ATK/DEF+10% ในรอบนั้น</t>
+  </si>
+  <si>
+    <t>FATTY ECHO</t>
+  </si>
+  <si>
+    <t>Damage taken -10%; while HP &gt; 70%, ATK/DEF +15%; while HP &lt; 70%, ATK +25%</t>
+  </si>
+  <si>
+    <t>ลดดาเมจที่รับ 10% เมื่อ HP &gt; 70% ATK/DEF+15% เมื่อ HP &lt; 70% ATK+25%</t>
+  </si>
+  <si>
+    <t>GUANLET ECHO</t>
+  </si>
+  <si>
+    <t>On LOSE: damage dealt +8% per stack (max 5 stacks per battle)</t>
+  </si>
+  <si>
+    <t>เมื่อ LOSE ดาเมจเพิ่มขึ้นครั้งละ 8% (สะสมสูงสุด 5 ครั้ง)</t>
+  </si>
+  <si>
+    <t>BASTION ECHO</t>
+  </si>
+  <si>
+    <t>10% chance to fully dodge; every 3 turns, attacks cannot miss, deal +25% damage, and guarantee a crit</t>
+  </si>
+  <si>
+    <t>10% โอกาสหลบการโจมตี ทุก 3 เทิร์น โจมตีไม่พลาดเป้า ดาเมจ+25% และติดคริแน่นอน</t>
+  </si>
+  <si>
+    <t>💎</t>
+  </si>
+  <si>
+    <t>CRYSTAL ECHO</t>
+  </si>
+  <si>
+    <t>GOLEM ECHO</t>
+  </si>
+  <si>
+    <t>Damage taken -10%; while HP &lt; 30%, ATK +15% and recovers 2.5% HP each round</t>
+  </si>
+  <si>
+    <t>ลดดาเมจที่รับ 10% เมื่อ HP &lt; 30% ATK+15% และฟื้นฟู HP 2.5%</t>
+  </si>
+  <si>
+    <t>12% โอกาสหลบการโจมตี เมื่อหลบสำเร็จโต้กลับดาเมจ 75%</t>
+  </si>
+  <si>
+    <t>12% chance to fully dodge; on dodge, counter-attacks for 75% damage</t>
+  </si>
+  <si>
+    <t>12% โอกาสรับดาเมจครึ่งหนึ่งและโต้กลับด้วยดาเมจ 75%</t>
+  </si>
+  <si>
+    <t>12% chance to take half damage and counter-attack for 75% damage</t>
+  </si>
+  <si>
+    <t>Damage taken -10%; 25% chance to counter-attack for 75% damage</t>
+  </si>
+  <si>
+    <t>ลดดาเมจที่รับ 10% และ 25% โอกาสโต้กลับด้วยดาเมจ 75%</t>
+  </si>
+  <si>
+    <t>8% โอกาสสตันศัตรู และทุกรอบได้รับ Rune สุ่ม: ATK+50% หรือ DEF+50%</t>
+  </si>
+  <si>
+    <t>เมื่อ HP &lt; 50% ลดดาเมจที่รับ 10% และโต้กลับด้วยดาเมจ 75%</t>
+  </si>
+  <si>
+    <t>8% chance to stun the enemy; each round gains a random Rune: ATK+50% or DEF+50%</t>
+  </si>
+  <si>
+    <t>While HP &lt; 50%: damage taken -10% and counter-attacks for 75% damage</t>
+  </si>
+  <si>
+    <t>10% โอกาสหลบการโจมตี เมื่อหลบสำเร็จ ATK+50% รอบถัดไป</t>
+  </si>
+  <si>
+    <t>10% chance to fully dodge; on dodge, ATK +50% next round</t>
+  </si>
+  <si>
+    <t>8% โอกาส Stun ศัตรู ถ้าไม่ติดจะได้โอกาสหลบ 25% แทนในรอบนั้น</t>
+  </si>
+  <si>
+    <t>ลดดาเมจที่รับ 10% และเมื่อถูกโจมตีมีโอกาส 15% ทำให้อีกฝ่าย Stun 1 รอบ</t>
+  </si>
+  <si>
+    <t>8% chance to stun the enemy; if not stunned, gains 25% dodge that round instead</t>
+  </si>
+  <si>
+    <t>Damage taken -10%; when hit, 15% chance to stun the attacker for 1 round</t>
+  </si>
+  <si>
+    <t>ลดดาเมจที่รับ 12% และมีโอกาส 25% ฟื้นฟู HP 5%</t>
+  </si>
+  <si>
+    <t>Damage taken -12%; 25% chance to recover 5% HP each round</t>
+  </si>
+  <si>
+    <t>เมื่อ HP &gt; 50%: ATK+12% เมื่อ HP &lt; 50%: DEF+12%, โต้กลับดาเมจ 75%, 5% โอกาสสตันเมื่อโดนโจมตี</t>
+  </si>
+  <si>
+    <t>While HP &gt; 50%: ATK+12%. While HP &lt; 50%: DEF+12%, counter-attacks for 75% damage, 5% chance to stun when hit</t>
+  </si>
+  <si>
+    <t>On WIN: curses the enemy, ATK -12% for 2 turns; on DRAW: enemy cannot heal for 3 turns; on LOSE: damage taken -5%</t>
+  </si>
+  <si>
+    <t>เมื่อ WIN: สาปศัตรู ATK-12% นาน 2 เทิร์น เมื่อ DRAW: สาปให้ศัตรูฟื้นฟู HP ไม่ได้ 3 เทิร์น เมื่อ LOSE: ลดดาเมจที่รับ 5%</t>
   </si>
 </sst>
 </file>
@@ -13042,6 +14049,2048 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBF0D8DD-BA0A-4ACD-BB65-CCCC29CBF622}">
+  <dimension ref="A1:G59"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="3" width="12.69921875" customWidth="1"/>
+    <col min="4" max="4" width="6.69921875" customWidth="1"/>
+    <col min="5" max="5" width="20.69921875" customWidth="1"/>
+    <col min="6" max="7" width="55.69921875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>1656</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>1657</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>1658</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1659</v>
+      </c>
+      <c r="C4" t="s">
+        <v>1660</v>
+      </c>
+      <c r="D4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" t="s">
+        <v>267</v>
+      </c>
+      <c r="G4" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>1661</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" t="s">
+        <v>1662</v>
+      </c>
+      <c r="E5" t="s">
+        <v>1663</v>
+      </c>
+      <c r="F5" t="s">
+        <v>1664</v>
+      </c>
+      <c r="G5" t="s">
+        <v>1665</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>1661</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" t="s">
+        <v>1666</v>
+      </c>
+      <c r="E6" t="s">
+        <v>1667</v>
+      </c>
+      <c r="F6" t="s">
+        <v>1668</v>
+      </c>
+      <c r="G6" t="s">
+        <v>1669</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>1661</v>
+      </c>
+      <c r="B7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" t="s">
+        <v>1670</v>
+      </c>
+      <c r="E7" t="s">
+        <v>1671</v>
+      </c>
+      <c r="F7" t="s">
+        <v>1672</v>
+      </c>
+      <c r="G7" t="s">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>1661</v>
+      </c>
+      <c r="B8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" t="s">
+        <v>1674</v>
+      </c>
+      <c r="F8" t="s">
+        <v>1675</v>
+      </c>
+      <c r="G8" t="s">
+        <v>1676</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>1661</v>
+      </c>
+      <c r="B9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" t="s">
+        <v>1677</v>
+      </c>
+      <c r="E9" t="s">
+        <v>1678</v>
+      </c>
+      <c r="F9" t="s">
+        <v>1679</v>
+      </c>
+      <c r="G9" t="s">
+        <v>1680</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>1661</v>
+      </c>
+      <c r="B10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" t="s">
+        <v>31</v>
+      </c>
+      <c r="D10" t="s">
+        <v>1681</v>
+      </c>
+      <c r="E10" t="s">
+        <v>1682</v>
+      </c>
+      <c r="F10" t="s">
+        <v>1683</v>
+      </c>
+      <c r="G10" t="s">
+        <v>1684</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>1661</v>
+      </c>
+      <c r="B11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" t="s">
+        <v>1685</v>
+      </c>
+      <c r="E11" t="s">
+        <v>1686</v>
+      </c>
+      <c r="F11" t="s">
+        <v>1687</v>
+      </c>
+      <c r="G11" t="s">
+        <v>1688</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>1661</v>
+      </c>
+      <c r="B12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" t="s">
+        <v>1689</v>
+      </c>
+      <c r="E12" t="s">
+        <v>1690</v>
+      </c>
+      <c r="F12" t="s">
+        <v>1691</v>
+      </c>
+      <c r="G12" t="s">
+        <v>1692</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>1661</v>
+      </c>
+      <c r="B13" t="s">
+        <v>43</v>
+      </c>
+      <c r="C13" t="s">
+        <v>43</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1693</v>
+      </c>
+      <c r="E13" t="s">
+        <v>1694</v>
+      </c>
+      <c r="F13" t="s">
+        <v>1695</v>
+      </c>
+      <c r="G13" t="s">
+        <v>1696</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>1661</v>
+      </c>
+      <c r="B14" t="s">
+        <v>47</v>
+      </c>
+      <c r="C14" t="s">
+        <v>47</v>
+      </c>
+      <c r="D14" t="s">
+        <v>46</v>
+      </c>
+      <c r="E14" t="s">
+        <v>1697</v>
+      </c>
+      <c r="F14" t="s">
+        <v>1698</v>
+      </c>
+      <c r="G14" t="s">
+        <v>1699</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>1700</v>
+      </c>
+      <c r="B15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" t="s">
+        <v>16</v>
+      </c>
+      <c r="D15" t="s">
+        <v>1701</v>
+      </c>
+      <c r="E15" t="s">
+        <v>1702</v>
+      </c>
+      <c r="F15" t="s">
+        <v>1703</v>
+      </c>
+      <c r="G15" t="s">
+        <v>1704</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>1700</v>
+      </c>
+      <c r="B16" t="s">
+        <v>12</v>
+      </c>
+      <c r="C16" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" t="s">
+        <v>1705</v>
+      </c>
+      <c r="E16" t="s">
+        <v>1706</v>
+      </c>
+      <c r="F16" t="s">
+        <v>1707</v>
+      </c>
+      <c r="G16" t="s">
+        <v>1708</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>1700</v>
+      </c>
+      <c r="B17" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17" t="s">
+        <v>23</v>
+      </c>
+      <c r="D17" t="s">
+        <v>15</v>
+      </c>
+      <c r="E17" t="s">
+        <v>1709</v>
+      </c>
+      <c r="F17" t="s">
+        <v>1710</v>
+      </c>
+      <c r="G17" t="s">
+        <v>1711</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>1700</v>
+      </c>
+      <c r="B18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" t="s">
+        <v>27</v>
+      </c>
+      <c r="D18" t="s">
+        <v>1712</v>
+      </c>
+      <c r="E18" t="s">
+        <v>1713</v>
+      </c>
+      <c r="F18" t="s">
+        <v>1714</v>
+      </c>
+      <c r="G18" t="s">
+        <v>1715</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>1700</v>
+      </c>
+      <c r="B19" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19" t="s">
+        <v>31</v>
+      </c>
+      <c r="D19" t="s">
+        <v>498</v>
+      </c>
+      <c r="E19" t="s">
+        <v>1716</v>
+      </c>
+      <c r="F19" t="s">
+        <v>1717</v>
+      </c>
+      <c r="G19" t="s">
+        <v>1718</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>1700</v>
+      </c>
+      <c r="B20" t="s">
+        <v>12</v>
+      </c>
+      <c r="C20" t="s">
+        <v>35</v>
+      </c>
+      <c r="D20" t="s">
+        <v>1719</v>
+      </c>
+      <c r="E20" t="s">
+        <v>1720</v>
+      </c>
+      <c r="F20" t="s">
+        <v>1721</v>
+      </c>
+      <c r="G20" t="s">
+        <v>1722</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>1700</v>
+      </c>
+      <c r="B21" t="s">
+        <v>12</v>
+      </c>
+      <c r="C21" t="s">
+        <v>39</v>
+      </c>
+      <c r="D21" t="s">
+        <v>1723</v>
+      </c>
+      <c r="E21" t="s">
+        <v>1724</v>
+      </c>
+      <c r="F21" t="s">
+        <v>1725</v>
+      </c>
+      <c r="G21" t="s">
+        <v>1726</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>1700</v>
+      </c>
+      <c r="B22" t="s">
+        <v>12</v>
+      </c>
+      <c r="C22" t="s">
+        <v>43</v>
+      </c>
+      <c r="D22" t="s">
+        <v>498</v>
+      </c>
+      <c r="E22" t="s">
+        <v>1727</v>
+      </c>
+      <c r="F22" t="s">
+        <v>1728</v>
+      </c>
+      <c r="G22" t="s">
+        <v>1729</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>1700</v>
+      </c>
+      <c r="B23" t="s">
+        <v>12</v>
+      </c>
+      <c r="C23" t="s">
+        <v>47</v>
+      </c>
+      <c r="D23" t="s">
+        <v>1730</v>
+      </c>
+      <c r="E23" t="s">
+        <v>1731</v>
+      </c>
+      <c r="F23" t="s">
+        <v>1732</v>
+      </c>
+      <c r="G23" t="s">
+        <v>1733</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>1700</v>
+      </c>
+      <c r="B24" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" t="s">
+        <v>20</v>
+      </c>
+      <c r="D24" t="s">
+        <v>1670</v>
+      </c>
+      <c r="E24" t="s">
+        <v>1734</v>
+      </c>
+      <c r="F24" t="s">
+        <v>1735</v>
+      </c>
+      <c r="G24" t="s">
+        <v>1736</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>1700</v>
+      </c>
+      <c r="B25" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" t="s">
+        <v>23</v>
+      </c>
+      <c r="D25" t="s">
+        <v>15</v>
+      </c>
+      <c r="E25" t="s">
+        <v>1737</v>
+      </c>
+      <c r="F25" t="s">
+        <v>1738</v>
+      </c>
+      <c r="G25" t="s">
+        <v>1739</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>1700</v>
+      </c>
+      <c r="B26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" t="s">
+        <v>27</v>
+      </c>
+      <c r="D26" t="s">
+        <v>1740</v>
+      </c>
+      <c r="E26" t="s">
+        <v>1741</v>
+      </c>
+      <c r="F26" t="s">
+        <v>1742</v>
+      </c>
+      <c r="G26" t="s">
+        <v>1743</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>1700</v>
+      </c>
+      <c r="B27" t="s">
+        <v>16</v>
+      </c>
+      <c r="C27" t="s">
+        <v>31</v>
+      </c>
+      <c r="D27" t="s">
+        <v>1744</v>
+      </c>
+      <c r="E27" t="s">
+        <v>1745</v>
+      </c>
+      <c r="F27" t="s">
+        <v>1746</v>
+      </c>
+      <c r="G27" t="s">
+        <v>1747</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>1700</v>
+      </c>
+      <c r="B28" t="s">
+        <v>16</v>
+      </c>
+      <c r="C28" t="s">
+        <v>35</v>
+      </c>
+      <c r="D28" t="s">
+        <v>1748</v>
+      </c>
+      <c r="E28" t="s">
+        <v>1749</v>
+      </c>
+      <c r="F28" t="s">
+        <v>1750</v>
+      </c>
+      <c r="G28" t="s">
+        <v>1751</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>1700</v>
+      </c>
+      <c r="B29" t="s">
+        <v>16</v>
+      </c>
+      <c r="C29" t="s">
+        <v>39</v>
+      </c>
+      <c r="D29" t="s">
+        <v>1752</v>
+      </c>
+      <c r="E29" t="s">
+        <v>1753</v>
+      </c>
+      <c r="F29" t="s">
+        <v>1754</v>
+      </c>
+      <c r="G29" t="s">
+        <v>1755</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>1700</v>
+      </c>
+      <c r="B30" t="s">
+        <v>16</v>
+      </c>
+      <c r="C30" t="s">
+        <v>43</v>
+      </c>
+      <c r="D30" t="s">
+        <v>1693</v>
+      </c>
+      <c r="E30" t="s">
+        <v>1756</v>
+      </c>
+      <c r="F30" t="s">
+        <v>1757</v>
+      </c>
+      <c r="G30" t="s">
+        <v>1758</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>1700</v>
+      </c>
+      <c r="B31" t="s">
+        <v>16</v>
+      </c>
+      <c r="C31" t="s">
+        <v>47</v>
+      </c>
+      <c r="D31" t="s">
+        <v>498</v>
+      </c>
+      <c r="E31" t="s">
+        <v>1759</v>
+      </c>
+      <c r="F31" t="s">
+        <v>1760</v>
+      </c>
+      <c r="G31" t="s">
+        <v>1761</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>1700</v>
+      </c>
+      <c r="B32" t="s">
+        <v>20</v>
+      </c>
+      <c r="C32" t="s">
+        <v>23</v>
+      </c>
+      <c r="D32" t="s">
+        <v>1762</v>
+      </c>
+      <c r="E32" t="s">
+        <v>1763</v>
+      </c>
+      <c r="F32" t="s">
+        <v>1764</v>
+      </c>
+      <c r="G32" t="s">
+        <v>1765</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>1700</v>
+      </c>
+      <c r="B33" t="s">
+        <v>20</v>
+      </c>
+      <c r="C33" t="s">
+        <v>27</v>
+      </c>
+      <c r="D33" t="s">
+        <v>1670</v>
+      </c>
+      <c r="E33" t="s">
+        <v>1766</v>
+      </c>
+      <c r="F33" t="s">
+        <v>1767</v>
+      </c>
+      <c r="G33" t="s">
+        <v>1768</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>1700</v>
+      </c>
+      <c r="B34" t="s">
+        <v>20</v>
+      </c>
+      <c r="C34" t="s">
+        <v>31</v>
+      </c>
+      <c r="D34" t="s">
+        <v>1769</v>
+      </c>
+      <c r="E34" t="s">
+        <v>1770</v>
+      </c>
+      <c r="F34" t="s">
+        <v>1771</v>
+      </c>
+      <c r="G34" t="s">
+        <v>1772</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>1700</v>
+      </c>
+      <c r="B35" t="s">
+        <v>20</v>
+      </c>
+      <c r="C35" t="s">
+        <v>35</v>
+      </c>
+      <c r="D35" t="s">
+        <v>1773</v>
+      </c>
+      <c r="E35" t="s">
+        <v>1774</v>
+      </c>
+      <c r="F35" t="s">
+        <v>1775</v>
+      </c>
+      <c r="G35" t="s">
+        <v>1776</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>1700</v>
+      </c>
+      <c r="B36" t="s">
+        <v>20</v>
+      </c>
+      <c r="C36" t="s">
+        <v>39</v>
+      </c>
+      <c r="D36" t="s">
+        <v>1752</v>
+      </c>
+      <c r="E36" t="s">
+        <v>1777</v>
+      </c>
+      <c r="F36" t="s">
+        <v>1778</v>
+      </c>
+      <c r="G36" t="s">
+        <v>1779</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>1700</v>
+      </c>
+      <c r="B37" t="s">
+        <v>20</v>
+      </c>
+      <c r="C37" t="s">
+        <v>43</v>
+      </c>
+      <c r="D37" t="s">
+        <v>1693</v>
+      </c>
+      <c r="E37" t="s">
+        <v>1780</v>
+      </c>
+      <c r="F37" t="s">
+        <v>1781</v>
+      </c>
+      <c r="G37" t="s">
+        <v>1782</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>1700</v>
+      </c>
+      <c r="B38" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38" t="s">
+        <v>47</v>
+      </c>
+      <c r="D38" t="s">
+        <v>1681</v>
+      </c>
+      <c r="E38" t="s">
+        <v>1783</v>
+      </c>
+      <c r="F38" t="s">
+        <v>1784</v>
+      </c>
+      <c r="G38" t="s">
+        <v>1785</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>1700</v>
+      </c>
+      <c r="B39" t="s">
+        <v>23</v>
+      </c>
+      <c r="C39" t="s">
+        <v>27</v>
+      </c>
+      <c r="D39" t="s">
+        <v>15</v>
+      </c>
+      <c r="E39" t="s">
+        <v>1786</v>
+      </c>
+      <c r="F39" t="s">
+        <v>1787</v>
+      </c>
+      <c r="G39" t="s">
+        <v>1788</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>1700</v>
+      </c>
+      <c r="B40" t="s">
+        <v>23</v>
+      </c>
+      <c r="C40" t="s">
+        <v>31</v>
+      </c>
+      <c r="D40" t="s">
+        <v>1769</v>
+      </c>
+      <c r="E40" t="s">
+        <v>1789</v>
+      </c>
+      <c r="F40" t="s">
+        <v>1790</v>
+      </c>
+      <c r="G40" t="s">
+        <v>1791</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>1700</v>
+      </c>
+      <c r="B41" t="s">
+        <v>23</v>
+      </c>
+      <c r="C41" t="s">
+        <v>35</v>
+      </c>
+      <c r="D41" t="s">
+        <v>1685</v>
+      </c>
+      <c r="E41" t="s">
+        <v>1792</v>
+      </c>
+      <c r="F41" t="s">
+        <v>1793</v>
+      </c>
+      <c r="G41" t="s">
+        <v>1794</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>1700</v>
+      </c>
+      <c r="B42" t="s">
+        <v>23</v>
+      </c>
+      <c r="C42" t="s">
+        <v>39</v>
+      </c>
+      <c r="D42" t="s">
+        <v>504</v>
+      </c>
+      <c r="E42" t="s">
+        <v>1795</v>
+      </c>
+      <c r="F42" t="s">
+        <v>1796</v>
+      </c>
+      <c r="G42" t="s">
+        <v>1797</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>1700</v>
+      </c>
+      <c r="B43" t="s">
+        <v>23</v>
+      </c>
+      <c r="C43" t="s">
+        <v>43</v>
+      </c>
+      <c r="D43" t="s">
+        <v>1239</v>
+      </c>
+      <c r="E43" t="s">
+        <v>1798</v>
+      </c>
+      <c r="F43" t="s">
+        <v>1799</v>
+      </c>
+      <c r="G43" t="s">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>1700</v>
+      </c>
+      <c r="B44" t="s">
+        <v>23</v>
+      </c>
+      <c r="C44" t="s">
+        <v>47</v>
+      </c>
+      <c r="D44" t="s">
+        <v>1730</v>
+      </c>
+      <c r="E44" t="s">
+        <v>1801</v>
+      </c>
+      <c r="F44" t="s">
+        <v>1802</v>
+      </c>
+      <c r="G44" t="s">
+        <v>1803</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>1700</v>
+      </c>
+      <c r="B45" t="s">
+        <v>27</v>
+      </c>
+      <c r="C45" t="s">
+        <v>31</v>
+      </c>
+      <c r="D45" t="s">
+        <v>1677</v>
+      </c>
+      <c r="E45" t="s">
+        <v>1804</v>
+      </c>
+      <c r="F45" t="s">
+        <v>1805</v>
+      </c>
+      <c r="G45" t="s">
+        <v>1806</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>1700</v>
+      </c>
+      <c r="B46" t="s">
+        <v>27</v>
+      </c>
+      <c r="C46" t="s">
+        <v>35</v>
+      </c>
+      <c r="D46" t="s">
+        <v>1807</v>
+      </c>
+      <c r="E46" t="s">
+        <v>1808</v>
+      </c>
+      <c r="F46" t="s">
+        <v>1809</v>
+      </c>
+      <c r="G46" t="s">
+        <v>1810</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>1700</v>
+      </c>
+      <c r="B47" t="s">
+        <v>27</v>
+      </c>
+      <c r="C47" t="s">
+        <v>39</v>
+      </c>
+      <c r="D47" t="s">
+        <v>1811</v>
+      </c>
+      <c r="E47" t="s">
+        <v>1812</v>
+      </c>
+      <c r="F47" t="s">
+        <v>1813</v>
+      </c>
+      <c r="G47" t="s">
+        <v>1814</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>1700</v>
+      </c>
+      <c r="B48" t="s">
+        <v>27</v>
+      </c>
+      <c r="C48" t="s">
+        <v>43</v>
+      </c>
+      <c r="D48" t="s">
+        <v>1807</v>
+      </c>
+      <c r="E48" t="s">
+        <v>1815</v>
+      </c>
+      <c r="F48" t="s">
+        <v>1816</v>
+      </c>
+      <c r="G48" t="s">
+        <v>1817</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>1700</v>
+      </c>
+      <c r="B49" t="s">
+        <v>27</v>
+      </c>
+      <c r="C49" t="s">
+        <v>47</v>
+      </c>
+      <c r="D49" t="s">
+        <v>1807</v>
+      </c>
+      <c r="E49" t="s">
+        <v>1818</v>
+      </c>
+      <c r="F49" t="s">
+        <v>1819</v>
+      </c>
+      <c r="G49" t="s">
+        <v>1820</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>1700</v>
+      </c>
+      <c r="B50" t="s">
+        <v>31</v>
+      </c>
+      <c r="C50" t="s">
+        <v>35</v>
+      </c>
+      <c r="D50" t="s">
+        <v>1685</v>
+      </c>
+      <c r="E50" t="s">
+        <v>1821</v>
+      </c>
+      <c r="F50" t="s">
+        <v>1822</v>
+      </c>
+      <c r="G50" t="s">
+        <v>1823</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>1700</v>
+      </c>
+      <c r="B51" t="s">
+        <v>31</v>
+      </c>
+      <c r="C51" t="s">
+        <v>39</v>
+      </c>
+      <c r="D51" t="s">
+        <v>1752</v>
+      </c>
+      <c r="E51" t="s">
+        <v>1824</v>
+      </c>
+      <c r="F51" t="s">
+        <v>1825</v>
+      </c>
+      <c r="G51" t="s">
+        <v>1826</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>1700</v>
+      </c>
+      <c r="B52" t="s">
+        <v>31</v>
+      </c>
+      <c r="C52" t="s">
+        <v>43</v>
+      </c>
+      <c r="D52" t="s">
+        <v>1693</v>
+      </c>
+      <c r="E52" t="s">
+        <v>1827</v>
+      </c>
+      <c r="F52" t="s">
+        <v>1828</v>
+      </c>
+      <c r="G52" t="s">
+        <v>1829</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>1700</v>
+      </c>
+      <c r="B53" t="s">
+        <v>31</v>
+      </c>
+      <c r="C53" t="s">
+        <v>47</v>
+      </c>
+      <c r="D53" t="s">
+        <v>46</v>
+      </c>
+      <c r="E53" t="s">
+        <v>1830</v>
+      </c>
+      <c r="F53" t="s">
+        <v>1831</v>
+      </c>
+      <c r="G53" t="s">
+        <v>1832</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>1700</v>
+      </c>
+      <c r="B54" t="s">
+        <v>35</v>
+      </c>
+      <c r="C54" t="s">
+        <v>39</v>
+      </c>
+      <c r="D54" t="s">
+        <v>1752</v>
+      </c>
+      <c r="E54" t="s">
+        <v>1833</v>
+      </c>
+      <c r="F54" t="s">
+        <v>1834</v>
+      </c>
+      <c r="G54" t="s">
+        <v>1835</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>1700</v>
+      </c>
+      <c r="B55" t="s">
+        <v>35</v>
+      </c>
+      <c r="C55" t="s">
+        <v>43</v>
+      </c>
+      <c r="D55" t="s">
+        <v>1693</v>
+      </c>
+      <c r="E55" t="s">
+        <v>1836</v>
+      </c>
+      <c r="F55" t="s">
+        <v>1837</v>
+      </c>
+      <c r="G55" t="s">
+        <v>1838</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>1700</v>
+      </c>
+      <c r="B56" t="s">
+        <v>35</v>
+      </c>
+      <c r="C56" t="s">
+        <v>47</v>
+      </c>
+      <c r="D56" t="s">
+        <v>46</v>
+      </c>
+      <c r="E56" t="s">
+        <v>1839</v>
+      </c>
+      <c r="F56" t="s">
+        <v>1840</v>
+      </c>
+      <c r="G56" t="s">
+        <v>1841</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>1700</v>
+      </c>
+      <c r="B57" t="s">
+        <v>39</v>
+      </c>
+      <c r="C57" t="s">
+        <v>43</v>
+      </c>
+      <c r="D57" t="s">
+        <v>1693</v>
+      </c>
+      <c r="E57" t="s">
+        <v>1842</v>
+      </c>
+      <c r="F57" t="s">
+        <v>1843</v>
+      </c>
+      <c r="G57" t="s">
+        <v>1692</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>1700</v>
+      </c>
+      <c r="B58" t="s">
+        <v>39</v>
+      </c>
+      <c r="C58" t="s">
+        <v>47</v>
+      </c>
+      <c r="D58" t="s">
+        <v>1844</v>
+      </c>
+      <c r="E58" t="s">
+        <v>1845</v>
+      </c>
+      <c r="F58" t="s">
+        <v>1846</v>
+      </c>
+      <c r="G58" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>1700</v>
+      </c>
+      <c r="B59" t="s">
+        <v>43</v>
+      </c>
+      <c r="C59" t="s">
+        <v>47</v>
+      </c>
+      <c r="D59" t="s">
+        <v>46</v>
+      </c>
+      <c r="E59" t="s">
+        <v>1848</v>
+      </c>
+      <c r="F59" t="s">
+        <v>1849</v>
+      </c>
+      <c r="G59" t="s">
+        <v>1850</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F00FD1CF-924F-4FD0-B28B-32154B63F96A}">
+  <dimension ref="A1:E45"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="18.69921875" customWidth="1"/>
+    <col min="2" max="2" width="6.69921875" customWidth="1"/>
+    <col min="3" max="3" width="18.69921875" customWidth="1"/>
+    <col min="4" max="5" width="60.69921875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>1851</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>1852</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>1853</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>1854</v>
+      </c>
+      <c r="B5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" t="s">
+        <v>1855</v>
+      </c>
+      <c r="D5" t="s">
+        <v>267</v>
+      </c>
+      <c r="E5" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1662</v>
+      </c>
+      <c r="C6" t="s">
+        <v>1856</v>
+      </c>
+      <c r="D6" t="s">
+        <v>1857</v>
+      </c>
+      <c r="E6" t="s">
+        <v>1858</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>64</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1859</v>
+      </c>
+      <c r="C7" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D7" t="s">
+        <v>1970</v>
+      </c>
+      <c r="E7" t="s">
+        <v>1969</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>69</v>
+      </c>
+      <c r="B8" t="s">
+        <v>1861</v>
+      </c>
+      <c r="C8" t="s">
+        <v>1862</v>
+      </c>
+      <c r="D8" t="s">
+        <v>1863</v>
+      </c>
+      <c r="E8" t="s">
+        <v>1864</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>73</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1865</v>
+      </c>
+      <c r="C9" t="s">
+        <v>1866</v>
+      </c>
+      <c r="D9" t="s">
+        <v>1867</v>
+      </c>
+      <c r="E9" t="s">
+        <v>1868</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>76</v>
+      </c>
+      <c r="B10" t="s">
+        <v>1712</v>
+      </c>
+      <c r="C10" t="s">
+        <v>1869</v>
+      </c>
+      <c r="D10" t="s">
+        <v>1870</v>
+      </c>
+      <c r="E10" t="s">
+        <v>1871</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>80</v>
+      </c>
+      <c r="B11" t="s">
+        <v>1748</v>
+      </c>
+      <c r="C11" t="s">
+        <v>1872</v>
+      </c>
+      <c r="D11" t="s">
+        <v>1873</v>
+      </c>
+      <c r="E11" t="s">
+        <v>1874</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>84</v>
+      </c>
+      <c r="B12" t="s">
+        <v>1666</v>
+      </c>
+      <c r="C12" t="s">
+        <v>1875</v>
+      </c>
+      <c r="D12" t="s">
+        <v>1972</v>
+      </c>
+      <c r="E12" t="s">
+        <v>1971</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>88</v>
+      </c>
+      <c r="B13" t="s">
+        <v>1876</v>
+      </c>
+      <c r="C13" t="s">
+        <v>1877</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1973</v>
+      </c>
+      <c r="E13" t="s">
+        <v>1974</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>91</v>
+      </c>
+      <c r="B14" t="s">
+        <v>1670</v>
+      </c>
+      <c r="C14" t="s">
+        <v>1878</v>
+      </c>
+      <c r="D14" t="s">
+        <v>1879</v>
+      </c>
+      <c r="E14" t="s">
+        <v>1880</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>95</v>
+      </c>
+      <c r="B15" t="s">
+        <v>429</v>
+      </c>
+      <c r="C15" t="s">
+        <v>1881</v>
+      </c>
+      <c r="D15" t="s">
+        <v>1882</v>
+      </c>
+      <c r="E15" t="s">
+        <v>1883</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>99</v>
+      </c>
+      <c r="B16" t="s">
+        <v>1884</v>
+      </c>
+      <c r="C16" t="s">
+        <v>1885</v>
+      </c>
+      <c r="D16" t="s">
+        <v>1977</v>
+      </c>
+      <c r="E16" t="s">
+        <v>1975</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>103</v>
+      </c>
+      <c r="B17" t="s">
+        <v>1876</v>
+      </c>
+      <c r="C17" t="s">
+        <v>1886</v>
+      </c>
+      <c r="D17" t="s">
+        <v>1978</v>
+      </c>
+      <c r="E17" t="s">
+        <v>1976</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>107</v>
+      </c>
+      <c r="B18" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18" t="s">
+        <v>1887</v>
+      </c>
+      <c r="D18" t="s">
+        <v>1888</v>
+      </c>
+      <c r="E18" t="s">
+        <v>1889</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>111</v>
+      </c>
+      <c r="B19" t="s">
+        <v>1890</v>
+      </c>
+      <c r="C19" t="s">
+        <v>1891</v>
+      </c>
+      <c r="D19" t="s">
+        <v>1980</v>
+      </c>
+      <c r="E19" t="s">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>115</v>
+      </c>
+      <c r="B20" t="s">
+        <v>1239</v>
+      </c>
+      <c r="C20" t="s">
+        <v>1892</v>
+      </c>
+      <c r="D20" t="s">
+        <v>1983</v>
+      </c>
+      <c r="E20" t="s">
+        <v>1981</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>119</v>
+      </c>
+      <c r="B21" t="s">
+        <v>1876</v>
+      </c>
+      <c r="C21" t="s">
+        <v>1893</v>
+      </c>
+      <c r="D21" t="s">
+        <v>1984</v>
+      </c>
+      <c r="E21" t="s">
+        <v>1982</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>123</v>
+      </c>
+      <c r="B22" t="s">
+        <v>681</v>
+      </c>
+      <c r="C22" t="s">
+        <v>1894</v>
+      </c>
+      <c r="D22" t="s">
+        <v>1895</v>
+      </c>
+      <c r="E22" t="s">
+        <v>1896</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>127</v>
+      </c>
+      <c r="B23" t="s">
+        <v>1807</v>
+      </c>
+      <c r="C23" t="s">
+        <v>1897</v>
+      </c>
+      <c r="D23" t="s">
+        <v>1898</v>
+      </c>
+      <c r="E23" t="s">
+        <v>1899</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>131</v>
+      </c>
+      <c r="B24" t="s">
+        <v>1844</v>
+      </c>
+      <c r="C24" t="s">
+        <v>1900</v>
+      </c>
+      <c r="D24" t="s">
+        <v>1901</v>
+      </c>
+      <c r="E24" t="s">
+        <v>1902</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>134</v>
+      </c>
+      <c r="B25" t="s">
+        <v>1752</v>
+      </c>
+      <c r="C25" t="s">
+        <v>1903</v>
+      </c>
+      <c r="D25" t="s">
+        <v>1904</v>
+      </c>
+      <c r="E25" t="s">
+        <v>1905</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>138</v>
+      </c>
+      <c r="B26" t="s">
+        <v>1701</v>
+      </c>
+      <c r="C26" t="s">
+        <v>1906</v>
+      </c>
+      <c r="D26" t="s">
+        <v>1907</v>
+      </c>
+      <c r="E26" t="s">
+        <v>1908</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>142</v>
+      </c>
+      <c r="B27" t="s">
+        <v>1769</v>
+      </c>
+      <c r="C27" t="s">
+        <v>1909</v>
+      </c>
+      <c r="D27" t="s">
+        <v>1910</v>
+      </c>
+      <c r="E27" t="s">
+        <v>1911</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>146</v>
+      </c>
+      <c r="B28" t="s">
+        <v>453</v>
+      </c>
+      <c r="C28" t="s">
+        <v>1912</v>
+      </c>
+      <c r="D28" t="s">
+        <v>1913</v>
+      </c>
+      <c r="E28" t="s">
+        <v>1914</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>150</v>
+      </c>
+      <c r="B29" t="s">
+        <v>1915</v>
+      </c>
+      <c r="C29" t="s">
+        <v>1916</v>
+      </c>
+      <c r="D29" t="s">
+        <v>1917</v>
+      </c>
+      <c r="E29" t="s">
+        <v>1918</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>154</v>
+      </c>
+      <c r="B30" t="s">
+        <v>1919</v>
+      </c>
+      <c r="C30" t="s">
+        <v>1920</v>
+      </c>
+      <c r="D30" t="s">
+        <v>1921</v>
+      </c>
+      <c r="E30" t="s">
+        <v>1922</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>158</v>
+      </c>
+      <c r="B31" t="s">
+        <v>1685</v>
+      </c>
+      <c r="C31" t="s">
+        <v>1923</v>
+      </c>
+      <c r="D31" t="s">
+        <v>1924</v>
+      </c>
+      <c r="E31" t="s">
+        <v>1925</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>162</v>
+      </c>
+      <c r="B32" t="s">
+        <v>1926</v>
+      </c>
+      <c r="C32" t="s">
+        <v>1927</v>
+      </c>
+      <c r="D32" t="s">
+        <v>1989</v>
+      </c>
+      <c r="E32" t="s">
+        <v>1990</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>166</v>
+      </c>
+      <c r="B33" t="s">
+        <v>1928</v>
+      </c>
+      <c r="C33" t="s">
+        <v>1929</v>
+      </c>
+      <c r="D33" t="s">
+        <v>1986</v>
+      </c>
+      <c r="E33" t="s">
+        <v>1985</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>171</v>
+      </c>
+      <c r="B34" t="s">
+        <v>1930</v>
+      </c>
+      <c r="C34" t="s">
+        <v>1931</v>
+      </c>
+      <c r="D34" t="s">
+        <v>1932</v>
+      </c>
+      <c r="E34" t="s">
+        <v>1933</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>175</v>
+      </c>
+      <c r="B35" t="s">
+        <v>504</v>
+      </c>
+      <c r="C35" t="s">
+        <v>1934</v>
+      </c>
+      <c r="D35" t="s">
+        <v>1935</v>
+      </c>
+      <c r="E35" t="s">
+        <v>1936</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>179</v>
+      </c>
+      <c r="B36" t="s">
+        <v>1701</v>
+      </c>
+      <c r="C36" t="s">
+        <v>1937</v>
+      </c>
+      <c r="D36" t="s">
+        <v>1938</v>
+      </c>
+      <c r="E36" t="s">
+        <v>1939</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>181</v>
+      </c>
+      <c r="B37" t="s">
+        <v>1876</v>
+      </c>
+      <c r="C37" t="s">
+        <v>1940</v>
+      </c>
+      <c r="D37" t="s">
+        <v>1941</v>
+      </c>
+      <c r="E37" t="s">
+        <v>1942</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>185</v>
+      </c>
+      <c r="B38" t="s">
+        <v>1943</v>
+      </c>
+      <c r="C38" t="s">
+        <v>1944</v>
+      </c>
+      <c r="D38" t="s">
+        <v>1945</v>
+      </c>
+      <c r="E38" t="s">
+        <v>1946</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>189</v>
+      </c>
+      <c r="B39" t="s">
+        <v>1947</v>
+      </c>
+      <c r="C39" t="s">
+        <v>1948</v>
+      </c>
+      <c r="D39" t="s">
+        <v>1949</v>
+      </c>
+      <c r="E39" t="s">
+        <v>1950</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>193</v>
+      </c>
+      <c r="B40" t="s">
+        <v>1951</v>
+      </c>
+      <c r="C40" t="s">
+        <v>1952</v>
+      </c>
+      <c r="D40" t="s">
+        <v>1953</v>
+      </c>
+      <c r="E40" t="s">
+        <v>1954</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>197</v>
+      </c>
+      <c r="B41" t="s">
+        <v>1876</v>
+      </c>
+      <c r="C41" t="s">
+        <v>1955</v>
+      </c>
+      <c r="D41" t="s">
+        <v>1956</v>
+      </c>
+      <c r="E41" t="s">
+        <v>1957</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>201</v>
+      </c>
+      <c r="B42" t="s">
+        <v>1712</v>
+      </c>
+      <c r="C42" t="s">
+        <v>1958</v>
+      </c>
+      <c r="D42" t="s">
+        <v>1959</v>
+      </c>
+      <c r="E42" t="s">
+        <v>1960</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>205</v>
+      </c>
+      <c r="B43" t="s">
+        <v>1740</v>
+      </c>
+      <c r="C43" t="s">
+        <v>1961</v>
+      </c>
+      <c r="D43" t="s">
+        <v>1962</v>
+      </c>
+      <c r="E43" t="s">
+        <v>1963</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>209</v>
+      </c>
+      <c r="B44" t="s">
+        <v>1964</v>
+      </c>
+      <c r="C44" t="s">
+        <v>1965</v>
+      </c>
+      <c r="D44" t="s">
+        <v>1988</v>
+      </c>
+      <c r="E44" t="s">
+        <v>1987</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>212</v>
+      </c>
+      <c r="B45" t="s">
+        <v>1681</v>
+      </c>
+      <c r="C45" t="s">
+        <v>1966</v>
+      </c>
+      <c r="D45" t="s">
+        <v>1967</v>
+      </c>
+      <c r="E45" t="s">
+        <v>1968</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:L44"/>
@@ -14829,12 +17878,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="B29:B31"/>
-    <mergeCell ref="B14:B16"/>
-    <mergeCell ref="A8:A10"/>
-    <mergeCell ref="A26:A28"/>
-    <mergeCell ref="A17:A19"/>
-    <mergeCell ref="A20:A22"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A5:A7"/>
     <mergeCell ref="A23:A25"/>
@@ -14851,6 +17894,12 @@
     <mergeCell ref="B17:B19"/>
     <mergeCell ref="B23:B25"/>
     <mergeCell ref="A29:A31"/>
+    <mergeCell ref="B29:B31"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="A8:A10"/>
+    <mergeCell ref="A26:A28"/>
+    <mergeCell ref="A17:A19"/>
+    <mergeCell ref="A20:A22"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <ignoredErrors>

--- a/SYMBEAST_Evolve_Forms.xlsx
+++ b/SYMBEAST_Evolve_Forms.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\skyit\Desktop\Symbeast-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2068D9C-48DA-419B-8811-7E187A3DE873}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B108191-F671-49A6-8113-83BAD93AB664}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="10" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="11" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Evolved Forms" sheetId="1" r:id="rId1"/>
@@ -29,13 +29,14 @@
     <sheet name="Scout Rewards" sheetId="14" r:id="rId14"/>
     <sheet name="Fusion Passives" sheetId="15" r:id="rId15"/>
     <sheet name="Fusion Passives v2" sheetId="16" r:id="rId16"/>
+    <sheet name="Weapon Tiers" sheetId="17" r:id="rId17"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3203" uniqueCount="1991">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3608" uniqueCount="2127">
   <si>
     <t>SYMBEAST — Evolved Forms (Stage 1, 10 forms)</t>
   </si>
@@ -6008,6 +6009,414 @@
   </si>
   <si>
     <t>เมื่อ WIN: สาปศัตรู ATK-12% นาน 2 เทิร์น เมื่อ DRAW: สาปให้ศัตรูฟื้นฟู HP ไม่ได้ 3 เทิร์น เมื่อ LOSE: ลดดาเมจที่รับ 5%</t>
+  </si>
+  <si>
+    <t>SYMBEAST — Weapon Quality Tiers (proposal, ยังไม่ implement) — R/E grade only, N grade unchanged</t>
+  </si>
+  <si>
+    <t>แต่ละอาวุธ R/E จะมี 3 ระดับคุณภาพ: Low (x0.75 สเตตัส+โอกาส), Normal (ของเดิม), High (x1.25 สเตตัส+โอกาส) -- ความแรงตอนพาสซีฟติด (เช่น dmg+50%) คงเดิมทุกระดับ ไม่ปรับ</t>
+  </si>
+  <si>
+    <t>โอกาสสุ่มระดับตอนดรอป (แยกชั้นจากการสุ่มเกรด N/R/E เดิม): Low 50% / Normal 35% / High 15%</t>
+  </si>
+  <si>
+    <t>Stat Bonus</t>
+  </si>
+  <si>
+    <t>Passive Effect</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>ATK+38</t>
+  </si>
+  <si>
+    <t>8% chance dmg dealt +50%</t>
+  </si>
+  <si>
+    <t>ATK+50</t>
+  </si>
+  <si>
+    <t>10% chance dmg dealt +50%</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>ATK+63</t>
+  </si>
+  <si>
+    <t>13% chance dmg dealt +50%</t>
+  </si>
+  <si>
+    <t>DEF+38</t>
+  </si>
+  <si>
+    <t>8% chance block (-50% dmg)</t>
+  </si>
+  <si>
+    <t>DEF+50</t>
+  </si>
+  <si>
+    <t>10% chance block (-50% dmg)</t>
+  </si>
+  <si>
+    <t>DEF+63</t>
+  </si>
+  <si>
+    <t>13% chance block (-50% dmg)</t>
+  </si>
+  <si>
+    <t>SPD+38</t>
+  </si>
+  <si>
+    <t>4% chance dodge</t>
+  </si>
+  <si>
+    <t>SPD+50</t>
+  </si>
+  <si>
+    <t>5% chance dodge</t>
+  </si>
+  <si>
+    <t>SPD+63</t>
+  </si>
+  <si>
+    <t>6% chance dodge</t>
+  </si>
+  <si>
+    <t>MaxHP+150</t>
+  </si>
+  <si>
+    <t>8% chance regen 5% Max HP</t>
+  </si>
+  <si>
+    <t>MaxHP+200</t>
+  </si>
+  <si>
+    <t>10% chance regen 5% Max HP</t>
+  </si>
+  <si>
+    <t>MaxHP+250</t>
+  </si>
+  <si>
+    <t>13% chance regen 5% Max HP</t>
+  </si>
+  <si>
+    <t>ATK+23, SPD+23</t>
+  </si>
+  <si>
+    <t>8% chance attack twice</t>
+  </si>
+  <si>
+    <t>ATK+30, SPD+30</t>
+  </si>
+  <si>
+    <t>10% chance attack twice</t>
+  </si>
+  <si>
+    <t>ATK+38, SPD+38</t>
+  </si>
+  <si>
+    <t>13% chance attack twice</t>
+  </si>
+  <si>
+    <t>DEF+23, MaxHP+113</t>
+  </si>
+  <si>
+    <t>8% chance counter (75% dmg)</t>
+  </si>
+  <si>
+    <t>DEF+30, MaxHP+150</t>
+  </si>
+  <si>
+    <t>10% chance counter (75% dmg)</t>
+  </si>
+  <si>
+    <t>DEF+38, MaxHP+188</t>
+  </si>
+  <si>
+    <t>13% chance counter (75% dmg)</t>
+  </si>
+  <si>
+    <t>ATK/DEF/SPD+15, MaxHP+75</t>
+  </si>
+  <si>
+    <t>On LOSE, damage received -8%</t>
+  </si>
+  <si>
+    <t>ATK/DEF/SPD+20, MaxHP+100</t>
+  </si>
+  <si>
+    <t>On LOSE, damage received -10%</t>
+  </si>
+  <si>
+    <t>ATK/DEF/SPD+25, MaxHP+125</t>
+  </si>
+  <si>
+    <t>On LOSE, damage received -13%</t>
+  </si>
+  <si>
+    <t>ATK+23, DEF+23</t>
+  </si>
+  <si>
+    <t>8% chance poison on a landed hit</t>
+  </si>
+  <si>
+    <t>ATK+30, DEF+30</t>
+  </si>
+  <si>
+    <t>10% chance poison on a landed hit</t>
+  </si>
+  <si>
+    <t>ATK+38, DEF+38</t>
+  </si>
+  <si>
+    <t>13% chance poison on a landed hit</t>
+  </si>
+  <si>
+    <t>SPD+23, MaxHP+113</t>
+  </si>
+  <si>
+    <t>8% chance reflect 50% damage</t>
+  </si>
+  <si>
+    <t>SPD+30, MaxHP+150</t>
+  </si>
+  <si>
+    <t>10% chance reflect 50% damage</t>
+  </si>
+  <si>
+    <t>SPD+38, MaxHP+188</t>
+  </si>
+  <si>
+    <t>13% chance reflect 50% damage</t>
+  </si>
+  <si>
+    <t>ATK+23, MaxHP+113</t>
+  </si>
+  <si>
+    <t>4% chance stun enemy</t>
+  </si>
+  <si>
+    <t>ATK+30, MaxHP+150</t>
+  </si>
+  <si>
+    <t>5% chance stun enemy</t>
+  </si>
+  <si>
+    <t>ATK+38, MaxHP+188</t>
+  </si>
+  <si>
+    <t>6% chance stun enemy</t>
+  </si>
+  <si>
+    <t>DEF+23, SPD+23</t>
+  </si>
+  <si>
+    <t>On WIN, damage dealt +8%</t>
+  </si>
+  <si>
+    <t>DEF+30, SPD+30</t>
+  </si>
+  <si>
+    <t>DEF+38, SPD+38</t>
+  </si>
+  <si>
+    <t>On WIN, damage dealt +13%</t>
+  </si>
+  <si>
+    <t>ATK+90</t>
+  </si>
+  <si>
+    <t>19% chance dmg dealt +75%</t>
+  </si>
+  <si>
+    <t>ATK+120</t>
+  </si>
+  <si>
+    <t>25% chance dmg dealt +75%</t>
+  </si>
+  <si>
+    <t>ATK+150</t>
+  </si>
+  <si>
+    <t>31% chance dmg dealt +75%</t>
+  </si>
+  <si>
+    <t>DEF+90</t>
+  </si>
+  <si>
+    <t>15% chance block (-50% dmg)</t>
+  </si>
+  <si>
+    <t>DEF+120</t>
+  </si>
+  <si>
+    <t>20% chance block (-50% dmg)</t>
+  </si>
+  <si>
+    <t>DEF+150</t>
+  </si>
+  <si>
+    <t>25% chance block (-50% dmg)</t>
+  </si>
+  <si>
+    <t>SPD+90</t>
+  </si>
+  <si>
+    <t>11% chance dodge</t>
+  </si>
+  <si>
+    <t>SPD+120</t>
+  </si>
+  <si>
+    <t>15% chance dodge</t>
+  </si>
+  <si>
+    <t>SPD+150</t>
+  </si>
+  <si>
+    <t>19% chance dodge</t>
+  </si>
+  <si>
+    <t>MaxHP+450</t>
+  </si>
+  <si>
+    <t>15% chance regen 5% Max HP</t>
+  </si>
+  <si>
+    <t>MaxHP+600</t>
+  </si>
+  <si>
+    <t>20% chance regen 5% Max HP</t>
+  </si>
+  <si>
+    <t>MaxHP+750</t>
+  </si>
+  <si>
+    <t>25% chance regen 5% Max HP</t>
+  </si>
+  <si>
+    <t>ATK+60, SPD+60</t>
+  </si>
+  <si>
+    <t>8% chance triple attack</t>
+  </si>
+  <si>
+    <t>ATK+80, SPD+80</t>
+  </si>
+  <si>
+    <t>10% chance triple attack</t>
+  </si>
+  <si>
+    <t>ATK+100, SPD+100</t>
+  </si>
+  <si>
+    <t>13% chance triple attack</t>
+  </si>
+  <si>
+    <t>DEF+60, MaxHP+300</t>
+  </si>
+  <si>
+    <t>15% chance counter (75% dmg)</t>
+  </si>
+  <si>
+    <t>DEF+80, MaxHP+400</t>
+  </si>
+  <si>
+    <t>20% chance counter (75% dmg)</t>
+  </si>
+  <si>
+    <t>DEF+100, MaxHP+500</t>
+  </si>
+  <si>
+    <t>25% chance counter (75% dmg)</t>
+  </si>
+  <si>
+    <t>ATK/DEF/SPD+38, MaxHP+225</t>
+  </si>
+  <si>
+    <t>On WIN, damage dealt +38%</t>
+  </si>
+  <si>
+    <t>ATK/DEF/SPD+50, MaxHP+300</t>
+  </si>
+  <si>
+    <t>ATK/DEF/SPD+63, MaxHP+375</t>
+  </si>
+  <si>
+    <t>On WIN, damage dealt +63%</t>
+  </si>
+  <si>
+    <t>fire_dragon_spear</t>
+  </si>
+  <si>
+    <t>ATK+60, DEF+60</t>
+  </si>
+  <si>
+    <t>11% chance to burn on a landed hit</t>
+  </si>
+  <si>
+    <t>ATK+80, DEF+80</t>
+  </si>
+  <si>
+    <t>ATK+100, DEF+100</t>
+  </si>
+  <si>
+    <t>19% chance to burn on a landed hit</t>
+  </si>
+  <si>
+    <t>SPD+60, MaxHP+300</t>
+  </si>
+  <si>
+    <t>15% chance to poison when attacked</t>
+  </si>
+  <si>
+    <t>SPD+80, MaxHP+400</t>
+  </si>
+  <si>
+    <t>SPD+100, MaxHP+500</t>
+  </si>
+  <si>
+    <t>25% chance to poison when attacked</t>
+  </si>
+  <si>
+    <t>ATK+60, MaxHP+300</t>
+  </si>
+  <si>
+    <t>8% chance stun enemy</t>
+  </si>
+  <si>
+    <t>ATK+80, MaxHP+400</t>
+  </si>
+  <si>
+    <t>10% chance stun enemy</t>
+  </si>
+  <si>
+    <t>ATK+100, MaxHP+500</t>
+  </si>
+  <si>
+    <t>13% chance stun enemy</t>
+  </si>
+  <si>
+    <t>DEF+60, SPD+60</t>
+  </si>
+  <si>
+    <t>Damage received -8%</t>
+  </si>
+  <si>
+    <t>DEF+80, SPD+80</t>
+  </si>
+  <si>
+    <t>Damage received -10%</t>
+  </si>
+  <si>
+    <t>DEF+100, SPD+100</t>
+  </si>
+  <si>
+    <t>Damage received -13%</t>
   </si>
 </sst>
 </file>
@@ -16091,6 +16500,1379 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{264581E1-9912-4314-81CC-4BBD6853D3D9}">
+  <dimension ref="A1:F71"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.69921875" customWidth="1"/>
+    <col min="2" max="2" width="16.69921875" customWidth="1"/>
+    <col min="3" max="3" width="20.69921875" customWidth="1"/>
+    <col min="4" max="4" width="8.69921875" customWidth="1"/>
+    <col min="5" max="5" width="28.69921875" customWidth="1"/>
+    <col min="6" max="6" width="38.69921875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>1991</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>1992</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>1993</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>263</v>
+      </c>
+      <c r="B5" t="s">
+        <v>264</v>
+      </c>
+      <c r="C5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" t="s">
+        <v>763</v>
+      </c>
+      <c r="E5" t="s">
+        <v>1994</v>
+      </c>
+      <c r="F5" t="s">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>327</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1100</v>
+      </c>
+      <c r="C6" t="s">
+        <v>1101</v>
+      </c>
+      <c r="D6" t="s">
+        <v>1996</v>
+      </c>
+      <c r="E6" t="s">
+        <v>1997</v>
+      </c>
+      <c r="F6" t="s">
+        <v>1998</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>327</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1100</v>
+      </c>
+      <c r="C7" t="s">
+        <v>1101</v>
+      </c>
+      <c r="D7" t="s">
+        <v>892</v>
+      </c>
+      <c r="E7" t="s">
+        <v>1999</v>
+      </c>
+      <c r="F7" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>327</v>
+      </c>
+      <c r="B8" t="s">
+        <v>1100</v>
+      </c>
+      <c r="C8" t="s">
+        <v>1101</v>
+      </c>
+      <c r="D8" t="s">
+        <v>2001</v>
+      </c>
+      <c r="E8" t="s">
+        <v>2002</v>
+      </c>
+      <c r="F8" t="s">
+        <v>2003</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>327</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C9" t="s">
+        <v>1107</v>
+      </c>
+      <c r="D9" t="s">
+        <v>1996</v>
+      </c>
+      <c r="E9" t="s">
+        <v>2004</v>
+      </c>
+      <c r="F9" t="s">
+        <v>2005</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>327</v>
+      </c>
+      <c r="B10" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C10" t="s">
+        <v>1107</v>
+      </c>
+      <c r="D10" t="s">
+        <v>892</v>
+      </c>
+      <c r="E10" t="s">
+        <v>2006</v>
+      </c>
+      <c r="F10" t="s">
+        <v>2007</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>327</v>
+      </c>
+      <c r="B11" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C11" t="s">
+        <v>1107</v>
+      </c>
+      <c r="D11" t="s">
+        <v>2001</v>
+      </c>
+      <c r="E11" t="s">
+        <v>2008</v>
+      </c>
+      <c r="F11" t="s">
+        <v>2009</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>327</v>
+      </c>
+      <c r="B12" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C12" t="s">
+        <v>1114</v>
+      </c>
+      <c r="D12" t="s">
+        <v>1996</v>
+      </c>
+      <c r="E12" t="s">
+        <v>2010</v>
+      </c>
+      <c r="F12" t="s">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>327</v>
+      </c>
+      <c r="B13" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C13" t="s">
+        <v>1114</v>
+      </c>
+      <c r="D13" t="s">
+        <v>892</v>
+      </c>
+      <c r="E13" t="s">
+        <v>2012</v>
+      </c>
+      <c r="F13" t="s">
+        <v>2013</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>327</v>
+      </c>
+      <c r="B14" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C14" t="s">
+        <v>1114</v>
+      </c>
+      <c r="D14" t="s">
+        <v>2001</v>
+      </c>
+      <c r="E14" t="s">
+        <v>2014</v>
+      </c>
+      <c r="F14" t="s">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>327</v>
+      </c>
+      <c r="B15" t="s">
+        <v>1120</v>
+      </c>
+      <c r="C15" t="s">
+        <v>1121</v>
+      </c>
+      <c r="D15" t="s">
+        <v>1996</v>
+      </c>
+      <c r="E15" t="s">
+        <v>2016</v>
+      </c>
+      <c r="F15" t="s">
+        <v>2017</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>327</v>
+      </c>
+      <c r="B16" t="s">
+        <v>1120</v>
+      </c>
+      <c r="C16" t="s">
+        <v>1121</v>
+      </c>
+      <c r="D16" t="s">
+        <v>892</v>
+      </c>
+      <c r="E16" t="s">
+        <v>2018</v>
+      </c>
+      <c r="F16" t="s">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>327</v>
+      </c>
+      <c r="B17" t="s">
+        <v>1120</v>
+      </c>
+      <c r="C17" t="s">
+        <v>1121</v>
+      </c>
+      <c r="D17" t="s">
+        <v>2001</v>
+      </c>
+      <c r="E17" t="s">
+        <v>2020</v>
+      </c>
+      <c r="F17" t="s">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>327</v>
+      </c>
+      <c r="B18" t="s">
+        <v>1127</v>
+      </c>
+      <c r="C18" t="s">
+        <v>1128</v>
+      </c>
+      <c r="D18" t="s">
+        <v>1996</v>
+      </c>
+      <c r="E18" t="s">
+        <v>2022</v>
+      </c>
+      <c r="F18" t="s">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>327</v>
+      </c>
+      <c r="B19" t="s">
+        <v>1127</v>
+      </c>
+      <c r="C19" t="s">
+        <v>1128</v>
+      </c>
+      <c r="D19" t="s">
+        <v>892</v>
+      </c>
+      <c r="E19" t="s">
+        <v>2024</v>
+      </c>
+      <c r="F19" t="s">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>327</v>
+      </c>
+      <c r="B20" t="s">
+        <v>1127</v>
+      </c>
+      <c r="C20" t="s">
+        <v>1128</v>
+      </c>
+      <c r="D20" t="s">
+        <v>2001</v>
+      </c>
+      <c r="E20" t="s">
+        <v>2026</v>
+      </c>
+      <c r="F20" t="s">
+        <v>2027</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>327</v>
+      </c>
+      <c r="B21" t="s">
+        <v>1133</v>
+      </c>
+      <c r="C21" t="s">
+        <v>1134</v>
+      </c>
+      <c r="D21" t="s">
+        <v>1996</v>
+      </c>
+      <c r="E21" t="s">
+        <v>2028</v>
+      </c>
+      <c r="F21" t="s">
+        <v>2029</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>327</v>
+      </c>
+      <c r="B22" t="s">
+        <v>1133</v>
+      </c>
+      <c r="C22" t="s">
+        <v>1134</v>
+      </c>
+      <c r="D22" t="s">
+        <v>892</v>
+      </c>
+      <c r="E22" t="s">
+        <v>2030</v>
+      </c>
+      <c r="F22" t="s">
+        <v>2031</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>327</v>
+      </c>
+      <c r="B23" t="s">
+        <v>1133</v>
+      </c>
+      <c r="C23" t="s">
+        <v>1134</v>
+      </c>
+      <c r="D23" t="s">
+        <v>2001</v>
+      </c>
+      <c r="E23" t="s">
+        <v>2032</v>
+      </c>
+      <c r="F23" t="s">
+        <v>2033</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>327</v>
+      </c>
+      <c r="B24" t="s">
+        <v>1140</v>
+      </c>
+      <c r="C24" t="s">
+        <v>1141</v>
+      </c>
+      <c r="D24" t="s">
+        <v>1996</v>
+      </c>
+      <c r="E24" t="s">
+        <v>2034</v>
+      </c>
+      <c r="F24" t="s">
+        <v>2035</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>327</v>
+      </c>
+      <c r="B25" t="s">
+        <v>1140</v>
+      </c>
+      <c r="C25" t="s">
+        <v>1141</v>
+      </c>
+      <c r="D25" t="s">
+        <v>892</v>
+      </c>
+      <c r="E25" t="s">
+        <v>2036</v>
+      </c>
+      <c r="F25" t="s">
+        <v>2037</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>327</v>
+      </c>
+      <c r="B26" t="s">
+        <v>1140</v>
+      </c>
+      <c r="C26" t="s">
+        <v>1141</v>
+      </c>
+      <c r="D26" t="s">
+        <v>2001</v>
+      </c>
+      <c r="E26" t="s">
+        <v>2038</v>
+      </c>
+      <c r="F26" t="s">
+        <v>2039</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>327</v>
+      </c>
+      <c r="B27" t="s">
+        <v>1147</v>
+      </c>
+      <c r="C27" t="s">
+        <v>1148</v>
+      </c>
+      <c r="D27" t="s">
+        <v>1996</v>
+      </c>
+      <c r="E27" t="s">
+        <v>2040</v>
+      </c>
+      <c r="F27" t="s">
+        <v>2041</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>327</v>
+      </c>
+      <c r="B28" t="s">
+        <v>1147</v>
+      </c>
+      <c r="C28" t="s">
+        <v>1148</v>
+      </c>
+      <c r="D28" t="s">
+        <v>892</v>
+      </c>
+      <c r="E28" t="s">
+        <v>2042</v>
+      </c>
+      <c r="F28" t="s">
+        <v>2043</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>327</v>
+      </c>
+      <c r="B29" t="s">
+        <v>1147</v>
+      </c>
+      <c r="C29" t="s">
+        <v>1148</v>
+      </c>
+      <c r="D29" t="s">
+        <v>2001</v>
+      </c>
+      <c r="E29" t="s">
+        <v>2044</v>
+      </c>
+      <c r="F29" t="s">
+        <v>2045</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>327</v>
+      </c>
+      <c r="B30" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C30" t="s">
+        <v>1154</v>
+      </c>
+      <c r="D30" t="s">
+        <v>1996</v>
+      </c>
+      <c r="E30" t="s">
+        <v>2046</v>
+      </c>
+      <c r="F30" t="s">
+        <v>2047</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>327</v>
+      </c>
+      <c r="B31" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C31" t="s">
+        <v>1154</v>
+      </c>
+      <c r="D31" t="s">
+        <v>892</v>
+      </c>
+      <c r="E31" t="s">
+        <v>2048</v>
+      </c>
+      <c r="F31" t="s">
+        <v>2049</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>327</v>
+      </c>
+      <c r="B32" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C32" t="s">
+        <v>1154</v>
+      </c>
+      <c r="D32" t="s">
+        <v>2001</v>
+      </c>
+      <c r="E32" t="s">
+        <v>2050</v>
+      </c>
+      <c r="F32" t="s">
+        <v>2051</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>327</v>
+      </c>
+      <c r="B33" t="s">
+        <v>1160</v>
+      </c>
+      <c r="C33" t="s">
+        <v>1161</v>
+      </c>
+      <c r="D33" t="s">
+        <v>1996</v>
+      </c>
+      <c r="E33" t="s">
+        <v>2052</v>
+      </c>
+      <c r="F33" t="s">
+        <v>2053</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>327</v>
+      </c>
+      <c r="B34" t="s">
+        <v>1160</v>
+      </c>
+      <c r="C34" t="s">
+        <v>1161</v>
+      </c>
+      <c r="D34" t="s">
+        <v>892</v>
+      </c>
+      <c r="E34" t="s">
+        <v>2054</v>
+      </c>
+      <c r="F34" t="s">
+        <v>2055</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>327</v>
+      </c>
+      <c r="B35" t="s">
+        <v>1160</v>
+      </c>
+      <c r="C35" t="s">
+        <v>1161</v>
+      </c>
+      <c r="D35" t="s">
+        <v>2001</v>
+      </c>
+      <c r="E35" t="s">
+        <v>2056</v>
+      </c>
+      <c r="F35" t="s">
+        <v>2057</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>327</v>
+      </c>
+      <c r="B36" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C36" t="s">
+        <v>1168</v>
+      </c>
+      <c r="D36" t="s">
+        <v>1996</v>
+      </c>
+      <c r="E36" t="s">
+        <v>2058</v>
+      </c>
+      <c r="F36" t="s">
+        <v>2059</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>327</v>
+      </c>
+      <c r="B37" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C37" t="s">
+        <v>1168</v>
+      </c>
+      <c r="D37" t="s">
+        <v>892</v>
+      </c>
+      <c r="E37" t="s">
+        <v>2060</v>
+      </c>
+      <c r="F37" t="s">
+        <v>1171</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>327</v>
+      </c>
+      <c r="B38" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C38" t="s">
+        <v>1168</v>
+      </c>
+      <c r="D38" t="s">
+        <v>2001</v>
+      </c>
+      <c r="E38" t="s">
+        <v>2061</v>
+      </c>
+      <c r="F38" t="s">
+        <v>2062</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>410</v>
+      </c>
+      <c r="B39" t="s">
+        <v>1174</v>
+      </c>
+      <c r="C39" t="s">
+        <v>1175</v>
+      </c>
+      <c r="D39" t="s">
+        <v>1996</v>
+      </c>
+      <c r="E39" t="s">
+        <v>2063</v>
+      </c>
+      <c r="F39" t="s">
+        <v>2064</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>410</v>
+      </c>
+      <c r="B40" t="s">
+        <v>1174</v>
+      </c>
+      <c r="C40" t="s">
+        <v>1175</v>
+      </c>
+      <c r="D40" t="s">
+        <v>892</v>
+      </c>
+      <c r="E40" t="s">
+        <v>2065</v>
+      </c>
+      <c r="F40" t="s">
+        <v>2066</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>410</v>
+      </c>
+      <c r="B41" t="s">
+        <v>1174</v>
+      </c>
+      <c r="C41" t="s">
+        <v>1175</v>
+      </c>
+      <c r="D41" t="s">
+        <v>2001</v>
+      </c>
+      <c r="E41" t="s">
+        <v>2067</v>
+      </c>
+      <c r="F41" t="s">
+        <v>2068</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>410</v>
+      </c>
+      <c r="B42" t="s">
+        <v>1181</v>
+      </c>
+      <c r="C42" t="s">
+        <v>1182</v>
+      </c>
+      <c r="D42" t="s">
+        <v>1996</v>
+      </c>
+      <c r="E42" t="s">
+        <v>2069</v>
+      </c>
+      <c r="F42" t="s">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>410</v>
+      </c>
+      <c r="B43" t="s">
+        <v>1181</v>
+      </c>
+      <c r="C43" t="s">
+        <v>1182</v>
+      </c>
+      <c r="D43" t="s">
+        <v>892</v>
+      </c>
+      <c r="E43" t="s">
+        <v>2071</v>
+      </c>
+      <c r="F43" t="s">
+        <v>2072</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>410</v>
+      </c>
+      <c r="B44" t="s">
+        <v>1181</v>
+      </c>
+      <c r="C44" t="s">
+        <v>1182</v>
+      </c>
+      <c r="D44" t="s">
+        <v>2001</v>
+      </c>
+      <c r="E44" t="s">
+        <v>2073</v>
+      </c>
+      <c r="F44" t="s">
+        <v>2074</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>410</v>
+      </c>
+      <c r="B45" t="s">
+        <v>1187</v>
+      </c>
+      <c r="C45" t="s">
+        <v>1188</v>
+      </c>
+      <c r="D45" t="s">
+        <v>1996</v>
+      </c>
+      <c r="E45" t="s">
+        <v>2075</v>
+      </c>
+      <c r="F45" t="s">
+        <v>2076</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>410</v>
+      </c>
+      <c r="B46" t="s">
+        <v>1187</v>
+      </c>
+      <c r="C46" t="s">
+        <v>1188</v>
+      </c>
+      <c r="D46" t="s">
+        <v>892</v>
+      </c>
+      <c r="E46" t="s">
+        <v>2077</v>
+      </c>
+      <c r="F46" t="s">
+        <v>2078</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>410</v>
+      </c>
+      <c r="B47" t="s">
+        <v>1187</v>
+      </c>
+      <c r="C47" t="s">
+        <v>1188</v>
+      </c>
+      <c r="D47" t="s">
+        <v>2001</v>
+      </c>
+      <c r="E47" t="s">
+        <v>2079</v>
+      </c>
+      <c r="F47" t="s">
+        <v>2080</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>410</v>
+      </c>
+      <c r="B48" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C48" t="s">
+        <v>1194</v>
+      </c>
+      <c r="D48" t="s">
+        <v>1996</v>
+      </c>
+      <c r="E48" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F48" t="s">
+        <v>2082</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>410</v>
+      </c>
+      <c r="B49" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C49" t="s">
+        <v>1194</v>
+      </c>
+      <c r="D49" t="s">
+        <v>892</v>
+      </c>
+      <c r="E49" t="s">
+        <v>2083</v>
+      </c>
+      <c r="F49" t="s">
+        <v>2084</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>410</v>
+      </c>
+      <c r="B50" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C50" t="s">
+        <v>1194</v>
+      </c>
+      <c r="D50" t="s">
+        <v>2001</v>
+      </c>
+      <c r="E50" t="s">
+        <v>2085</v>
+      </c>
+      <c r="F50" t="s">
+        <v>2086</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>410</v>
+      </c>
+      <c r="B51" t="s">
+        <v>1200</v>
+      </c>
+      <c r="C51" t="s">
+        <v>1201</v>
+      </c>
+      <c r="D51" t="s">
+        <v>1996</v>
+      </c>
+      <c r="E51" t="s">
+        <v>2087</v>
+      </c>
+      <c r="F51" t="s">
+        <v>2088</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>410</v>
+      </c>
+      <c r="B52" t="s">
+        <v>1200</v>
+      </c>
+      <c r="C52" t="s">
+        <v>1201</v>
+      </c>
+      <c r="D52" t="s">
+        <v>892</v>
+      </c>
+      <c r="E52" t="s">
+        <v>2089</v>
+      </c>
+      <c r="F52" t="s">
+        <v>2090</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>410</v>
+      </c>
+      <c r="B53" t="s">
+        <v>1200</v>
+      </c>
+      <c r="C53" t="s">
+        <v>1201</v>
+      </c>
+      <c r="D53" t="s">
+        <v>2001</v>
+      </c>
+      <c r="E53" t="s">
+        <v>2091</v>
+      </c>
+      <c r="F53" t="s">
+        <v>2092</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>410</v>
+      </c>
+      <c r="B54" t="s">
+        <v>1207</v>
+      </c>
+      <c r="C54" t="s">
+        <v>1208</v>
+      </c>
+      <c r="D54" t="s">
+        <v>1996</v>
+      </c>
+      <c r="E54" t="s">
+        <v>2093</v>
+      </c>
+      <c r="F54" t="s">
+        <v>2094</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>410</v>
+      </c>
+      <c r="B55" t="s">
+        <v>1207</v>
+      </c>
+      <c r="C55" t="s">
+        <v>1208</v>
+      </c>
+      <c r="D55" t="s">
+        <v>892</v>
+      </c>
+      <c r="E55" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F55" t="s">
+        <v>2096</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>410</v>
+      </c>
+      <c r="B56" t="s">
+        <v>1207</v>
+      </c>
+      <c r="C56" t="s">
+        <v>1208</v>
+      </c>
+      <c r="D56" t="s">
+        <v>2001</v>
+      </c>
+      <c r="E56" t="s">
+        <v>2097</v>
+      </c>
+      <c r="F56" t="s">
+        <v>2098</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>410</v>
+      </c>
+      <c r="B57" t="s">
+        <v>1214</v>
+      </c>
+      <c r="C57" t="s">
+        <v>1215</v>
+      </c>
+      <c r="D57" t="s">
+        <v>1996</v>
+      </c>
+      <c r="E57" t="s">
+        <v>2099</v>
+      </c>
+      <c r="F57" t="s">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>410</v>
+      </c>
+      <c r="B58" t="s">
+        <v>1214</v>
+      </c>
+      <c r="C58" t="s">
+        <v>1215</v>
+      </c>
+      <c r="D58" t="s">
+        <v>892</v>
+      </c>
+      <c r="E58" t="s">
+        <v>2101</v>
+      </c>
+      <c r="F58" t="s">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>410</v>
+      </c>
+      <c r="B59" t="s">
+        <v>1214</v>
+      </c>
+      <c r="C59" t="s">
+        <v>1215</v>
+      </c>
+      <c r="D59" t="s">
+        <v>2001</v>
+      </c>
+      <c r="E59" t="s">
+        <v>2102</v>
+      </c>
+      <c r="F59" t="s">
+        <v>2103</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>410</v>
+      </c>
+      <c r="B60" t="s">
+        <v>2104</v>
+      </c>
+      <c r="C60" t="s">
+        <v>1652</v>
+      </c>
+      <c r="D60" t="s">
+        <v>1996</v>
+      </c>
+      <c r="E60" t="s">
+        <v>2105</v>
+      </c>
+      <c r="F60" t="s">
+        <v>2106</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>410</v>
+      </c>
+      <c r="B61" t="s">
+        <v>2104</v>
+      </c>
+      <c r="C61" t="s">
+        <v>1652</v>
+      </c>
+      <c r="D61" t="s">
+        <v>892</v>
+      </c>
+      <c r="E61" t="s">
+        <v>2107</v>
+      </c>
+      <c r="F61" t="s">
+        <v>1654</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>410</v>
+      </c>
+      <c r="B62" t="s">
+        <v>2104</v>
+      </c>
+      <c r="C62" t="s">
+        <v>1652</v>
+      </c>
+      <c r="D62" t="s">
+        <v>2001</v>
+      </c>
+      <c r="E62" t="s">
+        <v>2108</v>
+      </c>
+      <c r="F62" t="s">
+        <v>2109</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>410</v>
+      </c>
+      <c r="B63" t="s">
+        <v>1224</v>
+      </c>
+      <c r="C63" t="s">
+        <v>1225</v>
+      </c>
+      <c r="D63" t="s">
+        <v>1996</v>
+      </c>
+      <c r="E63" t="s">
+        <v>2110</v>
+      </c>
+      <c r="F63" t="s">
+        <v>2111</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>410</v>
+      </c>
+      <c r="B64" t="s">
+        <v>1224</v>
+      </c>
+      <c r="C64" t="s">
+        <v>1225</v>
+      </c>
+      <c r="D64" t="s">
+        <v>892</v>
+      </c>
+      <c r="E64" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F64" t="s">
+        <v>1229</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>410</v>
+      </c>
+      <c r="B65" t="s">
+        <v>1224</v>
+      </c>
+      <c r="C65" t="s">
+        <v>1225</v>
+      </c>
+      <c r="D65" t="s">
+        <v>2001</v>
+      </c>
+      <c r="E65" t="s">
+        <v>2113</v>
+      </c>
+      <c r="F65" t="s">
+        <v>2114</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>410</v>
+      </c>
+      <c r="B66" t="s">
+        <v>1232</v>
+      </c>
+      <c r="C66" t="s">
+        <v>1233</v>
+      </c>
+      <c r="D66" t="s">
+        <v>1996</v>
+      </c>
+      <c r="E66" t="s">
+        <v>2115</v>
+      </c>
+      <c r="F66" t="s">
+        <v>2116</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>410</v>
+      </c>
+      <c r="B67" t="s">
+        <v>1232</v>
+      </c>
+      <c r="C67" t="s">
+        <v>1233</v>
+      </c>
+      <c r="D67" t="s">
+        <v>892</v>
+      </c>
+      <c r="E67" t="s">
+        <v>2117</v>
+      </c>
+      <c r="F67" t="s">
+        <v>2118</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>410</v>
+      </c>
+      <c r="B68" t="s">
+        <v>1232</v>
+      </c>
+      <c r="C68" t="s">
+        <v>1233</v>
+      </c>
+      <c r="D68" t="s">
+        <v>2001</v>
+      </c>
+      <c r="E68" t="s">
+        <v>2119</v>
+      </c>
+      <c r="F68" t="s">
+        <v>2120</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>410</v>
+      </c>
+      <c r="B69" t="s">
+        <v>1240</v>
+      </c>
+      <c r="C69" t="s">
+        <v>1241</v>
+      </c>
+      <c r="D69" t="s">
+        <v>1996</v>
+      </c>
+      <c r="E69" t="s">
+        <v>2121</v>
+      </c>
+      <c r="F69" t="s">
+        <v>2122</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>410</v>
+      </c>
+      <c r="B70" t="s">
+        <v>1240</v>
+      </c>
+      <c r="C70" t="s">
+        <v>1241</v>
+      </c>
+      <c r="D70" t="s">
+        <v>892</v>
+      </c>
+      <c r="E70" t="s">
+        <v>2123</v>
+      </c>
+      <c r="F70" t="s">
+        <v>2124</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>410</v>
+      </c>
+      <c r="B71" t="s">
+        <v>1240</v>
+      </c>
+      <c r="C71" t="s">
+        <v>1241</v>
+      </c>
+      <c r="D71" t="s">
+        <v>2001</v>
+      </c>
+      <c r="E71" t="s">
+        <v>2125</v>
+      </c>
+      <c r="F71" t="s">
+        <v>2126</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:L44"/>
@@ -17878,6 +19660,12 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="B29:B31"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="A8:A10"/>
+    <mergeCell ref="A26:A28"/>
+    <mergeCell ref="A17:A19"/>
+    <mergeCell ref="A20:A22"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A5:A7"/>
     <mergeCell ref="A23:A25"/>
@@ -17894,12 +19682,6 @@
     <mergeCell ref="B17:B19"/>
     <mergeCell ref="B23:B25"/>
     <mergeCell ref="A29:A31"/>
-    <mergeCell ref="B29:B31"/>
-    <mergeCell ref="B14:B16"/>
-    <mergeCell ref="A8:A10"/>
-    <mergeCell ref="A26:A28"/>
-    <mergeCell ref="A17:A19"/>
-    <mergeCell ref="A20:A22"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <ignoredErrors>

--- a/SYMBEAST_Evolve_Forms.xlsx
+++ b/SYMBEAST_Evolve_Forms.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\skyit\Desktop\Symbeast-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B108191-F671-49A6-8113-83BAD93AB664}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34B510CA-2E55-47F7-A5AD-9F249BF4CEA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="11" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3608" uniqueCount="2127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3862" uniqueCount="2317">
   <si>
     <t>SYMBEAST — Evolved Forms (Stage 1, 10 forms)</t>
   </si>
@@ -6417,6 +6417,576 @@
   </si>
   <si>
     <t>Damage received -13%</t>
+  </si>
+  <si>
+    <t>GHOST</t>
+  </si>
+  <si>
+    <t>🌟</t>
+  </si>
+  <si>
+    <t>เมื่อเริ่มต่อสู้ สุ่มได้รับ 1 บัฟ: ATK+25%, โอกาสหลบ +25% หรือ DEF+25% (ตลอดการต่อสู้)</t>
+  </si>
+  <si>
+    <t>RAGEBEAR-GHOST</t>
+  </si>
+  <si>
+    <t>โจมตี x1.75 เมื่อศัตรูมี HP &gt; 70%</t>
+  </si>
+  <si>
+    <t>BEAR RAGE</t>
+  </si>
+  <si>
+    <t>โจมตี x4.0 + สตันเทิร์นนี้ จากนั้น ATK+30% และ Crit+25% นาน 3 เทิร์น</t>
+  </si>
+  <si>
+    <t>LION-GHOST</t>
+  </si>
+  <si>
+    <t>โจมตี 3 เทิร์นแรกใส่ศัตรูแต่ละตัวติดคริติคอลแน่นอน และลด ATK ศัตรู 10% ตลอดการต่อสู้</t>
+  </si>
+  <si>
+    <t>KING'S ROAR</t>
+  </si>
+  <si>
+    <t>โจมตี x3.5 จากนั้น ATK+40% และศัตรู DEF-20% นาน 3 เทิร์น</t>
+  </si>
+  <si>
+    <t>TIGER-GHOST</t>
+  </si>
+  <si>
+    <t>เมื่อ WIN ดาเมจ+50% เมื่อ LOSE SPD+100% ในรอบถัดไป</t>
+  </si>
+  <si>
+    <t>TIGER CLAW</t>
+  </si>
+  <si>
+    <t>โจมตี x4.0 ทะลุ DEF + คริติคอลแน่นอนเป็นเวลา 3 เทิร์น</t>
+  </si>
+  <si>
+    <t>WOLF-GHOST</t>
+  </si>
+  <si>
+    <t>โอกาสโจมตี 2 ครั้ง 25% เพิ่มเป็น 35% เมื่อ HP&lt;50%</t>
+  </si>
+  <si>
+    <t>WOLF FANG</t>
+  </si>
+  <si>
+    <t>โจมตี 2 ครั้ง x2.5 จากนั้นโอกาสโจมตี 2 ครั้ง +50% นาน 3 เทิร์น</t>
+  </si>
+  <si>
+    <t>SHARK-GHOST</t>
+  </si>
+  <si>
+    <t>ดาเมจ+30% ดูดเลือด 30% ใส่ศัตรูที่ HP&lt;50%</t>
+  </si>
+  <si>
+    <t>SHARK BITE</t>
+  </si>
+  <si>
+    <t>โจมตี x4.0 หากศัตรู HP&lt;50% หรือ x2.5 หาก HP&gt;50% จากนั้นดูดเลือด 25% นาน 3 เทิร์น</t>
+  </si>
+  <si>
+    <t>MANTIS-GHOST</t>
+  </si>
+  <si>
+    <t>ความแรงของดาเมจคริติคอล x2.0 แทน x1.6 และเมื่อ HP&lt;20% ดาเมจที่ทำได้ +50%</t>
+  </si>
+  <si>
+    <t>MANTIS SLASH</t>
+  </si>
+  <si>
+    <t>โจมตี x3.5 (คริบังคับ) + DEF ศัตรู -50% นาน 3 เทิร์น</t>
+  </si>
+  <si>
+    <t>BEE-GHOST</t>
+  </si>
+  <si>
+    <t>โอกาส 15% โจมตี 3 ครั้ง เมื่อสำเร็จมีโอกาสทำให้ศัตรูติดพิษ 50%</t>
+  </si>
+  <si>
+    <t>BEE SWARM</t>
+  </si>
+  <si>
+    <t>โจมตี 4 ครั้ง x1.5 จากนั้นหลบ+25% นาน 3 เทิร์น</t>
+  </si>
+  <si>
+    <t>BUNNY-GHOST</t>
+  </si>
+  <si>
+    <t>หลบ 20% เมื่อหลบสำเร็จ ATK+50% รอบถัดไป</t>
+  </si>
+  <si>
+    <t>BUNNY HOP</t>
+  </si>
+  <si>
+    <t>โจมตี x3.0 + หลบสมบูรณ์เทิร์นนี้ จากนั้นหลบ+35% และมีโอกาส 50% ทำให้ศัตรูติดสถานะตาบอด (โจมตีพลาด 50%) นาน 3 เทิร์น</t>
+  </si>
+  <si>
+    <t>TRICKFOX-GHOST</t>
+  </si>
+  <si>
+    <t>โอกาส 50% ทำให้ศัตรูติดสถานะเผาไหม้ เป็นเวลา 3 เทิร์น</t>
+  </si>
+  <si>
+    <t>FOX TRICK</t>
+  </si>
+  <si>
+    <t>โจมตี x3.0 + ทำให้ศัตรูติดสถานะฟื้นฟู HP ไม่ได้ 3 เทิร์น จากนั้นหลบ+25% นาน 3 เทิร์น</t>
+  </si>
+  <si>
+    <t>OWL-GHOST</t>
+  </si>
+  <si>
+    <t>โจมตีไม่พลาดเป้า และมีโอกาส 15% ทำให้ศัตรูติดสถานะตาบอด (โจมตีพลาด 50% เป็นเวลา 3 เทิร์น)</t>
+  </si>
+  <si>
+    <t>OWL SIGHT</t>
+  </si>
+  <si>
+    <t>โจมตี x3.0 (ติดคริติคอล) + จากนั้น ATK/SPD+25% นาน 3 เทิร์น</t>
+  </si>
+  <si>
+    <t>VOLTMOUSE-GHOST</t>
+  </si>
+  <si>
+    <t>ทุกเทิร์นมีโอกาสสุ่ม ทำให้ศัตรูสตัน, ลด ATK 50%, ลด DEF 50%, เพิ่ม ATK 25%(ให้ศัตรู)</t>
+  </si>
+  <si>
+    <t>THUNDER SHOCK</t>
+  </si>
+  <si>
+    <t>โจมตี x3.0 + สตันเทิร์นนี้ จากนั้น SPDx2.0 และโอกาสสตัน+30% นาน 3 เทิร์น</t>
+  </si>
+  <si>
+    <t>PENGUIN-GHOST</t>
+  </si>
+  <si>
+    <t>ลดดาเมจ 15% เมื่อ HP&lt;50% หลบ+25% ATK+25%</t>
+  </si>
+  <si>
+    <t>ICE SLIDE</t>
+  </si>
+  <si>
+    <t>โจมตี x3.5 + หลบสมบูรณ์เทิร์นนี้ + DEF+50% นาน 3 เทิร์น</t>
+  </si>
+  <si>
+    <t>COCKROACH-GHOST</t>
+  </si>
+  <si>
+    <t>เมื่อถูกโจมตีถึงตายจะเหลือ HP 1 (1 ครั้ง/การต่อสู้) และ DEF/SPD+100% ตลอดการต่อสู้นั้น</t>
+  </si>
+  <si>
+    <t>ROACH SURVIVAL</t>
+  </si>
+  <si>
+    <t>รับดาเมจ 1 เทิร์นนี้ + ฟื้น HP 30% จากนั้นลดดาเมจ 25% และมีโอกาส 50% ทำให้ศัตรูติดสถานะตาบอด (โจมตีพลาด 50%) นาน 3 เทิร์น</t>
+  </si>
+  <si>
+    <t>SLIME-GHOST</t>
+  </si>
+  <si>
+    <t>ฟื้น HP 5% ทุกรอบ และเมื่อถูกโจมตีหรือโจมตีศัตรูมีโอกาส 25% ทำให้ศัตรูติดพิษ</t>
+  </si>
+  <si>
+    <t>SLIME ABSORB</t>
+  </si>
+  <si>
+    <t>ดูด HP ศัตรู 25% + ฟื้น HP 30% จากนั้นฟื้น 10% ต่อเทิร์น นาน 3 เทิร์น</t>
+  </si>
+  <si>
+    <t>LEAPFROG-GHOST</t>
+  </si>
+  <si>
+    <t>โอกาส 25% สะท้อนดาเมจ 50% และทำให้ศัตรูติดพิษ</t>
+  </si>
+  <si>
+    <t>FROG LEAP</t>
+  </si>
+  <si>
+    <t>โจมตี x2.5 + สะท้อนดาเมจ 100% เทิร์นนี้ จากนั้นสะท้อน 50% + ATK+25% นาน 3 เทิร์น</t>
+  </si>
+  <si>
+    <t>HAMSTER-GHOST</t>
+  </si>
+  <si>
+    <t>ทุก 3 เทิร์นฟื้น HP 20% และ DEF+50% ในรอบนั้น</t>
+  </si>
+  <si>
+    <t>HAMSTER STASH</t>
+  </si>
+  <si>
+    <t>รับดาเมจ 1 เทิร์นนี้ + ฟื้น HP 40% จากนั้น DEF+30% + ฟื้น 8% ต่อเทิร์น 3 เทิร์น</t>
+  </si>
+  <si>
+    <t>AXOLOTL-GHOST</t>
+  </si>
+  <si>
+    <t>เมื่อถูกโจมตีโอกาส 30% ฟื้น HP 15%</t>
+  </si>
+  <si>
+    <t>AXOLOTL REGEN</t>
+  </si>
+  <si>
+    <t>โจมตี x2.0 + ฟื้น HP 50% และล้างสถานะผิดปกติทั้งหมด จากนั้นฟื้น 12% ต่อเทิร์น นาน 3 เทิร์น</t>
+  </si>
+  <si>
+    <t>CAT-GHOST</t>
+  </si>
+  <si>
+    <t>หลบ 25% ถ้าโดนโจมตี รอบถัดไปจะ ATK+50%</t>
+  </si>
+  <si>
+    <t>CAT NINE LIVES</t>
+  </si>
+  <si>
+    <t>โจมตี x3.0 + หลบสมบูรณ์เทิร์นนี้ จากนั้นหลบ+30% + ATK+50% นาน 3 เทิร์น</t>
+  </si>
+  <si>
+    <t>DRAGON-GHOST</t>
+  </si>
+  <si>
+    <t>ATK/DEF/SPD +3% ทุกรอบ (สูงสุด 10 ครั้ง) และมีโอกาส 15% ทำให้ศัตรูติดสถานะเผาไหม้ เป็นเวลา 3 เทิร์น</t>
+  </si>
+  <si>
+    <t>DRAGON BREATH</t>
+  </si>
+  <si>
+    <t>โจมตี x3.5 + ทำให้ศัตรูติดสถานะเผาไหม้ จากนั้น ATK/DEF/SPD+20% นาน 3 เทิร์น</t>
+  </si>
+  <si>
+    <t>GRIFFON-GHOST</t>
+  </si>
+  <si>
+    <t>หลบ 15%, Crit Rate+15% เมื่อโจมตีติดคริติคอล จะทำให้ศัตรูติดสถานะฟื้นฟู HP ไม่ได้ 3 เทิร์น</t>
+  </si>
+  <si>
+    <t>GRIFFON DIVE</t>
+  </si>
+  <si>
+    <t>โจมตี x3.5 ทะลุ DEF + หลบเทิร์นนี้ จากนั้น ATK/SPD+30% นาน 3 เทิร์น</t>
+  </si>
+  <si>
+    <t>OCTOPUS-GHOST</t>
+  </si>
+  <si>
+    <t>โอกาส 30% ทำให้ศัตรูติดสถานะตาบอด (โจมตีพลาด 50% เป็นเวลา 3 เทิร์น)</t>
+  </si>
+  <si>
+    <t>OCTOPUS INK</t>
+  </si>
+  <si>
+    <t>โจมตี x2.5 + ศัตรูตาบอด (โจมตีพลาด 50%) 3 เทิร์น จากนั้น ATK+25% นาน 3 เทิร์น</t>
+  </si>
+  <si>
+    <t>PHOENIX-GHOST</t>
+  </si>
+  <si>
+    <t>เมื่อตายจะฟื้นคืนชีพด้วย HP 50% และทำให้ศัตรูติดสถานะเผาไหม้ 10 เทิร์น (1 ครั้ง/การต่อสู้)</t>
+  </si>
+  <si>
+    <t>PHOENIX REBIRTH</t>
+  </si>
+  <si>
+    <t>โจมตี x3.5 + ฟื้น HP 25% จากนั้น ATK/SPD+30% นาน 3 เทิร์น</t>
+  </si>
+  <si>
+    <t>UNICORN-GHOST</t>
+  </si>
+  <si>
+    <t>ฟื้น HP 8% ต่อเทิร์น ล้างดีบัฟ 1 อย่างต่อเทิร์น (Curse/No-Heal/Burn/Poison/Stun/Blind/Heal-Block — ครอบคลุมทุกประเภท)</t>
+  </si>
+  <si>
+    <t>UNICORN BLESS</t>
+  </si>
+  <si>
+    <t>โจมตี x3.0 + ฟื้น 40% + ล้างสถานะทั้งหมด จากนั้น ATK/SPD/DEF+20% + ฟื้น 10% ต่อเทิร์น 3 เทิร์น</t>
+  </si>
+  <si>
+    <t>PANDA-GHOST</t>
+  </si>
+  <si>
+    <t>Crit Rate+25% โอกาสสตัน 15% เมื่อโจมตี</t>
+  </si>
+  <si>
+    <t>PANDA STRIKE</t>
+  </si>
+  <si>
+    <t>โจมตี x4 (คริบังคับ) + สตัน จากนั้น Crit+30% + โอกาสสตัน+20% นาน 3 เทิร์น</t>
+  </si>
+  <si>
+    <t>RAGE ECHO</t>
+  </si>
+  <si>
+    <t>Damage +35% when enemy HP &gt; 70%</t>
+  </si>
+  <si>
+    <t>ดาเมจ +35% เมื่อศัตรูมี HP &gt; 70%</t>
+  </si>
+  <si>
+    <t>ROAR ECHO</t>
+  </si>
+  <si>
+    <t>First 3 turns: crit chance +50% and permanently reduce enemy ATK by 5%</t>
+  </si>
+  <si>
+    <t>3 เทิร์นแรก: โอกาสคริ +50% และลด ATK ศัตรู 5% ตลอดการต่อสู้</t>
+  </si>
+  <si>
+    <t>🐯</t>
+  </si>
+  <si>
+    <t>TIGER ECHO</t>
+  </si>
+  <si>
+    <t>On WIN: damage +25%; on LOSE: SPD+50% next round</t>
+  </si>
+  <si>
+    <t>เมื่อ WIN: ดาเมจ+25% เมื่อ LOSE: SPD+50% รอบถัดไป</t>
+  </si>
+  <si>
+    <t>WOLF ECHO</t>
+  </si>
+  <si>
+    <t>12% chance to attack twice (20% when HP&lt;50%)</t>
+  </si>
+  <si>
+    <t>โอกาส 12% โจมตี 2 ครั้ง (20% เมื่อ HP&lt;50%)</t>
+  </si>
+  <si>
+    <t>🦈</t>
+  </si>
+  <si>
+    <t>SHARK ECHO</t>
+  </si>
+  <si>
+    <t>+15% damage and 15% lifesteal vs enemies with HP&lt;50%</t>
+  </si>
+  <si>
+    <t>ดาเมจ+15% และดูดเลือด 15% ใส่ศัตรู HP&lt;50%</t>
+  </si>
+  <si>
+    <t>MANTIS ECHO</t>
+  </si>
+  <si>
+    <t>Crit damage x2. When HP&lt;20%: damage +25%</t>
+  </si>
+  <si>
+    <t>คริติคอลดาเมจ x2 เมื่อ HP&lt;20%: ดาเมจ+25%</t>
+  </si>
+  <si>
+    <t>🐝</t>
+  </si>
+  <si>
+    <t>SWARM ECHO</t>
+  </si>
+  <si>
+    <t>10% chance to attack 3 times; on success, 25% chance to poison enemy</t>
+  </si>
+  <si>
+    <t>โอกาส 10% โจมตี 3 ครั้ง เมื่อสำเร็จ โอกาส 25% ทำให้ศัตรูติดพิษ</t>
+  </si>
+  <si>
+    <t>🐰</t>
+  </si>
+  <si>
+    <t>BUNNY ECHO</t>
+  </si>
+  <si>
+    <t>10% dodge; on dodge: ATK+25% next round</t>
+  </si>
+  <si>
+    <t>หลบ 10% เมื่อหลบสำเร็จ ATK+25% รอบถัดไป</t>
+  </si>
+  <si>
+    <t>🎭</t>
+  </si>
+  <si>
+    <t>TRICK ECHO</t>
+  </si>
+  <si>
+    <t>25% chance to Burn the enemy for 3 turns</t>
+  </si>
+  <si>
+    <t>โอกาส 25% ทำให้ศัตรูติดสถานะเผาไหม้ 3 เทิร์น</t>
+  </si>
+  <si>
+    <t>👁️</t>
+  </si>
+  <si>
+    <t>OWL ECHO</t>
+  </si>
+  <si>
+    <t>Attacks never miss; 10% chance to Blind enemy on hit</t>
+  </si>
+  <si>
+    <t>โจมตีไม่พลาดเป้า โอกาส 10% ทำให้ศัตรูตาบอดเมื่อโจมตี</t>
+  </si>
+  <si>
+    <t>VOLT ECHO</t>
+  </si>
+  <si>
+    <t>Every turn: random effect — stun enemy, ATK-50%, DEF-50%, or give enemy ATK+25%</t>
+  </si>
+  <si>
+    <t>ทุกเทิร์นมีโอกาสสุ่ม ทำให้ศัตรูสตัน,ลด ATK 50%,ลด DEF 50%, เพิ่ม ATK 25%(ให้ศัตรู)</t>
+  </si>
+  <si>
+    <t>🐧</t>
+  </si>
+  <si>
+    <t>PENGUIN ECHO</t>
+  </si>
+  <si>
+    <t>Damage taken -10%; when HP&lt;50%: dodge+10% and ATK+15%</t>
+  </si>
+  <si>
+    <t>ลดดาเมจ 10% เมื่อ HP&lt;50%: หลบ+10% และ ATK+15%</t>
+  </si>
+  <si>
+    <t>🪳</t>
+  </si>
+  <si>
+    <t>ROACH ECHO</t>
+  </si>
+  <si>
+    <t>Survive a fatal blow with 1 HP (once), then DEF/SPD+50% for rest of battle</t>
+  </si>
+  <si>
+    <t>เหลือ HP 1 เมื่อถูกโจมตีถึงตาย (1 ครั้ง) จากนั้น DEF/SPD+50% ตลอดการต่อสู้</t>
+  </si>
+  <si>
+    <t>🟢</t>
+  </si>
+  <si>
+    <t>OOZE ECHO</t>
+  </si>
+  <si>
+    <t>Recover 3% HP/round; 15% chance to poison on attack or when hit</t>
+  </si>
+  <si>
+    <t>ฟื้น HP 3% ทุกรอบ โอกาส 15% ทำให้ศัตรูติดพิษเมื่อโจมตีหรือถูกโจมตี</t>
+  </si>
+  <si>
+    <t>💦</t>
+  </si>
+  <si>
+    <t>FROG ECHO</t>
+  </si>
+  <si>
+    <t>15% chance to reflect 25% damage and poison the enemy</t>
+  </si>
+  <si>
+    <t>โอกาส 15% สะท้อนดาเมจ 25% และทำให้ศัตรูติดพิษ</t>
+  </si>
+  <si>
+    <t>🐹</t>
+  </si>
+  <si>
+    <t>HAMSTER ECHO</t>
+  </si>
+  <si>
+    <t>Every 3 turns: recover 10% HP and DEF+25% that round</t>
+  </si>
+  <si>
+    <t>ทุก 3 เทิร์น: ฟื้น HP 10% และ DEF+25% ในรอบนั้น</t>
+  </si>
+  <si>
+    <t>🦎</t>
+  </si>
+  <si>
+    <t>AXOLOTL ECHO</t>
+  </si>
+  <si>
+    <t>15% chance to recover 8% HP when hit</t>
+  </si>
+  <si>
+    <t>โอกาส 15% ฟื้น HP 8% เมื่อถูกโจมตี</t>
+  </si>
+  <si>
+    <t>😼</t>
+  </si>
+  <si>
+    <t>CAT ECHO</t>
+  </si>
+  <si>
+    <t>15% dodge; if hit: ATK+25% next round</t>
+  </si>
+  <si>
+    <t>หลบ 15% ถ้าโดนโจมตี: ATK+25% รอบถัดไป</t>
+  </si>
+  <si>
+    <t>DRAGON ECHO</t>
+  </si>
+  <si>
+    <t>ATK/DEF/SPD +1.5%/round (max 10 stacks); 8% chance to Burn enemy</t>
+  </si>
+  <si>
+    <t>ATK/DEF/SPD +1.5% ต่อรอบ (สูงสุด 10 ครั้ง) โอกาส 8% เผาศัตรู</t>
+  </si>
+  <si>
+    <t>GRIFFON ECHO</t>
+  </si>
+  <si>
+    <t>10% dodge, 10% crit; on crit: enemy cannot heal for 3 turns</t>
+  </si>
+  <si>
+    <t>หลบ 10%, Crit+10% เมื่อคริ: ศัตรูฟื้นฟู HP ไม่ได้ 3 เทิร์น</t>
+  </si>
+  <si>
+    <t>🐙</t>
+  </si>
+  <si>
+    <t>OCTOPUS ECHO</t>
+  </si>
+  <si>
+    <t>15% chance to Blind enemy on hit (50% miss for 3 turns)</t>
+  </si>
+  <si>
+    <t>โอกาส 15% ทำให้ศัตรูตาบอด (โจมตีพลาด 50% 3 เทิร์น)</t>
+  </si>
+  <si>
+    <t>🔱</t>
+  </si>
+  <si>
+    <t>Once: revive with 25% HP, Burn enemy for 5 turns</t>
+  </si>
+  <si>
+    <t>ครั้งเดียว: ฟื้นคืนชีพด้วย HP 25% เผาศัตรู 5 เทิร์น</t>
+  </si>
+  <si>
+    <t>UNICORN ECHO</t>
+  </si>
+  <si>
+    <t>Recover 4% HP/turn; cleanse 1 debuff every turn (covers all debuff types)</t>
+  </si>
+  <si>
+    <t>ฟื้น HP 4% ต่อเทิร์น ล้างดีบัฟ 1 อย่างต่อเทิร์น (ครอบคลุมทุกประเภท)</t>
+  </si>
+  <si>
+    <t>PANDA ECHO</t>
+  </si>
+  <si>
+    <t>Crit+15%; 10% chance to stun on hit</t>
+  </si>
+  <si>
+    <t>Crit+15% โอกาสสตัน 10% เมื่อโจมตี</t>
+  </si>
+  <si>
+    <t>blind_gaze</t>
+  </si>
+  <si>
+    <t>BLIND GAZE</t>
+  </si>
+  <si>
+    <t>จ้องตาบอด</t>
+  </si>
+  <si>
+    <t>20% chance to blind you on a landed hit (50% miss chance for 3 turns)</t>
+  </si>
+  <si>
+    <t>20% โอกาสทำให้ผู้เล่นตาบอดเมื่อโจมตีโดน (โจมตีพลาด 50% นาน 3 เทิร์น)</t>
   </si>
 </sst>
 </file>
@@ -6795,7 +7365,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
@@ -7106,6 +7676,32 @@
       </c>
       <c r="H14" t="s">
         <v>48</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>2127</v>
+      </c>
+      <c r="B15" t="s">
+        <v>2128</v>
+      </c>
+      <c r="C15" t="s">
+        <v>2127</v>
+      </c>
+      <c r="D15">
+        <v>75</v>
+      </c>
+      <c r="E15">
+        <v>20</v>
+      </c>
+      <c r="F15">
+        <v>16</v>
+      </c>
+      <c r="G15">
+        <v>10</v>
+      </c>
+      <c r="H15" t="s">
+        <v>2129</v>
       </c>
     </row>
   </sheetData>
@@ -15774,7 +16370,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F00FD1CF-924F-4FD0-B28B-32154B63F96A}">
-  <dimension ref="A1:E45"/>
+  <dimension ref="A1:E69"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.69921875" customWidth="1"/>
@@ -16493,6 +17089,414 @@
       </c>
       <c r="E45" t="s">
         <v>1968</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>2130</v>
+      </c>
+      <c r="B46" t="s">
+        <v>1662</v>
+      </c>
+      <c r="C46" t="s">
+        <v>2226</v>
+      </c>
+      <c r="D46" t="s">
+        <v>2227</v>
+      </c>
+      <c r="E46" t="s">
+        <v>2228</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>2134</v>
+      </c>
+      <c r="B47" t="s">
+        <v>1807</v>
+      </c>
+      <c r="C47" t="s">
+        <v>2229</v>
+      </c>
+      <c r="D47" t="s">
+        <v>2230</v>
+      </c>
+      <c r="E47" t="s">
+        <v>2231</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>2138</v>
+      </c>
+      <c r="B48" t="s">
+        <v>2232</v>
+      </c>
+      <c r="C48" t="s">
+        <v>2233</v>
+      </c>
+      <c r="D48" t="s">
+        <v>2234</v>
+      </c>
+      <c r="E48" t="s">
+        <v>2235</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>2142</v>
+      </c>
+      <c r="B49" t="s">
+        <v>1773</v>
+      </c>
+      <c r="C49" t="s">
+        <v>2236</v>
+      </c>
+      <c r="D49" t="s">
+        <v>2237</v>
+      </c>
+      <c r="E49" t="s">
+        <v>2238</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>2146</v>
+      </c>
+      <c r="B50" t="s">
+        <v>2239</v>
+      </c>
+      <c r="C50" t="s">
+        <v>2240</v>
+      </c>
+      <c r="D50" t="s">
+        <v>2241</v>
+      </c>
+      <c r="E50" t="s">
+        <v>2242</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>2150</v>
+      </c>
+      <c r="B51" t="s">
+        <v>681</v>
+      </c>
+      <c r="C51" t="s">
+        <v>2243</v>
+      </c>
+      <c r="D51" t="s">
+        <v>2244</v>
+      </c>
+      <c r="E51" t="s">
+        <v>2245</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>2154</v>
+      </c>
+      <c r="B52" t="s">
+        <v>2246</v>
+      </c>
+      <c r="C52" t="s">
+        <v>2247</v>
+      </c>
+      <c r="D52" t="s">
+        <v>2248</v>
+      </c>
+      <c r="E52" t="s">
+        <v>2249</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>2158</v>
+      </c>
+      <c r="B53" t="s">
+        <v>2250</v>
+      </c>
+      <c r="C53" t="s">
+        <v>2251</v>
+      </c>
+      <c r="D53" t="s">
+        <v>2252</v>
+      </c>
+      <c r="E53" t="s">
+        <v>2253</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>2162</v>
+      </c>
+      <c r="B54" t="s">
+        <v>2254</v>
+      </c>
+      <c r="C54" t="s">
+        <v>2255</v>
+      </c>
+      <c r="D54" t="s">
+        <v>2256</v>
+      </c>
+      <c r="E54" t="s">
+        <v>2257</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>2166</v>
+      </c>
+      <c r="B55" t="s">
+        <v>2258</v>
+      </c>
+      <c r="C55" t="s">
+        <v>2259</v>
+      </c>
+      <c r="D55" t="s">
+        <v>2260</v>
+      </c>
+      <c r="E55" t="s">
+        <v>2261</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>2170</v>
+      </c>
+      <c r="B56" t="s">
+        <v>15</v>
+      </c>
+      <c r="C56" t="s">
+        <v>2262</v>
+      </c>
+      <c r="D56" t="s">
+        <v>2263</v>
+      </c>
+      <c r="E56" t="s">
+        <v>2264</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>2174</v>
+      </c>
+      <c r="B57" t="s">
+        <v>2265</v>
+      </c>
+      <c r="C57" t="s">
+        <v>2266</v>
+      </c>
+      <c r="D57" t="s">
+        <v>2267</v>
+      </c>
+      <c r="E57" t="s">
+        <v>2268</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>2178</v>
+      </c>
+      <c r="B58" t="s">
+        <v>2269</v>
+      </c>
+      <c r="C58" t="s">
+        <v>2270</v>
+      </c>
+      <c r="D58" t="s">
+        <v>2271</v>
+      </c>
+      <c r="E58" t="s">
+        <v>2272</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>2182</v>
+      </c>
+      <c r="B59" t="s">
+        <v>2273</v>
+      </c>
+      <c r="C59" t="s">
+        <v>2274</v>
+      </c>
+      <c r="D59" t="s">
+        <v>2275</v>
+      </c>
+      <c r="E59" t="s">
+        <v>2276</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>2186</v>
+      </c>
+      <c r="B60" t="s">
+        <v>2277</v>
+      </c>
+      <c r="C60" t="s">
+        <v>2278</v>
+      </c>
+      <c r="D60" t="s">
+        <v>2279</v>
+      </c>
+      <c r="E60" t="s">
+        <v>2280</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>2190</v>
+      </c>
+      <c r="B61" t="s">
+        <v>2281</v>
+      </c>
+      <c r="C61" t="s">
+        <v>2282</v>
+      </c>
+      <c r="D61" t="s">
+        <v>2283</v>
+      </c>
+      <c r="E61" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>2194</v>
+      </c>
+      <c r="B62" t="s">
+        <v>2285</v>
+      </c>
+      <c r="C62" t="s">
+        <v>2286</v>
+      </c>
+      <c r="D62" t="s">
+        <v>2287</v>
+      </c>
+      <c r="E62" t="s">
+        <v>2288</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>2198</v>
+      </c>
+      <c r="B63" t="s">
+        <v>2289</v>
+      </c>
+      <c r="C63" t="s">
+        <v>2290</v>
+      </c>
+      <c r="D63" t="s">
+        <v>2291</v>
+      </c>
+      <c r="E63" t="s">
+        <v>2292</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>2202</v>
+      </c>
+      <c r="B64" t="s">
+        <v>1701</v>
+      </c>
+      <c r="C64" t="s">
+        <v>2293</v>
+      </c>
+      <c r="D64" t="s">
+        <v>2294</v>
+      </c>
+      <c r="E64" t="s">
+        <v>2295</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>2206</v>
+      </c>
+      <c r="B65" t="s">
+        <v>1693</v>
+      </c>
+      <c r="C65" t="s">
+        <v>2296</v>
+      </c>
+      <c r="D65" t="s">
+        <v>2297</v>
+      </c>
+      <c r="E65" t="s">
+        <v>2298</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>2210</v>
+      </c>
+      <c r="B66" t="s">
+        <v>2299</v>
+      </c>
+      <c r="C66" t="s">
+        <v>2300</v>
+      </c>
+      <c r="D66" t="s">
+        <v>2301</v>
+      </c>
+      <c r="E66" t="s">
+        <v>2302</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>2214</v>
+      </c>
+      <c r="B67" t="s">
+        <v>2303</v>
+      </c>
+      <c r="C67" t="s">
+        <v>1937</v>
+      </c>
+      <c r="D67" t="s">
+        <v>2304</v>
+      </c>
+      <c r="E67" t="s">
+        <v>2305</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>2218</v>
+      </c>
+      <c r="B68" t="s">
+        <v>589</v>
+      </c>
+      <c r="C68" t="s">
+        <v>2306</v>
+      </c>
+      <c r="D68" t="s">
+        <v>2307</v>
+      </c>
+      <c r="E68" t="s">
+        <v>2308</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>2222</v>
+      </c>
+      <c r="B69" t="s">
+        <v>1861</v>
+      </c>
+      <c r="C69" t="s">
+        <v>2309</v>
+      </c>
+      <c r="D69" t="s">
+        <v>2310</v>
+      </c>
+      <c r="E69" t="s">
+        <v>2311</v>
       </c>
     </row>
   </sheetData>
@@ -17875,7 +18879,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:L44"/>
+  <dimension ref="A1:L68"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="46.69921875" bestFit="1" customWidth="1"/>
@@ -19178,6 +20182,711 @@
       </c>
       <c r="L44" t="s">
         <v>215</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>2127</v>
+      </c>
+      <c r="B45" t="s">
+        <v>2127</v>
+      </c>
+      <c r="C45" t="s">
+        <v>2129</v>
+      </c>
+      <c r="D45" t="s">
+        <v>58</v>
+      </c>
+      <c r="E45" t="s">
+        <v>2130</v>
+      </c>
+      <c r="F45">
+        <v>112</v>
+      </c>
+      <c r="G45">
+        <v>48</v>
+      </c>
+      <c r="H45">
+        <v>15</v>
+      </c>
+      <c r="I45">
+        <v>6</v>
+      </c>
+      <c r="J45" t="s">
+        <v>2131</v>
+      </c>
+      <c r="K45" t="s">
+        <v>2132</v>
+      </c>
+      <c r="L45" t="s">
+        <v>2133</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="D46" t="s">
+        <v>58</v>
+      </c>
+      <c r="E46" t="s">
+        <v>2134</v>
+      </c>
+      <c r="F46">
+        <v>108</v>
+      </c>
+      <c r="G46">
+        <v>52</v>
+      </c>
+      <c r="H46">
+        <v>16</v>
+      </c>
+      <c r="I46">
+        <v>5</v>
+      </c>
+      <c r="J46" t="s">
+        <v>2135</v>
+      </c>
+      <c r="K46" t="s">
+        <v>2136</v>
+      </c>
+      <c r="L46" t="s">
+        <v>2137</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="D47" t="s">
+        <v>58</v>
+      </c>
+      <c r="E47" t="s">
+        <v>2138</v>
+      </c>
+      <c r="F47">
+        <v>114</v>
+      </c>
+      <c r="G47">
+        <v>50</v>
+      </c>
+      <c r="H47">
+        <v>18</v>
+      </c>
+      <c r="I47">
+        <v>5</v>
+      </c>
+      <c r="J47" t="s">
+        <v>2139</v>
+      </c>
+      <c r="K47" t="s">
+        <v>2140</v>
+      </c>
+      <c r="L47" t="s">
+        <v>2141</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="D48" t="s">
+        <v>58</v>
+      </c>
+      <c r="E48" t="s">
+        <v>2142</v>
+      </c>
+      <c r="F48">
+        <v>106</v>
+      </c>
+      <c r="G48">
+        <v>46</v>
+      </c>
+      <c r="H48">
+        <v>20</v>
+      </c>
+      <c r="I48">
+        <v>6</v>
+      </c>
+      <c r="J48" t="s">
+        <v>2143</v>
+      </c>
+      <c r="K48" t="s">
+        <v>2144</v>
+      </c>
+      <c r="L48" t="s">
+        <v>2145</v>
+      </c>
+    </row>
+    <row r="49" spans="4:12" x14ac:dyDescent="0.3">
+      <c r="D49" t="s">
+        <v>58</v>
+      </c>
+      <c r="E49" t="s">
+        <v>2146</v>
+      </c>
+      <c r="F49">
+        <v>118</v>
+      </c>
+      <c r="G49">
+        <v>49</v>
+      </c>
+      <c r="H49">
+        <v>14</v>
+      </c>
+      <c r="I49">
+        <v>7</v>
+      </c>
+      <c r="J49" t="s">
+        <v>2147</v>
+      </c>
+      <c r="K49" t="s">
+        <v>2148</v>
+      </c>
+      <c r="L49" t="s">
+        <v>2149</v>
+      </c>
+    </row>
+    <row r="50" spans="4:12" x14ac:dyDescent="0.3">
+      <c r="D50" t="s">
+        <v>58</v>
+      </c>
+      <c r="E50" t="s">
+        <v>2150</v>
+      </c>
+      <c r="F50">
+        <v>102</v>
+      </c>
+      <c r="G50">
+        <v>54</v>
+      </c>
+      <c r="H50">
+        <v>17</v>
+      </c>
+      <c r="I50">
+        <v>4</v>
+      </c>
+      <c r="J50" t="s">
+        <v>2151</v>
+      </c>
+      <c r="K50" t="s">
+        <v>2152</v>
+      </c>
+      <c r="L50" t="s">
+        <v>2153</v>
+      </c>
+    </row>
+    <row r="51" spans="4:12" x14ac:dyDescent="0.3">
+      <c r="D51" t="s">
+        <v>63</v>
+      </c>
+      <c r="E51" t="s">
+        <v>2154</v>
+      </c>
+      <c r="F51">
+        <v>100</v>
+      </c>
+      <c r="G51">
+        <v>28</v>
+      </c>
+      <c r="H51">
+        <v>44</v>
+      </c>
+      <c r="I51">
+        <v>5</v>
+      </c>
+      <c r="J51" t="s">
+        <v>2155</v>
+      </c>
+      <c r="K51" t="s">
+        <v>2156</v>
+      </c>
+      <c r="L51" t="s">
+        <v>2157</v>
+      </c>
+    </row>
+    <row r="52" spans="4:12" x14ac:dyDescent="0.3">
+      <c r="D52" t="s">
+        <v>63</v>
+      </c>
+      <c r="E52" t="s">
+        <v>2158</v>
+      </c>
+      <c r="F52">
+        <v>96</v>
+      </c>
+      <c r="G52">
+        <v>24</v>
+      </c>
+      <c r="H52">
+        <v>48</v>
+      </c>
+      <c r="I52">
+        <v>4</v>
+      </c>
+      <c r="J52" t="s">
+        <v>2159</v>
+      </c>
+      <c r="K52" t="s">
+        <v>2160</v>
+      </c>
+      <c r="L52" t="s">
+        <v>2161</v>
+      </c>
+    </row>
+    <row r="53" spans="4:12" x14ac:dyDescent="0.3">
+      <c r="D53" t="s">
+        <v>63</v>
+      </c>
+      <c r="E53" t="s">
+        <v>2162</v>
+      </c>
+      <c r="F53">
+        <v>104</v>
+      </c>
+      <c r="G53">
+        <v>30</v>
+      </c>
+      <c r="H53">
+        <v>42</v>
+      </c>
+      <c r="I53">
+        <v>5</v>
+      </c>
+      <c r="J53" t="s">
+        <v>2163</v>
+      </c>
+      <c r="K53" t="s">
+        <v>2164</v>
+      </c>
+      <c r="L53" t="s">
+        <v>2165</v>
+      </c>
+    </row>
+    <row r="54" spans="4:12" x14ac:dyDescent="0.3">
+      <c r="D54" t="s">
+        <v>63</v>
+      </c>
+      <c r="E54" t="s">
+        <v>2166</v>
+      </c>
+      <c r="F54">
+        <v>108</v>
+      </c>
+      <c r="G54">
+        <v>26</v>
+      </c>
+      <c r="H54">
+        <v>40</v>
+      </c>
+      <c r="I54">
+        <v>6</v>
+      </c>
+      <c r="J54" t="s">
+        <v>2167</v>
+      </c>
+      <c r="K54" t="s">
+        <v>2168</v>
+      </c>
+      <c r="L54" t="s">
+        <v>2169</v>
+      </c>
+    </row>
+    <row r="55" spans="4:12" x14ac:dyDescent="0.3">
+      <c r="D55" t="s">
+        <v>63</v>
+      </c>
+      <c r="E55" t="s">
+        <v>2170</v>
+      </c>
+      <c r="F55">
+        <v>98</v>
+      </c>
+      <c r="G55">
+        <v>32</v>
+      </c>
+      <c r="H55">
+        <v>46</v>
+      </c>
+      <c r="I55">
+        <v>4</v>
+      </c>
+      <c r="J55" t="s">
+        <v>2171</v>
+      </c>
+      <c r="K55" t="s">
+        <v>2172</v>
+      </c>
+      <c r="L55" t="s">
+        <v>2173</v>
+      </c>
+    </row>
+    <row r="56" spans="4:12" x14ac:dyDescent="0.3">
+      <c r="D56" t="s">
+        <v>63</v>
+      </c>
+      <c r="E56" t="s">
+        <v>2174</v>
+      </c>
+      <c r="F56">
+        <v>112</v>
+      </c>
+      <c r="G56">
+        <v>22</v>
+      </c>
+      <c r="H56">
+        <v>38</v>
+      </c>
+      <c r="I56">
+        <v>8</v>
+      </c>
+      <c r="J56" t="s">
+        <v>2175</v>
+      </c>
+      <c r="K56" t="s">
+        <v>2176</v>
+      </c>
+      <c r="L56" t="s">
+        <v>2177</v>
+      </c>
+    </row>
+    <row r="57" spans="4:12" x14ac:dyDescent="0.3">
+      <c r="D57" t="s">
+        <v>72</v>
+      </c>
+      <c r="E57" t="s">
+        <v>2178</v>
+      </c>
+      <c r="F57">
+        <v>135</v>
+      </c>
+      <c r="G57">
+        <v>22</v>
+      </c>
+      <c r="H57">
+        <v>16</v>
+      </c>
+      <c r="I57">
+        <v>24</v>
+      </c>
+      <c r="J57" t="s">
+        <v>2179</v>
+      </c>
+      <c r="K57" t="s">
+        <v>2180</v>
+      </c>
+      <c r="L57" t="s">
+        <v>2181</v>
+      </c>
+    </row>
+    <row r="58" spans="4:12" x14ac:dyDescent="0.3">
+      <c r="D58" t="s">
+        <v>72</v>
+      </c>
+      <c r="E58" t="s">
+        <v>2182</v>
+      </c>
+      <c r="F58">
+        <v>145</v>
+      </c>
+      <c r="G58">
+        <v>18</v>
+      </c>
+      <c r="H58">
+        <v>13</v>
+      </c>
+      <c r="I58">
+        <v>22</v>
+      </c>
+      <c r="J58" t="s">
+        <v>2183</v>
+      </c>
+      <c r="K58" t="s">
+        <v>2184</v>
+      </c>
+      <c r="L58" t="s">
+        <v>2185</v>
+      </c>
+    </row>
+    <row r="59" spans="4:12" x14ac:dyDescent="0.3">
+      <c r="D59" t="s">
+        <v>72</v>
+      </c>
+      <c r="E59" t="s">
+        <v>2186</v>
+      </c>
+      <c r="F59">
+        <v>125</v>
+      </c>
+      <c r="G59">
+        <v>24</v>
+      </c>
+      <c r="H59">
+        <v>18</v>
+      </c>
+      <c r="I59">
+        <v>22</v>
+      </c>
+      <c r="J59" t="s">
+        <v>2187</v>
+      </c>
+      <c r="K59" t="s">
+        <v>2188</v>
+      </c>
+      <c r="L59" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="60" spans="4:12" x14ac:dyDescent="0.3">
+      <c r="D60" t="s">
+        <v>72</v>
+      </c>
+      <c r="E60" t="s">
+        <v>2190</v>
+      </c>
+      <c r="F60">
+        <v>128</v>
+      </c>
+      <c r="G60">
+        <v>20</v>
+      </c>
+      <c r="H60">
+        <v>15</v>
+      </c>
+      <c r="I60">
+        <v>24</v>
+      </c>
+      <c r="J60" t="s">
+        <v>2191</v>
+      </c>
+      <c r="K60" t="s">
+        <v>2192</v>
+      </c>
+      <c r="L60" t="s">
+        <v>2193</v>
+      </c>
+    </row>
+    <row r="61" spans="4:12" x14ac:dyDescent="0.3">
+      <c r="D61" t="s">
+        <v>72</v>
+      </c>
+      <c r="E61" t="s">
+        <v>2194</v>
+      </c>
+      <c r="F61">
+        <v>140</v>
+      </c>
+      <c r="G61">
+        <v>21</v>
+      </c>
+      <c r="H61">
+        <v>15</v>
+      </c>
+      <c r="I61">
+        <v>26</v>
+      </c>
+      <c r="J61" t="s">
+        <v>2195</v>
+      </c>
+      <c r="K61" t="s">
+        <v>2196</v>
+      </c>
+      <c r="L61" t="s">
+        <v>2197</v>
+      </c>
+    </row>
+    <row r="62" spans="4:12" x14ac:dyDescent="0.3">
+      <c r="D62" t="s">
+        <v>72</v>
+      </c>
+      <c r="E62" t="s">
+        <v>2198</v>
+      </c>
+      <c r="F62">
+        <v>118</v>
+      </c>
+      <c r="G62">
+        <v>26</v>
+      </c>
+      <c r="H62">
+        <v>22</v>
+      </c>
+      <c r="I62">
+        <v>18</v>
+      </c>
+      <c r="J62" t="s">
+        <v>2199</v>
+      </c>
+      <c r="K62" t="s">
+        <v>2200</v>
+      </c>
+      <c r="L62" t="s">
+        <v>2201</v>
+      </c>
+    </row>
+    <row r="63" spans="4:12" x14ac:dyDescent="0.3">
+      <c r="D63" t="s">
+        <v>68</v>
+      </c>
+      <c r="E63" t="s">
+        <v>2202</v>
+      </c>
+      <c r="F63">
+        <v>118</v>
+      </c>
+      <c r="G63">
+        <v>34</v>
+      </c>
+      <c r="H63">
+        <v>22</v>
+      </c>
+      <c r="I63">
+        <v>14</v>
+      </c>
+      <c r="J63" t="s">
+        <v>2203</v>
+      </c>
+      <c r="K63" t="s">
+        <v>2204</v>
+      </c>
+      <c r="L63" t="s">
+        <v>2205</v>
+      </c>
+    </row>
+    <row r="64" spans="4:12" x14ac:dyDescent="0.3">
+      <c r="D64" t="s">
+        <v>68</v>
+      </c>
+      <c r="E64" t="s">
+        <v>2206</v>
+      </c>
+      <c r="F64">
+        <v>112</v>
+      </c>
+      <c r="G64">
+        <v>36</v>
+      </c>
+      <c r="H64">
+        <v>24</v>
+      </c>
+      <c r="I64">
+        <v>12</v>
+      </c>
+      <c r="J64" t="s">
+        <v>2207</v>
+      </c>
+      <c r="K64" t="s">
+        <v>2208</v>
+      </c>
+      <c r="L64" t="s">
+        <v>2209</v>
+      </c>
+    </row>
+    <row r="65" spans="4:12" x14ac:dyDescent="0.3">
+      <c r="D65" t="s">
+        <v>68</v>
+      </c>
+      <c r="E65" t="s">
+        <v>2210</v>
+      </c>
+      <c r="F65">
+        <v>125</v>
+      </c>
+      <c r="G65">
+        <v>30</v>
+      </c>
+      <c r="H65">
+        <v>20</v>
+      </c>
+      <c r="I65">
+        <v>16</v>
+      </c>
+      <c r="J65" t="s">
+        <v>2211</v>
+      </c>
+      <c r="K65" t="s">
+        <v>2212</v>
+      </c>
+      <c r="L65" t="s">
+        <v>2213</v>
+      </c>
+    </row>
+    <row r="66" spans="4:12" x14ac:dyDescent="0.3">
+      <c r="D66" t="s">
+        <v>68</v>
+      </c>
+      <c r="E66" t="s">
+        <v>2214</v>
+      </c>
+      <c r="F66">
+        <v>108</v>
+      </c>
+      <c r="G66">
+        <v>35</v>
+      </c>
+      <c r="H66">
+        <v>26</v>
+      </c>
+      <c r="I66">
+        <v>10</v>
+      </c>
+      <c r="J66" t="s">
+        <v>2215</v>
+      </c>
+      <c r="K66" t="s">
+        <v>2216</v>
+      </c>
+      <c r="L66" t="s">
+        <v>2217</v>
+      </c>
+    </row>
+    <row r="67" spans="4:12" x14ac:dyDescent="0.3">
+      <c r="D67" t="s">
+        <v>68</v>
+      </c>
+      <c r="E67" t="s">
+        <v>2218</v>
+      </c>
+      <c r="F67">
+        <v>115</v>
+      </c>
+      <c r="G67">
+        <v>32</v>
+      </c>
+      <c r="H67">
+        <v>25</v>
+      </c>
+      <c r="I67">
+        <v>12</v>
+      </c>
+      <c r="J67" t="s">
+        <v>2219</v>
+      </c>
+      <c r="K67" t="s">
+        <v>2220</v>
+      </c>
+      <c r="L67" t="s">
+        <v>2221</v>
+      </c>
+    </row>
+    <row r="68" spans="4:12" x14ac:dyDescent="0.3">
+      <c r="D68" t="s">
+        <v>68</v>
+      </c>
+      <c r="E68" t="s">
+        <v>2222</v>
+      </c>
+      <c r="F68">
+        <v>120</v>
+      </c>
+      <c r="G68">
+        <v>33</v>
+      </c>
+      <c r="H68">
+        <v>18</v>
+      </c>
+      <c r="I68">
+        <v>15</v>
+      </c>
+      <c r="J68" t="s">
+        <v>2223</v>
+      </c>
+      <c r="K68" t="s">
+        <v>2224</v>
+      </c>
+      <c r="L68" t="s">
+        <v>2225</v>
       </c>
     </row>
   </sheetData>
@@ -19660,12 +21369,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="B29:B31"/>
-    <mergeCell ref="B14:B16"/>
-    <mergeCell ref="A8:A10"/>
-    <mergeCell ref="A26:A28"/>
-    <mergeCell ref="A17:A19"/>
-    <mergeCell ref="A20:A22"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A5:A7"/>
     <mergeCell ref="A23:A25"/>
@@ -19682,6 +21385,12 @@
     <mergeCell ref="B17:B19"/>
     <mergeCell ref="B23:B25"/>
     <mergeCell ref="A29:A31"/>
+    <mergeCell ref="B29:B31"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="A8:A10"/>
+    <mergeCell ref="A26:A28"/>
+    <mergeCell ref="A17:A19"/>
+    <mergeCell ref="A20:A22"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <ignoredErrors>
@@ -21274,7 +22983,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
@@ -21722,6 +23431,29 @@
       </c>
       <c r="G22" t="s">
         <v>760</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>701</v>
+      </c>
+      <c r="B23" t="s">
+        <v>2312</v>
+      </c>
+      <c r="C23" t="s">
+        <v>2258</v>
+      </c>
+      <c r="D23" t="s">
+        <v>2313</v>
+      </c>
+      <c r="E23" t="s">
+        <v>2314</v>
+      </c>
+      <c r="F23" t="s">
+        <v>2315</v>
+      </c>
+      <c r="G23" t="s">
+        <v>2316</v>
       </c>
     </row>
   </sheetData>

--- a/SYMBEAST_Evolve_Forms.xlsx
+++ b/SYMBEAST_Evolve_Forms.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\skyit\Desktop\Symbeast-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34B510CA-2E55-47F7-A5AD-9F249BF4CEA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCF1E4BF-3AA6-4C0B-9E7D-3BA55DF767B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="11" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3862" uniqueCount="2317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3869" uniqueCount="2322">
   <si>
     <t>SYMBEAST — Evolved Forms (Stage 1, 10 forms)</t>
   </si>
@@ -6987,6 +6987,21 @@
   </si>
   <si>
     <t>20% โอกาสทำให้ผู้เล่นตาบอดเมื่อโจมตีโดน (โจมตีพลาด 50% นาน 3 เทิร์น)</t>
+  </si>
+  <si>
+    <t>regen_cleanse</t>
+  </si>
+  <si>
+    <t>REGENERATION</t>
+  </si>
+  <si>
+    <t>ฟื้นฟู</t>
+  </si>
+  <si>
+    <t>Heals 3% MaxHP and cleanses its own debuffs every turn</t>
+  </si>
+  <si>
+    <t>ฟื้นฟู HP 3% และล้างดีบัพของตัวเองทุกเทิร์น</t>
   </si>
 </sst>
 </file>
@@ -21369,6 +21384,12 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="B29:B31"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="A8:A10"/>
+    <mergeCell ref="A26:A28"/>
+    <mergeCell ref="A17:A19"/>
+    <mergeCell ref="A20:A22"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A5:A7"/>
     <mergeCell ref="A23:A25"/>
@@ -21385,12 +21406,6 @@
     <mergeCell ref="B17:B19"/>
     <mergeCell ref="B23:B25"/>
     <mergeCell ref="A29:A31"/>
-    <mergeCell ref="B29:B31"/>
-    <mergeCell ref="B14:B16"/>
-    <mergeCell ref="A8:A10"/>
-    <mergeCell ref="A26:A28"/>
-    <mergeCell ref="A17:A19"/>
-    <mergeCell ref="A20:A22"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <ignoredErrors>
@@ -22983,7 +22998,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
@@ -23454,6 +23469,29 @@
       </c>
       <c r="G23" t="s">
         <v>2316</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>717</v>
+      </c>
+      <c r="B24" t="s">
+        <v>2317</v>
+      </c>
+      <c r="C24" t="s">
+        <v>486</v>
+      </c>
+      <c r="D24" t="s">
+        <v>2318</v>
+      </c>
+      <c r="E24" t="s">
+        <v>2319</v>
+      </c>
+      <c r="F24" t="s">
+        <v>2320</v>
+      </c>
+      <c r="G24" t="s">
+        <v>2321</v>
       </c>
     </row>
   </sheetData>

--- a/SYMBEAST_Evolve_Forms.xlsx
+++ b/SYMBEAST_Evolve_Forms.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="600" firstSheet="11" activeTab="15" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="600" firstSheet="1" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Evolved Forms" sheetId="1" state="visible" r:id="rId1"/>
@@ -13718,12 +13718,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Every 3 turns: dodges 50% and attacks through DEF with ATK +25%</t>
+          <t>Every 3 turns: dodges 50%, attacks through DEF with ATK +25%, 25% chance to freeze the enemy</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>ทุก 3 เทิร์น: หลบ 50% และโจมตีทะลุ DEF ด้วย ATK+25%</t>
+          <t>ทุก 3 เทิร์น: หลบ 50% โจมตีทะลุ DEF ด้วย ATK+25% และโอกาส 25% แช่แข็งศัตรู</t>
         </is>
       </c>
     </row>
@@ -13745,12 +13745,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Every 3 rounds: recovers 8% of Max HP and ATK/DEF +10% that round</t>
+          <t>Every 3 rounds: recovers 8% of Max HP and ATK/DEF +10% that round; 5% chance to freeze the enemy on hit</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>ทุก 3 รอบ: ฟื้น HP 8% ของ Max HP และ ATK/DEF+10% ในรอบนั้น</t>
+          <t>ทุก 3 รอบ: ฟื้น HP 8% ของ Max HP และ ATK/DEF+10% ในรอบนั้น; 5% โอกาสแช่แข็งศัตรูเมื่อโจมตี</t>
         </is>
       </c>
     </row>
@@ -18700,7 +18700,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>ทุก 3 เทิร์น จะหลบการโจมตีได้ 100% และโจมตีทะลุ DEF ด้วย ATK+50%</t>
+          <t>ทุก 3 เทิร์น จะหลบการโจมตีได้ 100% และโจมตีทะลุ DEF ด้วย ATK+50% และมีโอกาส 50% แช่แข็งศัตรู</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -18710,7 +18710,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>โจมตี ×3.0 ทะลุ DEF + หลบการโจมตีสมบูรณ์เทิร์นนี้ จากนั้น 3 เทิร์น: โอกาสหลบ +30%, โจมตีทะลุ DEF ต่อเนื่อง</t>
+          <t>โจมตี ×3.0 ทะลุ DEF + หลบการโจมตีเทิร์นนี้ จากนั้น 3 เทิร์น: โอกาสหลบ +30%, โจมตีทะลุ DEF, 50% แช่แข็งศัตรู</t>
         </is>
       </c>
     </row>
@@ -18739,7 +18739,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>ทุก 3 รอบ: ฟื้น HP 15% ของ Max HP และ ATK/DEF+20% ในรอบนั้น</t>
+          <t>มีโอกาส 10% แช่แข็งศัตรู และทุก 3 รอบ: ฟื้น HP 15% ของ Max HP และ ATK/DEF+20% ในรอบนั้น</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -18749,7 +18749,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>โจมตี ×3.0 ทะลุ DEF + ฟื้นฟู HP 20% เทิร์นนี้ จากนั้น ATK/DEF +30% และฟื้นฟู HP 10% ต่อเทิร์น นาน 3 เทิร์น</t>
+          <t>โจมตี ×3.0 ทะลุ DEF + ฟื้นฟู HP 20% เทิร์นนี้ จากนั้น ATK/DEF +30%, ฟื้นฟู HP 10% ต่อเทิร์น, 10% แช่แข็งศัตรู นาน 3 เทิร์น</t>
         </is>
       </c>
     </row>
@@ -21138,7 +21138,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>โจมตี ×3.0 ทะลุ DEF + หลบการโจมตีสมบูรณ์เทิร์นนี้ → จากนั้น 3 เทิร์น: โอกาสหลบ +30%, โจมตีทะลุ DEF ต่อเนื่อง</t>
+          <t>โจมตี ×3.0 ทะลุ DEF + หลบการโจมตีเทิร์นนี้ → จากนั้น 3 เทิร์น: โอกาสหลบ +30%, โจมตีทะลุ DEF, 50% แช่แข็งศัตรู</t>
         </is>
       </c>
     </row>

--- a/SYMBEAST_Evolve_Forms.xlsx
+++ b/SYMBEAST_Evolve_Forms.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="600" firstSheet="1" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="600" firstSheet="11" activeTab="15" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Evolved Forms" sheetId="1" state="visible" r:id="rId1"/>
@@ -13718,12 +13718,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Every 3 turns: dodges 50%, attacks through DEF with ATK +25%, 25% chance to freeze the enemy</t>
+          <t>Every 3 turns: dodges 50% and attacks through DEF with ATK +25%</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>ทุก 3 เทิร์น: หลบ 50% โจมตีทะลุ DEF ด้วย ATK+25% และโอกาส 25% แช่แข็งศัตรู</t>
+          <t>ทุก 3 เทิร์น: หลบ 50% และโจมตีทะลุ DEF ด้วย ATK+25%</t>
         </is>
       </c>
     </row>
@@ -13745,12 +13745,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Every 3 rounds: recovers 8% of Max HP and ATK/DEF +10% that round; 5% chance to freeze the enemy on hit</t>
+          <t>Every 3 rounds: recovers 8% of Max HP and ATK/DEF +10% that round</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>ทุก 3 รอบ: ฟื้น HP 8% ของ Max HP และ ATK/DEF+10% ในรอบนั้น; 5% โอกาสแช่แข็งศัตรูเมื่อโจมตี</t>
+          <t>ทุก 3 รอบ: ฟื้น HP 8% ของ Max HP และ ATK/DEF+10% ในรอบนั้น</t>
         </is>
       </c>
     </row>
@@ -18700,7 +18700,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>ทุก 3 เทิร์น จะหลบการโจมตีได้ 100% และโจมตีทะลุ DEF ด้วย ATK+50% และมีโอกาส 50% แช่แข็งศัตรู</t>
+          <t>ทุก 3 เทิร์น จะหลบการโจมตีได้ 100% และโจมตีทะลุ DEF ด้วย ATK+50%</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -18710,7 +18710,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>โจมตี ×3.0 ทะลุ DEF + หลบการโจมตีเทิร์นนี้ จากนั้น 3 เทิร์น: โอกาสหลบ +30%, โจมตีทะลุ DEF, 50% แช่แข็งศัตรู</t>
+          <t>โจมตี ×3.0 ทะลุ DEF + หลบการโจมตีสมบูรณ์เทิร์นนี้ จากนั้น 3 เทิร์น: โอกาสหลบ +30%, โจมตีทะลุ DEF ต่อเนื่อง</t>
         </is>
       </c>
     </row>
@@ -18739,7 +18739,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>มีโอกาส 10% แช่แข็งศัตรู และทุก 3 รอบ: ฟื้น HP 15% ของ Max HP และ ATK/DEF+20% ในรอบนั้น</t>
+          <t>ทุก 3 รอบ: ฟื้น HP 15% ของ Max HP และ ATK/DEF+20% ในรอบนั้น</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -18749,7 +18749,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>โจมตี ×3.0 ทะลุ DEF + ฟื้นฟู HP 20% เทิร์นนี้ จากนั้น ATK/DEF +30%, ฟื้นฟู HP 10% ต่อเทิร์น, 10% แช่แข็งศัตรู นาน 3 เทิร์น</t>
+          <t>โจมตี ×3.0 ทะลุ DEF + ฟื้นฟู HP 20% เทิร์นนี้ จากนั้น ATK/DEF +30% และฟื้นฟู HP 10% ต่อเทิร์น นาน 3 เทิร์น</t>
         </is>
       </c>
     </row>
@@ -21138,7 +21138,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>โจมตี ×3.0 ทะลุ DEF + หลบการโจมตีเทิร์นนี้ → จากนั้น 3 เทิร์น: โอกาสหลบ +30%, โจมตีทะลุ DEF, 50% แช่แข็งศัตรู</t>
+          <t>โจมตี ×3.0 ทะลุ DEF + หลบการโจมตีสมบูรณ์เทิร์นนี้ → จากนั้น 3 เทิร์น: โอกาสหลบ +30%, โจมตีทะลุ DEF ต่อเนื่อง</t>
         </is>
       </c>
     </row>
